--- a/ds/planejamento/3semestre/planos/Plano_de_Ensino_PPDM.xlsx
+++ b/ds/planejamento/3semestre/planos/Plano_de_Ensino_PPDM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wellifabio\Desktop\senai2026\ds\planejamento\3semestre\planos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aluno\Desktop\senai2026\ds\planejamento\3semestre\planos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D709E8B-E458-495A-8BE1-8369512197E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5A30AE9-F57E-4844-94FA-3D7BA87C8402}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="144">
   <si>
     <t>PLANO DE ENSINO</t>
   </si>
@@ -268,12 +268,6 @@
     <t>Qual ferramenta podemos utilizar para projetar Aplicativos e simular funcionalidades? Para que serve o Figma? O que é um protótipo funcional?</t>
   </si>
   <si>
-    <t>Situação de aprendizagem formativa. Criação de um protótipo funcional.</t>
-  </si>
-  <si>
-    <t>Situação de aprendizagem formativa. Criação de um protótipo de alte fidelidade.</t>
-  </si>
-  <si>
     <t>O que são efeitos de transição de tela? Como adicionar animações? O que são animações de entrada e saída? Como criar menús flutuantes? Qual a diferença entre tela e modal?</t>
   </si>
   <si>
@@ -418,9 +412,6 @@
   </si>
   <si>
     <t>Como os requisitos funcionais foram definidos? Quais integrantes dos grupos são responsáveis por quais tarefas/requisitos?Qual framework o grupo vai utilizar?Qual problema o aplicativo vai resolver?</t>
-  </si>
-  <si>
-    <t>Projeto prático de um aplicativo com tema definido pelo grupo e apresentado ao instrutor</t>
   </si>
   <si>
     <t>O que é CRUD no desenvolvimento de aplicativos moveis? Como fazemos cadastro de dados via App? Como fazemos alteração e exclusão de dados via App?</t>
@@ -576,6 +567,30 @@
   <si>
     <t>Data:   /   /2026</t>
   </si>
+  <si>
+    <t>Atividade desafiadora. Criação de um protótipo funcional.</t>
+  </si>
+  <si>
+    <t>Atividade desafiadora. Criação de um protótipo de alte fidelidade.</t>
+  </si>
+  <si>
+    <t>Atividade desafiadora. A partir de um protótipo, codificar a interface de um aplicativo.</t>
+  </si>
+  <si>
+    <t>Acertou todos os critérios críticos e pelo menos 3 dos 4 desejáveis</t>
+  </si>
+  <si>
+    <t>Criu os formulários conforme wireframes / esboços disponibilizados</t>
+  </si>
+  <si>
+    <t>Criou os formulários conforme wireframes / esboços disponibilizados</t>
+  </si>
+  <si>
+    <t>Projetou um protótipo</t>
+  </si>
+  <si>
+    <t>Desenvolveu o aplicativo que resolve o problema proposto.</t>
+  </si>
 </sst>
 </file>
 
@@ -585,7 +600,7 @@
     <numFmt numFmtId="164" formatCode="dd/mm"/>
     <numFmt numFmtId="165" formatCode="d/m"/>
   </numFmts>
-  <fonts count="42" x14ac:knownFonts="1">
+  <fonts count="44" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -840,6 +855,20 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -867,7 +896,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="35">
+  <borders count="47">
     <border>
       <left/>
       <right/>
@@ -1187,32 +1216,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color rgb="FF000000"/>
@@ -1267,11 +1270,186 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="176">
+  <cellXfs count="248">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1407,29 +1585,214 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1461,229 +1824,23 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1726,11 +1883,26 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1750,8 +1922,231 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2758,7 +3153,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:AA958"/>
+  <dimension ref="A2:AA959"/>
   <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.125" customWidth="1"/>
@@ -2775,134 +3170,134 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:27" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="53" t="s">
+      <c r="A2" s="139" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
+      <c r="B2" s="139"/>
+      <c r="C2" s="139"/>
+      <c r="D2" s="139"/>
+      <c r="E2" s="139"/>
+      <c r="F2" s="139"/>
+      <c r="G2" s="139"/>
+      <c r="H2" s="139"/>
+      <c r="I2" s="139"/>
+      <c r="J2" s="139"/>
     </row>
     <row r="3" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="67" t="s">
+      <c r="A3" s="136" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="68"/>
-      <c r="C3" s="54" t="s">
+      <c r="B3" s="137"/>
+      <c r="C3" s="140" t="s">
         <v>54</v>
       </c>
-      <c r="D3" s="55"/>
-      <c r="E3" s="61" t="s">
-        <v>136</v>
+      <c r="D3" s="141"/>
+      <c r="E3" s="130" t="s">
+        <v>133</v>
       </c>
-      <c r="F3" s="62"/>
-      <c r="G3" s="52" t="s">
+      <c r="F3" s="131"/>
+      <c r="G3" s="138" t="s">
         <v>30</v>
       </c>
-      <c r="H3" s="52"/>
-      <c r="I3" s="52" t="s">
+      <c r="H3" s="138"/>
+      <c r="I3" s="138" t="s">
         <v>31</v>
       </c>
-      <c r="J3" s="52"/>
+      <c r="J3" s="138"/>
     </row>
     <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="67"/>
-      <c r="B4" s="68"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="65" t="s">
-        <v>137</v>
+      <c r="A4" s="136"/>
+      <c r="B4" s="137"/>
+      <c r="C4" s="142"/>
+      <c r="D4" s="143"/>
+      <c r="E4" s="134" t="s">
+        <v>134</v>
       </c>
-      <c r="F4" s="66"/>
-      <c r="G4" s="51" t="s">
-        <v>138</v>
+      <c r="F4" s="135"/>
+      <c r="G4" s="120" t="s">
+        <v>135</v>
       </c>
-      <c r="H4" s="51"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
+      <c r="H4" s="120"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="121"/>
     </row>
     <row r="5" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="74" t="s">
+      <c r="A5" s="122" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="75"/>
-      <c r="C5" s="58" t="s">
+      <c r="B5" s="103"/>
+      <c r="C5" s="121" t="s">
         <v>55</v>
       </c>
-      <c r="D5" s="58"/>
-      <c r="E5" s="82" t="s">
+      <c r="D5" s="121"/>
+      <c r="E5" s="126" t="s">
         <v>57</v>
       </c>
-      <c r="F5" s="83"/>
-      <c r="G5" s="51" t="s">
+      <c r="F5" s="127"/>
+      <c r="G5" s="120" t="s">
         <v>32</v>
       </c>
-      <c r="H5" s="51"/>
-      <c r="I5" s="51"/>
-      <c r="J5" s="51"/>
+      <c r="H5" s="120"/>
+      <c r="I5" s="120"/>
+      <c r="J5" s="120"/>
     </row>
     <row r="6" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="75"/>
-      <c r="B6" s="76"/>
-      <c r="C6" s="58"/>
-      <c r="D6" s="58"/>
-      <c r="E6" s="59" t="s">
+      <c r="A6" s="103"/>
+      <c r="B6" s="102"/>
+      <c r="C6" s="121"/>
+      <c r="D6" s="121"/>
+      <c r="E6" s="128" t="s">
         <v>43</v>
       </c>
-      <c r="F6" s="60"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="58"/>
-      <c r="I6" s="58"/>
-      <c r="J6" s="58"/>
+      <c r="F6" s="129"/>
+      <c r="G6" s="121"/>
+      <c r="H6" s="121"/>
+      <c r="I6" s="121"/>
+      <c r="J6" s="121"/>
     </row>
     <row r="7" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="74" t="s">
+      <c r="A7" s="122" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="75"/>
-      <c r="C7" s="77" t="s">
+      <c r="B7" s="103"/>
+      <c r="C7" s="123" t="s">
         <v>56</v>
       </c>
-      <c r="D7" s="77"/>
-      <c r="E7" s="63" t="s">
+      <c r="D7" s="123"/>
+      <c r="E7" s="132" t="s">
         <v>58</v>
       </c>
-      <c r="F7" s="64"/>
-      <c r="G7" s="58"/>
-      <c r="H7" s="58"/>
-      <c r="I7" s="58"/>
-      <c r="J7" s="58"/>
+      <c r="F7" s="133"/>
+      <c r="G7" s="121"/>
+      <c r="H7" s="121"/>
+      <c r="I7" s="121"/>
+      <c r="J7" s="121"/>
     </row>
     <row r="8" spans="1:27" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="75"/>
-      <c r="B8" s="76"/>
-      <c r="C8" s="77"/>
-      <c r="D8" s="77"/>
-      <c r="E8" s="63"/>
-      <c r="F8" s="64"/>
-      <c r="G8" s="58"/>
-      <c r="H8" s="58"/>
-      <c r="I8" s="58"/>
-      <c r="J8" s="58"/>
+      <c r="A8" s="103"/>
+      <c r="B8" s="102"/>
+      <c r="C8" s="123"/>
+      <c r="D8" s="123"/>
+      <c r="E8" s="132"/>
+      <c r="F8" s="133"/>
+      <c r="G8" s="121"/>
+      <c r="H8" s="121"/>
+      <c r="I8" s="121"/>
+      <c r="J8" s="121"/>
     </row>
     <row r="9" spans="1:27" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="78" t="s">
+      <c r="A9" s="124" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="78"/>
-      <c r="C9" s="78"/>
-      <c r="D9" s="78"/>
-      <c r="E9" s="78"/>
-      <c r="F9" s="78"/>
-      <c r="G9" s="78"/>
-      <c r="H9" s="78"/>
-      <c r="I9" s="78"/>
-      <c r="J9" s="78"/>
+      <c r="B9" s="124"/>
+      <c r="C9" s="124"/>
+      <c r="D9" s="124"/>
+      <c r="E9" s="124"/>
+      <c r="F9" s="124"/>
+      <c r="G9" s="124"/>
+      <c r="H9" s="124"/>
+      <c r="I9" s="124"/>
+      <c r="J9" s="124"/>
     </row>
     <row r="10" spans="1:27" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="33" t="s">
@@ -2923,14 +3318,14 @@
       <c r="F10" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="G10" s="79" t="s">
+      <c r="G10" s="125" t="s">
         <v>8</v>
       </c>
-      <c r="H10" s="79"/>
-      <c r="I10" s="79" t="s">
+      <c r="H10" s="125"/>
+      <c r="I10" s="125" t="s">
         <v>9</v>
       </c>
-      <c r="J10" s="79"/>
+      <c r="J10" s="125"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -2965,17 +3360,17 @@
       <c r="E11" s="40" t="s">
         <v>62</v>
       </c>
-      <c r="F11" s="32" t="s">
+      <c r="F11" s="174" t="s">
         <v>63</v>
       </c>
-      <c r="G11" s="80" t="s">
+      <c r="G11" s="51" t="s">
         <v>64</v>
       </c>
-      <c r="H11" s="81"/>
-      <c r="I11" s="80" t="s">
+      <c r="H11" s="52"/>
+      <c r="I11" s="51" t="s">
         <v>65</v>
       </c>
-      <c r="J11" s="81"/>
+      <c r="J11" s="52"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
@@ -3010,17 +3405,15 @@
       <c r="E12" s="42" t="s">
         <v>68</v>
       </c>
-      <c r="F12" s="32" t="s">
-        <v>63</v>
-      </c>
-      <c r="G12" s="80" t="s">
+      <c r="F12" s="175"/>
+      <c r="G12" s="51" t="s">
         <v>69</v>
       </c>
-      <c r="H12" s="81"/>
-      <c r="I12" s="72" t="s">
-        <v>71</v>
+      <c r="H12" s="52"/>
+      <c r="I12" s="53" t="s">
+        <v>137</v>
       </c>
-      <c r="J12" s="73"/>
+      <c r="J12" s="54"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
@@ -3055,17 +3448,15 @@
       <c r="E13" s="42" t="s">
         <v>68</v>
       </c>
-      <c r="F13" s="32" t="s">
-        <v>63</v>
-      </c>
-      <c r="G13" s="80" t="s">
-        <v>72</v>
-      </c>
-      <c r="H13" s="81"/>
-      <c r="I13" s="72" t="s">
+      <c r="F13" s="176"/>
+      <c r="G13" s="51" t="s">
         <v>70</v>
       </c>
-      <c r="J13" s="73"/>
+      <c r="H13" s="52"/>
+      <c r="I13" s="53" t="s">
+        <v>136</v>
+      </c>
+      <c r="J13" s="54"/>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
@@ -3086,13 +3477,13 @@
     </row>
     <row r="14" spans="1:27" ht="153" x14ac:dyDescent="0.2">
       <c r="A14" s="37" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B14" s="2">
         <v>8</v>
       </c>
       <c r="C14" s="45" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D14" s="43" t="s">
         <v>66</v>
@@ -3100,17 +3491,17 @@
       <c r="E14" s="44" t="s">
         <v>68</v>
       </c>
-      <c r="F14" s="32" t="s">
-        <v>76</v>
-      </c>
-      <c r="G14" s="80" t="s">
-        <v>73</v>
-      </c>
-      <c r="H14" s="81"/>
-      <c r="I14" s="72" t="s">
+      <c r="F14" s="177" t="s">
         <v>74</v>
       </c>
-      <c r="J14" s="73"/>
+      <c r="G14" s="51" t="s">
+        <v>71</v>
+      </c>
+      <c r="H14" s="52"/>
+      <c r="I14" s="53" t="s">
+        <v>138</v>
+      </c>
+      <c r="J14" s="54"/>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
@@ -3131,7 +3522,7 @@
     </row>
     <row r="15" spans="1:27" ht="140.25" x14ac:dyDescent="0.2">
       <c r="A15" s="36" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B15" s="31">
         <v>8</v>
@@ -3140,22 +3531,20 @@
         <v>67</v>
       </c>
       <c r="D15" s="43" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E15" s="44" t="s">
         <v>68</v>
       </c>
-      <c r="F15" s="32" t="s">
-        <v>76</v>
+      <c r="F15" s="175"/>
+      <c r="G15" s="51" t="s">
+        <v>75</v>
       </c>
-      <c r="G15" s="80" t="s">
-        <v>77</v>
+      <c r="H15" s="52"/>
+      <c r="I15" s="53" t="s">
+        <v>72</v>
       </c>
-      <c r="H15" s="81"/>
-      <c r="I15" s="72" t="s">
-        <v>74</v>
-      </c>
-      <c r="J15" s="73"/>
+      <c r="J15" s="54"/>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
@@ -3174,9 +3563,9 @@
       <c r="Z15" s="3"/>
       <c r="AA15" s="3"/>
     </row>
-    <row r="16" spans="1:27" ht="102" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" ht="102" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="37" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B16" s="2">
         <v>8</v>
@@ -3185,22 +3574,20 @@
         <v>67</v>
       </c>
       <c r="D16" s="43" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E16" s="44" t="s">
         <v>68</v>
       </c>
-      <c r="F16" s="32" t="s">
-        <v>76</v>
+      <c r="F16" s="175"/>
+      <c r="G16" s="51" t="s">
+        <v>78</v>
       </c>
-      <c r="G16" s="80" t="s">
-        <v>80</v>
+      <c r="H16" s="52"/>
+      <c r="I16" s="178" t="s">
+        <v>72</v>
       </c>
-      <c r="H16" s="81"/>
-      <c r="I16" s="72" t="s">
-        <v>74</v>
-      </c>
-      <c r="J16" s="73"/>
+      <c r="J16" s="179"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
@@ -3221,31 +3608,27 @@
     </row>
     <row r="17" spans="1:27" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A17" s="36" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B17" s="31">
         <v>8</v>
       </c>
       <c r="C17" s="45" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D17" s="43" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E17" s="44" t="s">
         <v>68</v>
       </c>
-      <c r="F17" s="32" t="s">
-        <v>76</v>
+      <c r="F17" s="175"/>
+      <c r="G17" s="51" t="s">
+        <v>79</v>
       </c>
-      <c r="G17" s="80" t="s">
-        <v>81</v>
-      </c>
-      <c r="H17" s="81"/>
-      <c r="I17" s="72" t="s">
-        <v>82</v>
-      </c>
-      <c r="J17" s="73"/>
+      <c r="H17" s="52"/>
+      <c r="I17" s="180"/>
+      <c r="J17" s="181"/>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
@@ -3272,25 +3655,23 @@
         <v>4</v>
       </c>
       <c r="C18" s="45" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D18" s="43" t="s">
+        <v>81</v>
+      </c>
+      <c r="E18" s="44" t="s">
+        <v>82</v>
+      </c>
+      <c r="F18" s="175"/>
+      <c r="G18" s="51" t="s">
         <v>83</v>
       </c>
-      <c r="E18" s="44" t="s">
-        <v>84</v>
+      <c r="H18" s="52"/>
+      <c r="I18" s="178" t="s">
+        <v>80</v>
       </c>
-      <c r="F18" s="32" t="s">
-        <v>76</v>
-      </c>
-      <c r="G18" s="80" t="s">
-        <v>85</v>
-      </c>
-      <c r="H18" s="81"/>
-      <c r="I18" s="72" t="s">
-        <v>74</v>
-      </c>
-      <c r="J18" s="73"/>
+      <c r="J18" s="179"/>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
@@ -3311,31 +3692,27 @@
     </row>
     <row r="19" spans="1:27" ht="242.25" x14ac:dyDescent="0.2">
       <c r="A19" s="36" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B19" s="31">
         <v>8</v>
       </c>
       <c r="C19" s="45" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D19" s="43" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E19" s="44" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
-      <c r="F19" s="32" t="s">
-        <v>76</v>
+      <c r="F19" s="176"/>
+      <c r="G19" s="51" t="s">
+        <v>93</v>
       </c>
-      <c r="G19" s="80" t="s">
-        <v>95</v>
-      </c>
-      <c r="H19" s="81"/>
-      <c r="I19" s="72" t="s">
-        <v>74</v>
-      </c>
-      <c r="J19" s="73"/>
+      <c r="H19" s="52"/>
+      <c r="I19" s="180"/>
+      <c r="J19" s="181"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
@@ -3356,31 +3733,31 @@
     </row>
     <row r="20" spans="1:27" ht="204" x14ac:dyDescent="0.2">
       <c r="A20" s="37" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B20" s="2">
         <v>16</v>
       </c>
       <c r="C20" s="45" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D20" s="47" t="s">
+        <v>99</v>
+      </c>
+      <c r="E20" s="44" t="s">
+        <v>100</v>
+      </c>
+      <c r="F20" s="32" t="s">
         <v>101</v>
       </c>
-      <c r="E20" s="44" t="s">
+      <c r="G20" s="51" t="s">
         <v>102</v>
       </c>
-      <c r="F20" s="32" t="s">
-        <v>103</v>
+      <c r="H20" s="52"/>
+      <c r="I20" s="178" t="s">
+        <v>72</v>
       </c>
-      <c r="G20" s="80" t="s">
-        <v>104</v>
-      </c>
-      <c r="H20" s="81"/>
-      <c r="I20" s="121" t="s">
-        <v>105</v>
-      </c>
-      <c r="J20" s="122"/>
+      <c r="J20" s="179"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
@@ -3399,33 +3776,31 @@
       <c r="Z20" s="1"/>
       <c r="AA20" s="1"/>
     </row>
-    <row r="21" spans="1:27" ht="76.5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:27" ht="76.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="37" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B21" s="2">
         <v>8</v>
       </c>
       <c r="C21" s="45" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D21" s="47" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E21" s="44" t="s">
         <v>68</v>
       </c>
       <c r="F21" s="32" t="s">
-        <v>76</v>
-      </c>
-      <c r="G21" s="80" t="s">
-        <v>106</v>
-      </c>
-      <c r="H21" s="81"/>
-      <c r="I21" s="72" t="s">
         <v>74</v>
       </c>
-      <c r="J21" s="73"/>
+      <c r="G21" s="51" t="s">
+        <v>103</v>
+      </c>
+      <c r="H21" s="52"/>
+      <c r="I21" s="180"/>
+      <c r="J21" s="181"/>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
@@ -3456,10 +3831,10 @@
       <c r="D22" s="22"/>
       <c r="E22" s="22"/>
       <c r="F22" s="23"/>
-      <c r="G22" s="142"/>
-      <c r="H22" s="143"/>
-      <c r="I22" s="144"/>
-      <c r="J22" s="145"/>
+      <c r="G22" s="55"/>
+      <c r="H22" s="56"/>
+      <c r="I22" s="57"/>
+      <c r="J22" s="58"/>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
@@ -3479,18 +3854,18 @@
       <c r="AA22" s="1"/>
     </row>
     <row r="23" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="123" t="s">
+      <c r="A23" s="74" t="s">
         <v>51</v>
       </c>
-      <c r="B23" s="124"/>
-      <c r="C23" s="124"/>
-      <c r="D23" s="124"/>
-      <c r="E23" s="124"/>
-      <c r="F23" s="124"/>
-      <c r="G23" s="124"/>
-      <c r="H23" s="124"/>
-      <c r="I23" s="124"/>
-      <c r="J23" s="125"/>
+      <c r="B23" s="75"/>
+      <c r="C23" s="75"/>
+      <c r="D23" s="75"/>
+      <c r="E23" s="75"/>
+      <c r="F23" s="75"/>
+      <c r="G23" s="75"/>
+      <c r="H23" s="75"/>
+      <c r="I23" s="75"/>
+      <c r="J23" s="76"/>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
@@ -3510,18 +3885,18 @@
       <c r="AA23" s="1"/>
     </row>
     <row r="24" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="126" t="s">
+      <c r="A24" s="77" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="126"/>
-      <c r="C24" s="126"/>
-      <c r="D24" s="126"/>
-      <c r="E24" s="126"/>
-      <c r="F24" s="126"/>
-      <c r="G24" s="126"/>
-      <c r="H24" s="126"/>
-      <c r="I24" s="126"/>
-      <c r="J24" s="126"/>
+      <c r="B24" s="77"/>
+      <c r="C24" s="77"/>
+      <c r="D24" s="77"/>
+      <c r="E24" s="77"/>
+      <c r="F24" s="77"/>
+      <c r="G24" s="77"/>
+      <c r="H24" s="77"/>
+      <c r="I24" s="77"/>
+      <c r="J24" s="77"/>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
@@ -3541,18 +3916,18 @@
       <c r="AA24" s="1"/>
     </row>
     <row r="25" spans="1:27" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="120" t="s">
-        <v>125</v>
+      <c r="A25" s="70" t="s">
+        <v>122</v>
       </c>
-      <c r="B25" s="120"/>
-      <c r="C25" s="120"/>
-      <c r="D25" s="120"/>
-      <c r="E25" s="120"/>
-      <c r="F25" s="120"/>
-      <c r="G25" s="120"/>
-      <c r="H25" s="120"/>
-      <c r="I25" s="120"/>
-      <c r="J25" s="120"/>
+      <c r="B25" s="70"/>
+      <c r="C25" s="70"/>
+      <c r="D25" s="70"/>
+      <c r="E25" s="70"/>
+      <c r="F25" s="70"/>
+      <c r="G25" s="70"/>
+      <c r="H25" s="70"/>
+      <c r="I25" s="70"/>
+      <c r="J25" s="70"/>
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
@@ -3572,18 +3947,18 @@
       <c r="AA25" s="1"/>
     </row>
     <row r="26" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="126" t="s">
+      <c r="A26" s="77" t="s">
         <v>35</v>
       </c>
-      <c r="B26" s="126"/>
-      <c r="C26" s="126"/>
-      <c r="D26" s="126"/>
-      <c r="E26" s="126"/>
-      <c r="F26" s="126"/>
-      <c r="G26" s="126"/>
-      <c r="H26" s="126"/>
-      <c r="I26" s="126"/>
-      <c r="J26" s="126"/>
+      <c r="B26" s="77"/>
+      <c r="C26" s="77"/>
+      <c r="D26" s="77"/>
+      <c r="E26" s="77"/>
+      <c r="F26" s="77"/>
+      <c r="G26" s="77"/>
+      <c r="H26" s="77"/>
+      <c r="I26" s="77"/>
+      <c r="J26" s="77"/>
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
@@ -3603,18 +3978,18 @@
       <c r="AA26" s="1"/>
     </row>
     <row r="27" spans="1:27" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="120" t="s">
-        <v>108</v>
+      <c r="A27" s="70" t="s">
+        <v>105</v>
       </c>
-      <c r="B27" s="120"/>
-      <c r="C27" s="120"/>
-      <c r="D27" s="120"/>
-      <c r="E27" s="120"/>
-      <c r="F27" s="120"/>
-      <c r="G27" s="120"/>
-      <c r="H27" s="120"/>
-      <c r="I27" s="120"/>
-      <c r="J27" s="120"/>
+      <c r="B27" s="70"/>
+      <c r="C27" s="70"/>
+      <c r="D27" s="70"/>
+      <c r="E27" s="70"/>
+      <c r="F27" s="70"/>
+      <c r="G27" s="70"/>
+      <c r="H27" s="70"/>
+      <c r="I27" s="70"/>
+      <c r="J27" s="70"/>
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
@@ -3631,18 +4006,18 @@
       <c r="AA27" s="1"/>
     </row>
     <row r="28" spans="1:27" ht="18" x14ac:dyDescent="0.2">
-      <c r="A28" s="126" t="s">
+      <c r="A28" s="77" t="s">
         <v>36</v>
       </c>
-      <c r="B28" s="126"/>
-      <c r="C28" s="126"/>
-      <c r="D28" s="126"/>
-      <c r="E28" s="126"/>
-      <c r="F28" s="126"/>
-      <c r="G28" s="126"/>
-      <c r="H28" s="126"/>
-      <c r="I28" s="126"/>
-      <c r="J28" s="126"/>
+      <c r="B28" s="77"/>
+      <c r="C28" s="77"/>
+      <c r="D28" s="77"/>
+      <c r="E28" s="77"/>
+      <c r="F28" s="77"/>
+      <c r="G28" s="77"/>
+      <c r="H28" s="77"/>
+      <c r="I28" s="77"/>
+      <c r="J28" s="77"/>
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
@@ -3662,18 +4037,18 @@
       <c r="AA28" s="1"/>
     </row>
     <row r="29" spans="1:27" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="120" t="s">
-        <v>109</v>
+      <c r="A29" s="70" t="s">
+        <v>106</v>
       </c>
-      <c r="B29" s="120"/>
-      <c r="C29" s="120"/>
-      <c r="D29" s="120"/>
-      <c r="E29" s="120"/>
-      <c r="F29" s="120"/>
-      <c r="G29" s="120"/>
-      <c r="H29" s="120"/>
-      <c r="I29" s="120"/>
-      <c r="J29" s="120"/>
+      <c r="B29" s="70"/>
+      <c r="C29" s="70"/>
+      <c r="D29" s="70"/>
+      <c r="E29" s="70"/>
+      <c r="F29" s="70"/>
+      <c r="G29" s="70"/>
+      <c r="H29" s="70"/>
+      <c r="I29" s="70"/>
+      <c r="J29" s="70"/>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
@@ -3693,16 +4068,16 @@
       <c r="AA29" s="1"/>
     </row>
     <row r="30" spans="1:27" ht="18" x14ac:dyDescent="0.2">
-      <c r="A30" s="130"/>
-      <c r="B30" s="131"/>
-      <c r="C30" s="131"/>
-      <c r="D30" s="131"/>
-      <c r="E30" s="131"/>
-      <c r="F30" s="131"/>
-      <c r="G30" s="131"/>
-      <c r="H30" s="131"/>
-      <c r="I30" s="131"/>
-      <c r="J30" s="132"/>
+      <c r="A30" s="83"/>
+      <c r="B30" s="84"/>
+      <c r="C30" s="84"/>
+      <c r="D30" s="84"/>
+      <c r="E30" s="84"/>
+      <c r="F30" s="84"/>
+      <c r="G30" s="84"/>
+      <c r="H30" s="84"/>
+      <c r="I30" s="84"/>
+      <c r="J30" s="85"/>
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
@@ -3722,16 +4097,16 @@
       <c r="AA30" s="1"/>
     </row>
     <row r="31" spans="1:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="133"/>
-      <c r="B31" s="134"/>
-      <c r="C31" s="134"/>
-      <c r="D31" s="134"/>
-      <c r="E31" s="134"/>
-      <c r="F31" s="134"/>
-      <c r="G31" s="134"/>
-      <c r="H31" s="134"/>
-      <c r="I31" s="134"/>
-      <c r="J31" s="135"/>
+      <c r="A31" s="86"/>
+      <c r="B31" s="87"/>
+      <c r="C31" s="87"/>
+      <c r="D31" s="87"/>
+      <c r="E31" s="87"/>
+      <c r="F31" s="87"/>
+      <c r="G31" s="87"/>
+      <c r="H31" s="87"/>
+      <c r="I31" s="87"/>
+      <c r="J31" s="88"/>
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
@@ -3751,18 +4126,18 @@
       <c r="AA31" s="1"/>
     </row>
     <row r="32" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="69" t="s">
+      <c r="A32" s="118" t="s">
         <v>37</v>
       </c>
-      <c r="B32" s="69"/>
-      <c r="C32" s="69"/>
-      <c r="D32" s="69"/>
-      <c r="E32" s="69"/>
-      <c r="F32" s="69"/>
-      <c r="G32" s="69"/>
-      <c r="H32" s="69"/>
-      <c r="I32" s="69"/>
-      <c r="J32" s="69"/>
+      <c r="B32" s="118"/>
+      <c r="C32" s="118"/>
+      <c r="D32" s="118"/>
+      <c r="E32" s="118"/>
+      <c r="F32" s="118"/>
+      <c r="G32" s="118"/>
+      <c r="H32" s="118"/>
+      <c r="I32" s="118"/>
+      <c r="J32" s="118"/>
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
@@ -3782,22 +4157,22 @@
       <c r="AA32" s="1"/>
     </row>
     <row r="33" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="127" t="s">
+      <c r="A33" s="80" t="s">
         <v>39</v>
       </c>
-      <c r="B33" s="128"/>
-      <c r="C33" s="128"/>
-      <c r="D33" s="129" t="s">
+      <c r="B33" s="81"/>
+      <c r="C33" s="81"/>
+      <c r="D33" s="82" t="s">
         <v>11</v>
       </c>
-      <c r="E33" s="129"/>
-      <c r="F33" s="129"/>
-      <c r="G33" s="70" t="s">
+      <c r="E33" s="82"/>
+      <c r="F33" s="82"/>
+      <c r="G33" s="119" t="s">
         <v>40</v>
       </c>
-      <c r="H33" s="71"/>
-      <c r="I33" s="71"/>
-      <c r="J33" s="71"/>
+      <c r="H33" s="66"/>
+      <c r="I33" s="66"/>
+      <c r="J33" s="66"/>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
@@ -3817,12 +4192,12 @@
       <c r="AA33" s="1"/>
     </row>
     <row r="34" spans="1:27" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="128"/>
-      <c r="B34" s="128"/>
-      <c r="C34" s="128"/>
-      <c r="D34" s="129"/>
-      <c r="E34" s="129"/>
-      <c r="F34" s="129"/>
+      <c r="A34" s="81"/>
+      <c r="B34" s="81"/>
+      <c r="C34" s="81"/>
+      <c r="D34" s="82"/>
+      <c r="E34" s="82"/>
+      <c r="F34" s="82"/>
       <c r="G34" s="29">
         <v>1</v>
       </c>
@@ -3854,18 +4229,18 @@
       <c r="AA34" s="1"/>
     </row>
     <row r="35" spans="1:27" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="113" t="s">
+      <c r="A35" s="107" t="s">
         <v>14</v>
       </c>
-      <c r="B35" s="84" t="s">
-        <v>110</v>
+      <c r="B35" s="110" t="s">
+        <v>107</v>
       </c>
-      <c r="C35" s="85"/>
-      <c r="D35" s="86" t="s">
-        <v>114</v>
+      <c r="C35" s="111"/>
+      <c r="D35" s="112" t="s">
+        <v>111</v>
       </c>
-      <c r="E35" s="76"/>
-      <c r="F35" s="75"/>
+      <c r="E35" s="102"/>
+      <c r="F35" s="103"/>
       <c r="G35" s="12"/>
       <c r="H35" s="26"/>
       <c r="I35" s="27"/>
@@ -3889,16 +4264,16 @@
       <c r="AA35" s="1"/>
     </row>
     <row r="36" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="114"/>
-      <c r="B36" s="84" t="s">
-        <v>111</v>
+      <c r="A36" s="108"/>
+      <c r="B36" s="110" t="s">
+        <v>108</v>
       </c>
-      <c r="C36" s="85"/>
-      <c r="D36" s="86" t="s">
-        <v>115</v>
+      <c r="C36" s="111"/>
+      <c r="D36" s="112" t="s">
+        <v>112</v>
       </c>
-      <c r="E36" s="76"/>
-      <c r="F36" s="75"/>
+      <c r="E36" s="102"/>
+      <c r="F36" s="103"/>
       <c r="G36" s="12"/>
       <c r="H36" s="26"/>
       <c r="I36" s="22"/>
@@ -3921,17 +4296,17 @@
       <c r="Z36" s="1"/>
       <c r="AA36" s="1"/>
     </row>
-    <row r="37" spans="1:27" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="114"/>
-      <c r="B37" s="87" t="s">
-        <v>112</v>
+    <row r="37" spans="1:27" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="108"/>
+      <c r="B37" s="242" t="s">
+        <v>109</v>
       </c>
-      <c r="C37" s="88"/>
-      <c r="D37" s="89" t="s">
-        <v>116</v>
+      <c r="C37" s="243"/>
+      <c r="D37" s="246" t="s">
+        <v>142</v>
       </c>
-      <c r="E37" s="76"/>
-      <c r="F37" s="75"/>
+      <c r="E37" s="121"/>
+      <c r="F37" s="247"/>
       <c r="G37" s="12"/>
       <c r="H37" s="26"/>
       <c r="I37" s="22"/>
@@ -3954,17 +4329,15 @@
       <c r="Z37" s="1"/>
       <c r="AA37" s="1"/>
     </row>
-    <row r="38" spans="1:27" ht="69" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="114"/>
-      <c r="B38" s="90" t="s">
-        <v>113</v>
+    <row r="38" spans="1:27" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="108"/>
+      <c r="B38" s="244"/>
+      <c r="C38" s="245"/>
+      <c r="D38" s="101" t="s">
+        <v>143</v>
       </c>
-      <c r="C38" s="91"/>
-      <c r="D38" s="92" t="s">
-        <v>118</v>
-      </c>
-      <c r="E38" s="93"/>
-      <c r="F38" s="94"/>
+      <c r="E38" s="102"/>
+      <c r="F38" s="103"/>
       <c r="G38" s="12"/>
       <c r="H38" s="26"/>
       <c r="I38" s="22"/>
@@ -3987,17 +4360,17 @@
       <c r="Z38" s="1"/>
       <c r="AA38" s="1"/>
     </row>
-    <row r="39" spans="1:27" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="114"/>
-      <c r="B39" s="90" t="s">
-        <v>67</v>
+    <row r="39" spans="1:27" ht="69" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="108"/>
+      <c r="B39" s="78" t="s">
+        <v>110</v>
       </c>
-      <c r="C39" s="91"/>
-      <c r="D39" s="100" t="s">
-        <v>119</v>
+      <c r="C39" s="79"/>
+      <c r="D39" s="115" t="s">
+        <v>141</v>
       </c>
-      <c r="E39" s="101"/>
-      <c r="F39" s="102"/>
+      <c r="E39" s="116"/>
+      <c r="F39" s="117"/>
       <c r="G39" s="12"/>
       <c r="H39" s="26"/>
       <c r="I39" s="22"/>
@@ -4020,17 +4393,17 @@
       <c r="Z39" s="1"/>
       <c r="AA39" s="1"/>
     </row>
-    <row r="40" spans="1:27" ht="84" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="115"/>
-      <c r="B40" s="103" t="s">
-        <v>90</v>
+    <row r="40" spans="1:27" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="108"/>
+      <c r="B40" s="78" t="s">
+        <v>67</v>
       </c>
-      <c r="C40" s="104"/>
-      <c r="D40" s="89" t="s">
-        <v>117</v>
+      <c r="C40" s="79"/>
+      <c r="D40" s="96" t="s">
+        <v>116</v>
       </c>
-      <c r="E40" s="76"/>
-      <c r="F40" s="75"/>
+      <c r="E40" s="97"/>
+      <c r="F40" s="98"/>
       <c r="G40" s="12"/>
       <c r="H40" s="26"/>
       <c r="I40" s="22"/>
@@ -4053,19 +4426,17 @@
       <c r="Z40" s="1"/>
       <c r="AA40" s="1"/>
     </row>
-    <row r="41" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="105" t="s">
-        <v>33</v>
+    <row r="41" spans="1:27" ht="84" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="109"/>
+      <c r="B41" s="99" t="s">
+        <v>88</v>
       </c>
-      <c r="B41" s="108" t="s">
-        <v>47</v>
+      <c r="C41" s="100"/>
+      <c r="D41" s="101" t="s">
+        <v>114</v>
       </c>
-      <c r="C41" s="109"/>
-      <c r="D41" s="110" t="s">
-        <v>123</v>
-      </c>
-      <c r="E41" s="111"/>
-      <c r="F41" s="112"/>
+      <c r="E41" s="102"/>
+      <c r="F41" s="103"/>
       <c r="G41" s="12"/>
       <c r="H41" s="26"/>
       <c r="I41" s="22"/>
@@ -4089,16 +4460,18 @@
       <c r="AA41" s="1"/>
     </row>
     <row r="42" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="106"/>
-      <c r="B42" s="108" t="s">
+      <c r="A42" s="104" t="s">
+        <v>33</v>
+      </c>
+      <c r="B42" s="72" t="s">
+        <v>47</v>
+      </c>
+      <c r="C42" s="73"/>
+      <c r="D42" s="71" t="s">
         <v>120</v>
       </c>
-      <c r="C42" s="109"/>
-      <c r="D42" s="110" t="s">
-        <v>121</v>
-      </c>
-      <c r="E42" s="111"/>
-      <c r="F42" s="112"/>
+      <c r="E42" s="61"/>
+      <c r="F42" s="62"/>
       <c r="G42" s="12"/>
       <c r="H42" s="26"/>
       <c r="I42" s="22"/>
@@ -4122,16 +4495,16 @@
       <c r="AA42" s="1"/>
     </row>
     <row r="43" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="106"/>
-      <c r="B43" s="108" t="s">
-        <v>48</v>
+      <c r="A43" s="105"/>
+      <c r="B43" s="72" t="s">
+        <v>117</v>
       </c>
-      <c r="C43" s="109"/>
-      <c r="D43" s="110" t="s">
-        <v>122</v>
+      <c r="C43" s="73"/>
+      <c r="D43" s="71" t="s">
+        <v>118</v>
       </c>
-      <c r="E43" s="111"/>
-      <c r="F43" s="112"/>
+      <c r="E43" s="61"/>
+      <c r="F43" s="62"/>
       <c r="G43" s="12"/>
       <c r="H43" s="26"/>
       <c r="I43" s="22"/>
@@ -4155,16 +4528,16 @@
       <c r="AA43" s="1"/>
     </row>
     <row r="44" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="107"/>
-      <c r="B44" s="108" t="s">
-        <v>15</v>
+      <c r="A44" s="105"/>
+      <c r="B44" s="72" t="s">
+        <v>48</v>
       </c>
-      <c r="C44" s="109"/>
-      <c r="D44" s="110" t="s">
-        <v>124</v>
+      <c r="C44" s="73"/>
+      <c r="D44" s="71" t="s">
+        <v>119</v>
       </c>
-      <c r="E44" s="111"/>
-      <c r="F44" s="112"/>
+      <c r="E44" s="61"/>
+      <c r="F44" s="62"/>
       <c r="G44" s="12"/>
       <c r="H44" s="26"/>
       <c r="I44" s="22"/>
@@ -4187,17 +4560,21 @@
       <c r="Z44" s="1"/>
       <c r="AA44" s="1"/>
     </row>
-    <row r="45" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="99"/>
-      <c r="B45" s="99"/>
-      <c r="C45" s="99"/>
-      <c r="D45" s="99"/>
-      <c r="E45" s="99"/>
-      <c r="F45" s="99"/>
-      <c r="G45" s="99"/>
-      <c r="H45" s="99"/>
-      <c r="I45" s="1"/>
-      <c r="J45" s="1"/>
+    <row r="45" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="106"/>
+      <c r="B45" s="72" t="s">
+        <v>15</v>
+      </c>
+      <c r="C45" s="73"/>
+      <c r="D45" s="71" t="s">
+        <v>121</v>
+      </c>
+      <c r="E45" s="61"/>
+      <c r="F45" s="62"/>
+      <c r="G45" s="12"/>
+      <c r="H45" s="26"/>
+      <c r="I45" s="22"/>
+      <c r="J45" s="22"/>
       <c r="K45" s="1"/>
       <c r="L45" s="1"/>
       <c r="M45" s="1"/>
@@ -4217,18 +4594,14 @@
       <c r="AA45" s="1"/>
     </row>
     <row r="46" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="95" t="s">
-        <v>16</v>
-      </c>
-      <c r="B46" s="96"/>
-      <c r="C46" s="96"/>
-      <c r="D46" s="96"/>
-      <c r="E46" s="97"/>
-      <c r="F46" s="98" t="s">
-        <v>17</v>
-      </c>
-      <c r="G46" s="96"/>
-      <c r="H46" s="97"/>
+      <c r="A46" s="95"/>
+      <c r="B46" s="95"/>
+      <c r="C46" s="95"/>
+      <c r="D46" s="95"/>
+      <c r="E46" s="95"/>
+      <c r="F46" s="95"/>
+      <c r="G46" s="95"/>
+      <c r="H46" s="95"/>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
       <c r="K46" s="1"/>
@@ -4250,20 +4623,18 @@
       <c r="AA46" s="1"/>
     </row>
     <row r="47" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="13">
-        <v>5</v>
+      <c r="A47" s="91" t="s">
+        <v>16</v>
       </c>
-      <c r="B47" s="118" t="s">
-        <v>18</v>
+      <c r="B47" s="92"/>
+      <c r="C47" s="92"/>
+      <c r="D47" s="92"/>
+      <c r="E47" s="93"/>
+      <c r="F47" s="94" t="s">
+        <v>17</v>
       </c>
-      <c r="C47" s="111"/>
-      <c r="D47" s="111"/>
-      <c r="E47" s="112"/>
-      <c r="F47" s="117">
-        <v>100</v>
-      </c>
-      <c r="G47" s="111"/>
-      <c r="H47" s="112"/>
+      <c r="G47" s="92"/>
+      <c r="H47" s="93"/>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
       <c r="K47" s="1"/>
@@ -4286,19 +4657,19 @@
     </row>
     <row r="48" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="13">
-        <v>4</v>
+        <v>5</v>
       </c>
-      <c r="B48" s="119" t="s">
-        <v>50</v>
+      <c r="B48" s="60" t="s">
+        <v>18</v>
       </c>
-      <c r="C48" s="111"/>
-      <c r="D48" s="111"/>
-      <c r="E48" s="112"/>
-      <c r="F48" s="117">
-        <v>80</v>
+      <c r="C48" s="61"/>
+      <c r="D48" s="61"/>
+      <c r="E48" s="62"/>
+      <c r="F48" s="63">
+        <v>100</v>
       </c>
-      <c r="G48" s="111"/>
-      <c r="H48" s="112"/>
+      <c r="G48" s="61"/>
+      <c r="H48" s="62"/>
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
@@ -4321,19 +4692,19 @@
     </row>
     <row r="49" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="13">
-        <v>3</v>
+        <v>4</v>
       </c>
-      <c r="B49" s="119" t="s">
-        <v>49</v>
+      <c r="B49" s="90" t="s">
+        <v>50</v>
       </c>
-      <c r="C49" s="111"/>
-      <c r="D49" s="111"/>
-      <c r="E49" s="112"/>
-      <c r="F49" s="117">
-        <v>65</v>
+      <c r="C49" s="61"/>
+      <c r="D49" s="61"/>
+      <c r="E49" s="62"/>
+      <c r="F49" s="63">
+        <v>80</v>
       </c>
-      <c r="G49" s="111"/>
-      <c r="H49" s="112"/>
+      <c r="G49" s="61"/>
+      <c r="H49" s="62"/>
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
@@ -4356,19 +4727,19 @@
     </row>
     <row r="50" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
-      <c r="B50" s="116" t="s">
-        <v>19</v>
+      <c r="B50" s="90" t="s">
+        <v>49</v>
       </c>
-      <c r="C50" s="111"/>
-      <c r="D50" s="111"/>
-      <c r="E50" s="112"/>
-      <c r="F50" s="117">
-        <v>50</v>
+      <c r="C50" s="61"/>
+      <c r="D50" s="61"/>
+      <c r="E50" s="62"/>
+      <c r="F50" s="63">
+        <v>65</v>
       </c>
-      <c r="G50" s="111"/>
-      <c r="H50" s="112"/>
+      <c r="G50" s="61"/>
+      <c r="H50" s="62"/>
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
       <c r="K50" s="1"/>
@@ -4391,19 +4762,19 @@
     </row>
     <row r="51" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
-      <c r="B51" s="118" t="s">
-        <v>20</v>
+      <c r="B51" s="89" t="s">
+        <v>19</v>
       </c>
-      <c r="C51" s="111"/>
-      <c r="D51" s="111"/>
-      <c r="E51" s="112"/>
-      <c r="F51" s="117">
-        <v>30</v>
+      <c r="C51" s="61"/>
+      <c r="D51" s="61"/>
+      <c r="E51" s="62"/>
+      <c r="F51" s="63">
+        <v>50</v>
       </c>
-      <c r="G51" s="111"/>
-      <c r="H51" s="112"/>
+      <c r="G51" s="61"/>
+      <c r="H51" s="62"/>
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
@@ -4424,15 +4795,21 @@
       <c r="Z51" s="1"/>
       <c r="AA51" s="1"/>
     </row>
-    <row r="52" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="14"/>
-      <c r="B52" s="14"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="15"/>
-      <c r="E52" s="15"/>
-      <c r="F52" s="16"/>
-      <c r="G52" s="17"/>
-      <c r="H52" s="17"/>
+    <row r="52" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="13">
+        <v>1</v>
+      </c>
+      <c r="B52" s="60" t="s">
+        <v>20</v>
+      </c>
+      <c r="C52" s="61"/>
+      <c r="D52" s="61"/>
+      <c r="E52" s="62"/>
+      <c r="F52" s="63">
+        <v>30</v>
+      </c>
+      <c r="G52" s="61"/>
+      <c r="H52" s="62"/>
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
@@ -4453,19 +4830,13 @@
       <c r="Z52" s="1"/>
       <c r="AA52" s="1"/>
     </row>
-    <row r="53" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="17"/>
-      <c r="B53" s="17"/>
-      <c r="C53" s="18"/>
-      <c r="D53" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="E53" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="F53" s="24" t="s">
-        <v>23</v>
-      </c>
+    <row r="53" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="14"/>
+      <c r="B53" s="14"/>
+      <c r="C53" s="14"/>
+      <c r="D53" s="15"/>
+      <c r="E53" s="15"/>
+      <c r="F53" s="16"/>
       <c r="G53" s="17"/>
       <c r="H53" s="17"/>
       <c r="I53" s="1"/>
@@ -4491,22 +4862,18 @@
     <row r="54" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="17"/>
       <c r="B54" s="17"/>
-      <c r="C54" s="17"/>
-      <c r="D54" s="25" t="s">
-        <v>24</v>
+      <c r="C54" s="18"/>
+      <c r="D54" s="24" t="s">
+        <v>21</v>
       </c>
-      <c r="E54" s="137">
-        <v>1</v>
+      <c r="E54" s="24" t="s">
+        <v>22</v>
       </c>
-      <c r="F54" s="137">
-        <v>0</v>
+      <c r="F54" s="24" t="s">
+        <v>23</v>
       </c>
-      <c r="G54" s="71" t="s">
-        <v>25</v>
-      </c>
-      <c r="H54" s="140" t="s">
-        <v>26</v>
-      </c>
+      <c r="G54" s="17"/>
+      <c r="H54" s="17"/>
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
       <c r="K54" s="1"/>
@@ -4531,13 +4898,21 @@
       <c r="A55" s="17"/>
       <c r="B55" s="17"/>
       <c r="C55" s="17"/>
-      <c r="D55" s="35" t="s">
-        <v>27</v>
+      <c r="D55" s="25" t="s">
+        <v>24</v>
       </c>
-      <c r="E55" s="138"/>
-      <c r="F55" s="138"/>
-      <c r="G55" s="139"/>
-      <c r="H55" s="141"/>
+      <c r="E55" s="64">
+        <v>1</v>
+      </c>
+      <c r="F55" s="64">
+        <v>0</v>
+      </c>
+      <c r="G55" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="H55" s="68" t="s">
+        <v>26</v>
+      </c>
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
       <c r="K55" s="1"/>
@@ -4558,19 +4933,19 @@
       <c r="Z55" s="1"/>
       <c r="AA55" s="1"/>
     </row>
-    <row r="56" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="136" t="s">
-        <v>42</v>
+    <row r="56" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="17"/>
+      <c r="B56" s="17"/>
+      <c r="C56" s="17"/>
+      <c r="D56" s="35" t="s">
+        <v>27</v>
       </c>
-      <c r="B56" s="136"/>
-      <c r="C56" s="136"/>
-      <c r="D56" s="136"/>
-      <c r="E56" s="136"/>
-      <c r="F56" s="136"/>
-      <c r="G56" s="136"/>
-      <c r="H56" s="136"/>
-      <c r="I56" s="136"/>
-      <c r="J56" s="136"/>
+      <c r="E56" s="65"/>
+      <c r="F56" s="65"/>
+      <c r="G56" s="67"/>
+      <c r="H56" s="69"/>
+      <c r="I56" s="1"/>
+      <c r="J56" s="1"/>
       <c r="K56" s="1"/>
       <c r="L56" s="1"/>
       <c r="M56" s="1"/>
@@ -4590,16 +4965,18 @@
       <c r="AA56" s="1"/>
     </row>
     <row r="57" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="136"/>
-      <c r="B57" s="136"/>
-      <c r="C57" s="136"/>
-      <c r="D57" s="136"/>
-      <c r="E57" s="136"/>
-      <c r="F57" s="136"/>
-      <c r="G57" s="136"/>
-      <c r="H57" s="136"/>
-      <c r="I57" s="136"/>
-      <c r="J57" s="136"/>
+      <c r="A57" s="59" t="s">
+        <v>42</v>
+      </c>
+      <c r="B57" s="59"/>
+      <c r="C57" s="59"/>
+      <c r="D57" s="59"/>
+      <c r="E57" s="59"/>
+      <c r="F57" s="59"/>
+      <c r="G57" s="59"/>
+      <c r="H57" s="59"/>
+      <c r="I57" s="59"/>
+      <c r="J57" s="59"/>
       <c r="K57" s="1"/>
       <c r="L57" s="1"/>
       <c r="M57" s="1"/>
@@ -4619,16 +4996,16 @@
       <c r="AA57" s="1"/>
     </row>
     <row r="58" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="1"/>
-      <c r="B58" s="1"/>
-      <c r="C58" s="1"/>
-      <c r="D58" s="1"/>
-      <c r="E58" s="1"/>
-      <c r="F58" s="4"/>
-      <c r="G58" s="5"/>
-      <c r="H58" s="4"/>
-      <c r="I58" s="1"/>
-      <c r="J58" s="1"/>
+      <c r="A58" s="59"/>
+      <c r="B58" s="59"/>
+      <c r="C58" s="59"/>
+      <c r="D58" s="59"/>
+      <c r="E58" s="59"/>
+      <c r="F58" s="59"/>
+      <c r="G58" s="59"/>
+      <c r="H58" s="59"/>
+      <c r="I58" s="59"/>
+      <c r="J58" s="59"/>
       <c r="K58" s="1"/>
       <c r="L58" s="1"/>
       <c r="M58" s="1"/>
@@ -8301,34 +8678,34 @@
       <c r="Z184" s="1"/>
       <c r="AA184" s="1"/>
     </row>
-    <row r="185" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A185" s="6"/>
-      <c r="B185" s="6"/>
-      <c r="C185" s="6"/>
-      <c r="D185" s="6"/>
-      <c r="E185" s="6"/>
-      <c r="F185" s="6"/>
-      <c r="G185" s="6"/>
-      <c r="H185" s="6"/>
-      <c r="I185" s="6"/>
-      <c r="J185" s="6"/>
-      <c r="K185" s="6"/>
-      <c r="L185" s="6"/>
-      <c r="M185" s="6"/>
-      <c r="N185" s="6"/>
-      <c r="O185" s="6"/>
-      <c r="P185" s="6"/>
-      <c r="Q185" s="6"/>
-      <c r="R185" s="6"/>
-      <c r="S185" s="6"/>
-      <c r="T185" s="6"/>
-      <c r="U185" s="6"/>
-      <c r="V185" s="6"/>
-      <c r="W185" s="6"/>
-      <c r="X185" s="6"/>
-      <c r="Y185" s="6"/>
-      <c r="Z185" s="6"/>
-      <c r="AA185" s="6"/>
+    <row r="185" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A185" s="1"/>
+      <c r="B185" s="1"/>
+      <c r="C185" s="1"/>
+      <c r="D185" s="1"/>
+      <c r="E185" s="1"/>
+      <c r="F185" s="4"/>
+      <c r="G185" s="5"/>
+      <c r="H185" s="4"/>
+      <c r="I185" s="1"/>
+      <c r="J185" s="1"/>
+      <c r="K185" s="1"/>
+      <c r="L185" s="1"/>
+      <c r="M185" s="1"/>
+      <c r="N185" s="1"/>
+      <c r="O185" s="1"/>
+      <c r="P185" s="1"/>
+      <c r="Q185" s="1"/>
+      <c r="R185" s="1"/>
+      <c r="S185" s="1"/>
+      <c r="T185" s="1"/>
+      <c r="U185" s="1"/>
+      <c r="V185" s="1"/>
+      <c r="W185" s="1"/>
+      <c r="X185" s="1"/>
+      <c r="Y185" s="1"/>
+      <c r="Z185" s="1"/>
+      <c r="AA185" s="1"/>
     </row>
     <row r="186" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="6"/>
@@ -30747,79 +31124,53 @@
       <c r="Z958" s="6"/>
       <c r="AA958" s="6"/>
     </row>
+    <row r="959" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A959" s="6"/>
+      <c r="B959" s="6"/>
+      <c r="C959" s="6"/>
+      <c r="D959" s="6"/>
+      <c r="E959" s="6"/>
+      <c r="F959" s="6"/>
+      <c r="G959" s="6"/>
+      <c r="H959" s="6"/>
+      <c r="I959" s="6"/>
+      <c r="J959" s="6"/>
+      <c r="K959" s="6"/>
+      <c r="L959" s="6"/>
+      <c r="M959" s="6"/>
+      <c r="N959" s="6"/>
+      <c r="O959" s="6"/>
+      <c r="P959" s="6"/>
+      <c r="Q959" s="6"/>
+      <c r="R959" s="6"/>
+      <c r="S959" s="6"/>
+      <c r="T959" s="6"/>
+      <c r="U959" s="6"/>
+      <c r="V959" s="6"/>
+      <c r="W959" s="6"/>
+      <c r="X959" s="6"/>
+      <c r="Y959" s="6"/>
+      <c r="Z959" s="6"/>
+      <c r="AA959" s="6"/>
+    </row>
   </sheetData>
   <mergeCells count="98">
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="A56:J57"/>
-    <mergeCell ref="B51:E51"/>
-    <mergeCell ref="F51:H51"/>
-    <mergeCell ref="E54:E55"/>
-    <mergeCell ref="F54:F55"/>
-    <mergeCell ref="G54:G55"/>
-    <mergeCell ref="H54:H55"/>
-    <mergeCell ref="A27:J27"/>
-    <mergeCell ref="D44:F44"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="A23:J23"/>
-    <mergeCell ref="A24:J24"/>
-    <mergeCell ref="A26:J26"/>
-    <mergeCell ref="A28:J28"/>
-    <mergeCell ref="A25:J25"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="A33:C34"/>
-    <mergeCell ref="D33:F34"/>
-    <mergeCell ref="A30:J30"/>
-    <mergeCell ref="A31:J31"/>
-    <mergeCell ref="A29:J29"/>
-    <mergeCell ref="B50:E50"/>
-    <mergeCell ref="F50:H50"/>
-    <mergeCell ref="B47:E47"/>
-    <mergeCell ref="F47:H47"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="F48:H48"/>
-    <mergeCell ref="B49:E49"/>
-    <mergeCell ref="F49:H49"/>
-    <mergeCell ref="A46:E46"/>
-    <mergeCell ref="F46:H46"/>
-    <mergeCell ref="A45:H45"/>
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="A41:A44"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="D42:F42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="A35:A40"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="F11:F13"/>
+    <mergeCell ref="F14:F19"/>
+    <mergeCell ref="I18:J19"/>
+    <mergeCell ref="I20:J21"/>
+    <mergeCell ref="I16:J17"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="C3:D4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="E7:F8"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="A3:B4"/>
     <mergeCell ref="A32:J32"/>
     <mergeCell ref="G33:J33"/>
     <mergeCell ref="G5:J5"/>
@@ -30836,19 +31187,79 @@
     <mergeCell ref="G11:H11"/>
     <mergeCell ref="G12:H12"/>
     <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="E7:F8"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="A3:B4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="C3:D4"/>
-    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="B37:C38"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="F47:H47"/>
+    <mergeCell ref="A46:H46"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="A42:A45"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="A35:A41"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="B51:E51"/>
+    <mergeCell ref="F51:H51"/>
+    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="F48:H48"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="F49:H49"/>
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="F50:H50"/>
+    <mergeCell ref="A27:J27"/>
+    <mergeCell ref="D45:F45"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="A23:J23"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A26:J26"/>
+    <mergeCell ref="A28:J28"/>
+    <mergeCell ref="A25:J25"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="A33:C34"/>
+    <mergeCell ref="D33:F34"/>
+    <mergeCell ref="A30:J30"/>
+    <mergeCell ref="A31:J31"/>
+    <mergeCell ref="A29:J29"/>
+    <mergeCell ref="A57:J58"/>
+    <mergeCell ref="B52:E52"/>
+    <mergeCell ref="F52:H52"/>
+    <mergeCell ref="E55:E56"/>
+    <mergeCell ref="F55:F56"/>
+    <mergeCell ref="G55:G56"/>
+    <mergeCell ref="H55:H56"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="I16:J17" location="'Situação Avaliação Formativa 2'!A1" display="Situação de aprendizagem formativa. A partir de um protótipo, codificar a interface de um aplicativo." xr:uid="{E10CF16B-E655-42FB-9628-FEA65EB8C725}"/>
+    <hyperlink ref="I18:J19" location="'Situação Avaliação Formativa 3'!A1" display="Situação de aprendizagem formativa. A partir de um protótipo, codificar a interface de um aplicativo de agenda que salva dados." xr:uid="{FBBA7BD9-A065-4C7D-A196-AA6892072FD3}"/>
+    <hyperlink ref="I20:J21" location="'Situação Avaliação Formativa 4'!A1" display="Situação de aprendizagem formativa. A partir de um protótipo, codificar a interface de um aplicativo." xr:uid="{1E94F7A5-0AB2-4FEB-985D-8D18F717F9A5}"/>
+  </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965" bottom="0.78740157480314965" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="83" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -30875,16 +31286,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="151" t="s">
+      <c r="A1" s="144" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="152"/>
-      <c r="C1" s="152"/>
-      <c r="D1" s="152"/>
-      <c r="E1" s="152"/>
-      <c r="F1" s="152"/>
-      <c r="G1" s="152"/>
-      <c r="H1" s="153"/>
+      <c r="B1" s="145"/>
+      <c r="C1" s="145"/>
+      <c r="D1" s="145"/>
+      <c r="E1" s="145"/>
+      <c r="F1" s="145"/>
+      <c r="G1" s="145"/>
+      <c r="H1" s="146"/>
       <c r="I1" s="7"/>
       <c r="J1" s="8"/>
       <c r="K1" s="8"/>
@@ -30905,16 +31316,16 @@
       <c r="Z1" s="8"/>
     </row>
     <row r="2" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="159" t="s">
+      <c r="A2" s="152" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="160"/>
-      <c r="C2" s="160"/>
-      <c r="D2" s="160"/>
-      <c r="E2" s="160"/>
-      <c r="F2" s="160"/>
-      <c r="G2" s="160"/>
-      <c r="H2" s="161"/>
+      <c r="B2" s="153"/>
+      <c r="C2" s="153"/>
+      <c r="D2" s="153"/>
+      <c r="E2" s="153"/>
+      <c r="F2" s="153"/>
+      <c r="G2" s="153"/>
+      <c r="H2" s="154"/>
       <c r="I2" s="7"/>
       <c r="J2" s="8"/>
       <c r="K2" s="8"/>
@@ -30935,16 +31346,16 @@
       <c r="Z2" s="8"/>
     </row>
     <row r="3" spans="1:27" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="162" t="s">
-        <v>126</v>
+      <c r="A3" s="155" t="s">
+        <v>123</v>
       </c>
-      <c r="B3" s="162"/>
-      <c r="C3" s="162"/>
-      <c r="D3" s="162"/>
-      <c r="E3" s="162"/>
-      <c r="F3" s="162"/>
-      <c r="G3" s="162"/>
-      <c r="H3" s="162"/>
+      <c r="B3" s="155"/>
+      <c r="C3" s="155"/>
+      <c r="D3" s="155"/>
+      <c r="E3" s="155"/>
+      <c r="F3" s="155"/>
+      <c r="G3" s="155"/>
+      <c r="H3" s="155"/>
       <c r="I3" s="7"/>
       <c r="J3" s="8"/>
       <c r="K3" s="8"/>
@@ -30965,16 +31376,16 @@
       <c r="Z3" s="8"/>
     </row>
     <row r="4" spans="1:27" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="163" t="s">
+      <c r="A4" s="156" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="163"/>
-      <c r="C4" s="163"/>
-      <c r="D4" s="163"/>
-      <c r="E4" s="163"/>
-      <c r="F4" s="163"/>
-      <c r="G4" s="163"/>
-      <c r="H4" s="163"/>
+      <c r="B4" s="156"/>
+      <c r="C4" s="156"/>
+      <c r="D4" s="156"/>
+      <c r="E4" s="156"/>
+      <c r="F4" s="156"/>
+      <c r="G4" s="156"/>
+      <c r="H4" s="156"/>
       <c r="I4" s="7"/>
       <c r="J4" s="8"/>
       <c r="K4" s="8"/>
@@ -30995,16 +31406,16 @@
       <c r="Z4" s="8"/>
     </row>
     <row r="5" spans="1:27" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="162" t="s">
-        <v>127</v>
+      <c r="A5" s="155" t="s">
+        <v>124</v>
       </c>
-      <c r="B5" s="162"/>
-      <c r="C5" s="162"/>
-      <c r="D5" s="162"/>
-      <c r="E5" s="162"/>
-      <c r="F5" s="162"/>
-      <c r="G5" s="162"/>
-      <c r="H5" s="162"/>
+      <c r="B5" s="155"/>
+      <c r="C5" s="155"/>
+      <c r="D5" s="155"/>
+      <c r="E5" s="155"/>
+      <c r="F5" s="155"/>
+      <c r="G5" s="155"/>
+      <c r="H5" s="155"/>
       <c r="I5" s="7"/>
       <c r="J5" s="8"/>
       <c r="K5" s="8"/>
@@ -31025,14 +31436,14 @@
       <c r="Z5" s="8"/>
     </row>
     <row r="6" spans="1:27" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="164"/>
-      <c r="B6" s="164"/>
-      <c r="C6" s="164"/>
-      <c r="D6" s="164"/>
-      <c r="E6" s="164"/>
-      <c r="F6" s="164"/>
-      <c r="G6" s="164"/>
-      <c r="H6" s="164"/>
+      <c r="A6" s="157"/>
+      <c r="B6" s="157"/>
+      <c r="C6" s="157"/>
+      <c r="D6" s="157"/>
+      <c r="E6" s="157"/>
+      <c r="F6" s="157"/>
+      <c r="G6" s="157"/>
+      <c r="H6" s="157"/>
       <c r="J6" s="8"/>
       <c r="K6" s="8"/>
       <c r="L6" s="8"/>
@@ -31052,14 +31463,14 @@
       <c r="Z6" s="8"/>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A7" s="162"/>
-      <c r="B7" s="162"/>
-      <c r="C7" s="162"/>
-      <c r="D7" s="162"/>
-      <c r="E7" s="162"/>
-      <c r="F7" s="162"/>
-      <c r="G7" s="162"/>
-      <c r="H7" s="162"/>
+      <c r="A7" s="155"/>
+      <c r="B7" s="155"/>
+      <c r="C7" s="155"/>
+      <c r="D7" s="155"/>
+      <c r="E7" s="155"/>
+      <c r="F7" s="155"/>
+      <c r="G7" s="155"/>
+      <c r="H7" s="155"/>
       <c r="I7" s="7"/>
       <c r="J7" s="8"/>
       <c r="K7" s="8"/>
@@ -31080,16 +31491,16 @@
       <c r="Z7" s="8"/>
     </row>
     <row r="8" spans="1:27" ht="18" x14ac:dyDescent="0.25">
-      <c r="A8" s="163" t="s">
+      <c r="A8" s="156" t="s">
         <v>36</v>
       </c>
-      <c r="B8" s="165"/>
-      <c r="C8" s="165"/>
-      <c r="D8" s="165"/>
-      <c r="E8" s="165"/>
-      <c r="F8" s="165"/>
-      <c r="G8" s="165"/>
-      <c r="H8" s="165"/>
+      <c r="B8" s="158"/>
+      <c r="C8" s="158"/>
+      <c r="D8" s="158"/>
+      <c r="E8" s="158"/>
+      <c r="F8" s="158"/>
+      <c r="G8" s="158"/>
+      <c r="H8" s="158"/>
       <c r="I8" s="9"/>
       <c r="J8" s="10"/>
       <c r="K8" s="10"/>
@@ -31110,16 +31521,16 @@
       <c r="Z8" s="10"/>
     </row>
     <row r="9" spans="1:27" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="162" t="s">
-        <v>109</v>
+      <c r="A9" s="155" t="s">
+        <v>106</v>
       </c>
-      <c r="B9" s="162"/>
-      <c r="C9" s="162"/>
-      <c r="D9" s="162"/>
-      <c r="E9" s="162"/>
-      <c r="F9" s="162"/>
-      <c r="G9" s="162"/>
-      <c r="H9" s="162"/>
+      <c r="B9" s="155"/>
+      <c r="C9" s="155"/>
+      <c r="D9" s="155"/>
+      <c r="E9" s="155"/>
+      <c r="F9" s="155"/>
+      <c r="G9" s="155"/>
+      <c r="H9" s="155"/>
       <c r="J9" s="8"/>
       <c r="K9" s="8"/>
       <c r="L9" s="8"/>
@@ -31139,16 +31550,16 @@
       <c r="Z9" s="8"/>
     </row>
     <row r="10" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="166" t="s">
+      <c r="A10" s="241" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="167"/>
-      <c r="C10" s="167"/>
-      <c r="D10" s="167"/>
-      <c r="E10" s="167"/>
-      <c r="F10" s="167"/>
-      <c r="G10" s="167"/>
-      <c r="H10" s="168"/>
+      <c r="B10" s="241"/>
+      <c r="C10" s="241"/>
+      <c r="D10" s="241"/>
+      <c r="E10" s="241"/>
+      <c r="F10" s="241"/>
+      <c r="G10" s="241"/>
+      <c r="H10" s="241"/>
       <c r="I10" s="7"/>
       <c r="J10" s="8"/>
       <c r="K10" s="8"/>
@@ -31169,22 +31580,22 @@
       <c r="Z10" s="8"/>
     </row>
     <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="154" t="s">
+      <c r="A11" s="147" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="155"/>
-      <c r="C11" s="156"/>
-      <c r="D11" s="158" t="s">
+      <c r="B11" s="151"/>
+      <c r="C11" s="239"/>
+      <c r="D11" s="147" t="s">
         <v>11</v>
       </c>
-      <c r="E11" s="155"/>
-      <c r="F11" s="155"/>
-      <c r="G11" s="155"/>
-      <c r="H11" s="169" t="s">
+      <c r="E11" s="151"/>
+      <c r="F11" s="151"/>
+      <c r="G11" s="235"/>
+      <c r="H11" s="232" t="s">
         <v>12</v>
       </c>
-      <c r="I11" s="169"/>
-      <c r="J11" s="169"/>
+      <c r="I11" s="233"/>
+      <c r="J11" s="234"/>
       <c r="K11" s="8"/>
       <c r="L11" s="8"/>
       <c r="M11" s="8"/>
@@ -31203,13 +31614,13 @@
       <c r="Z11" s="8"/>
     </row>
     <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="157"/>
-      <c r="B12" s="111"/>
-      <c r="C12" s="112"/>
-      <c r="D12" s="111"/>
-      <c r="E12" s="111"/>
-      <c r="F12" s="111"/>
-      <c r="G12" s="111"/>
+      <c r="A12" s="236"/>
+      <c r="B12" s="237"/>
+      <c r="C12" s="240"/>
+      <c r="D12" s="236"/>
+      <c r="E12" s="237"/>
+      <c r="F12" s="237"/>
+      <c r="G12" s="238"/>
       <c r="H12" s="49" t="s">
         <v>13</v>
       </c>
@@ -31237,18 +31648,18 @@
       <c r="Z12" s="8"/>
     </row>
     <row r="13" spans="1:27" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="113" t="s">
+      <c r="A13" s="197" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="84" t="s">
-        <v>110</v>
+      <c r="B13" s="214" t="s">
+        <v>107</v>
       </c>
-      <c r="C13" s="85"/>
-      <c r="D13" s="86" t="s">
-        <v>114</v>
+      <c r="C13" s="215"/>
+      <c r="D13" s="229" t="s">
+        <v>111</v>
       </c>
-      <c r="E13" s="76"/>
-      <c r="F13" s="75"/>
+      <c r="E13" s="230"/>
+      <c r="F13" s="231"/>
       <c r="G13" s="50" t="s">
         <v>25</v>
       </c>
@@ -31274,16 +31685,16 @@
       <c r="AA13" s="1"/>
     </row>
     <row r="14" spans="1:27" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="114"/>
-      <c r="B14" s="84" t="s">
-        <v>111</v>
+      <c r="A14" s="198"/>
+      <c r="B14" s="110" t="s">
+        <v>108</v>
       </c>
-      <c r="C14" s="85"/>
-      <c r="D14" s="86" t="s">
-        <v>115</v>
+      <c r="C14" s="228"/>
+      <c r="D14" s="225" t="s">
+        <v>112</v>
       </c>
-      <c r="E14" s="76"/>
-      <c r="F14" s="75"/>
+      <c r="E14" s="226"/>
+      <c r="F14" s="227"/>
       <c r="G14" s="50" t="s">
         <v>25</v>
       </c>
@@ -31309,16 +31720,16 @@
       <c r="AA14" s="1"/>
     </row>
     <row r="15" spans="1:27" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="114"/>
-      <c r="B15" s="87" t="s">
-        <v>112</v>
+      <c r="A15" s="198"/>
+      <c r="B15" s="223" t="s">
+        <v>109</v>
       </c>
-      <c r="C15" s="88"/>
-      <c r="D15" s="89" t="s">
-        <v>116</v>
+      <c r="C15" s="224"/>
+      <c r="D15" s="96" t="s">
+        <v>113</v>
       </c>
-      <c r="E15" s="76"/>
-      <c r="F15" s="75"/>
+      <c r="E15" s="212"/>
+      <c r="F15" s="213"/>
       <c r="G15" s="50" t="s">
         <v>25</v>
       </c>
@@ -31344,16 +31755,16 @@
       <c r="AA15" s="1"/>
     </row>
     <row r="16" spans="1:27" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="114"/>
-      <c r="B16" s="90" t="s">
-        <v>113</v>
+      <c r="A16" s="198"/>
+      <c r="B16" s="221" t="s">
+        <v>110</v>
       </c>
-      <c r="C16" s="91"/>
-      <c r="D16" s="92" t="s">
-        <v>118</v>
+      <c r="C16" s="222"/>
+      <c r="D16" s="218" t="s">
+        <v>115</v>
       </c>
-      <c r="E16" s="93"/>
-      <c r="F16" s="94"/>
+      <c r="E16" s="219"/>
+      <c r="F16" s="220"/>
       <c r="G16" s="50" t="s">
         <v>25</v>
       </c>
@@ -31379,16 +31790,16 @@
       <c r="AA16" s="1"/>
     </row>
     <row r="17" spans="1:27" ht="50.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="114"/>
-      <c r="B17" s="90" t="s">
+      <c r="A17" s="198"/>
+      <c r="B17" s="214" t="s">
         <v>67</v>
       </c>
-      <c r="C17" s="91"/>
-      <c r="D17" s="100" t="s">
-        <v>119</v>
+      <c r="C17" s="215"/>
+      <c r="D17" s="96" t="s">
+        <v>116</v>
       </c>
-      <c r="E17" s="101"/>
-      <c r="F17" s="102"/>
+      <c r="E17" s="212"/>
+      <c r="F17" s="213"/>
       <c r="G17" s="50" t="s">
         <v>25</v>
       </c>
@@ -31414,16 +31825,16 @@
       <c r="AA17" s="1"/>
     </row>
     <row r="18" spans="1:27" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="115"/>
-      <c r="B18" s="103" t="s">
-        <v>90</v>
+      <c r="A18" s="199"/>
+      <c r="B18" s="110" t="s">
+        <v>88</v>
       </c>
-      <c r="C18" s="104"/>
-      <c r="D18" s="89" t="s">
-        <v>117</v>
+      <c r="C18" s="217"/>
+      <c r="D18" s="216" t="s">
+        <v>114</v>
       </c>
-      <c r="E18" s="76"/>
-      <c r="F18" s="75"/>
+      <c r="E18" s="212"/>
+      <c r="F18" s="213"/>
       <c r="G18" s="50" t="s">
         <v>25</v>
       </c>
@@ -31449,18 +31860,18 @@
       <c r="AA18" s="1"/>
     </row>
     <row r="19" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="105" t="s">
+      <c r="A19" s="210" t="s">
         <v>33</v>
       </c>
-      <c r="B19" s="108" t="s">
+      <c r="B19" s="208" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="109"/>
-      <c r="D19" s="110" t="s">
-        <v>123</v>
+      <c r="C19" s="209"/>
+      <c r="D19" s="205" t="s">
+        <v>120</v>
       </c>
-      <c r="E19" s="111"/>
-      <c r="F19" s="112"/>
+      <c r="E19" s="206"/>
+      <c r="F19" s="207"/>
       <c r="G19" s="50" t="s">
         <v>25</v>
       </c>
@@ -31486,16 +31897,16 @@
       <c r="AA19" s="1"/>
     </row>
     <row r="20" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="106"/>
-      <c r="B20" s="108" t="s">
-        <v>120</v>
+      <c r="A20" s="104"/>
+      <c r="B20" s="203" t="s">
+        <v>117</v>
       </c>
-      <c r="C20" s="109"/>
-      <c r="D20" s="110" t="s">
-        <v>121</v>
+      <c r="C20" s="204"/>
+      <c r="D20" s="200" t="s">
+        <v>118</v>
       </c>
-      <c r="E20" s="111"/>
-      <c r="F20" s="112"/>
+      <c r="E20" s="201"/>
+      <c r="F20" s="202"/>
       <c r="G20" s="50" t="s">
         <v>25</v>
       </c>
@@ -31521,16 +31932,16 @@
       <c r="AA20" s="1"/>
     </row>
     <row r="21" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="106"/>
-      <c r="B21" s="108" t="s">
+      <c r="A21" s="104"/>
+      <c r="B21" s="203" t="s">
         <v>48</v>
       </c>
-      <c r="C21" s="109"/>
-      <c r="D21" s="110" t="s">
-        <v>122</v>
+      <c r="C21" s="204"/>
+      <c r="D21" s="200" t="s">
+        <v>119</v>
       </c>
-      <c r="E21" s="111"/>
-      <c r="F21" s="112"/>
+      <c r="E21" s="201"/>
+      <c r="F21" s="202"/>
       <c r="G21" s="50" t="s">
         <v>25</v>
       </c>
@@ -31556,16 +31967,16 @@
       <c r="AA21" s="1"/>
     </row>
     <row r="22" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="107"/>
-      <c r="B22" s="108" t="s">
+      <c r="A22" s="211"/>
+      <c r="B22" s="203" t="s">
         <v>15</v>
       </c>
-      <c r="C22" s="109"/>
-      <c r="D22" s="110" t="s">
-        <v>124</v>
+      <c r="C22" s="204"/>
+      <c r="D22" s="200" t="s">
+        <v>121</v>
       </c>
-      <c r="E22" s="111"/>
-      <c r="F22" s="112"/>
+      <c r="E22" s="201"/>
+      <c r="F22" s="202"/>
       <c r="G22" s="50" t="s">
         <v>25</v>
       </c>
@@ -31619,18 +32030,18 @@
       <c r="Z23" s="8"/>
     </row>
     <row r="24" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="95" t="s">
+      <c r="A24" s="91" t="s">
         <v>16</v>
       </c>
-      <c r="B24" s="96"/>
-      <c r="C24" s="96"/>
-      <c r="D24" s="96"/>
-      <c r="E24" s="97"/>
-      <c r="F24" s="98" t="s">
+      <c r="B24" s="94"/>
+      <c r="C24" s="94"/>
+      <c r="D24" s="94"/>
+      <c r="E24" s="196"/>
+      <c r="F24" s="91" t="s">
         <v>17</v>
       </c>
-      <c r="G24" s="96"/>
-      <c r="H24" s="97"/>
+      <c r="G24" s="94"/>
+      <c r="H24" s="196"/>
       <c r="I24" s="7"/>
       <c r="J24" s="8"/>
       <c r="K24" s="8"/>
@@ -31654,17 +32065,17 @@
       <c r="A25" s="13">
         <v>5</v>
       </c>
-      <c r="B25" s="118" t="s">
+      <c r="B25" s="184" t="s">
         <v>18</v>
       </c>
-      <c r="C25" s="111"/>
-      <c r="D25" s="111"/>
-      <c r="E25" s="112"/>
-      <c r="F25" s="117">
+      <c r="C25" s="185"/>
+      <c r="D25" s="185"/>
+      <c r="E25" s="186"/>
+      <c r="F25" s="193">
         <v>100</v>
       </c>
-      <c r="G25" s="111"/>
-      <c r="H25" s="112"/>
+      <c r="G25" s="194"/>
+      <c r="H25" s="195"/>
       <c r="I25" s="7"/>
       <c r="J25" s="8"/>
       <c r="K25" s="8"/>
@@ -31688,17 +32099,17 @@
       <c r="A26" s="13">
         <v>4</v>
       </c>
-      <c r="B26" s="119" t="s">
+      <c r="B26" s="187" t="s">
         <v>50</v>
       </c>
-      <c r="C26" s="111"/>
-      <c r="D26" s="111"/>
-      <c r="E26" s="112"/>
-      <c r="F26" s="117">
+      <c r="C26" s="188"/>
+      <c r="D26" s="188"/>
+      <c r="E26" s="189"/>
+      <c r="F26" s="193">
         <v>80</v>
       </c>
-      <c r="G26" s="111"/>
-      <c r="H26" s="112"/>
+      <c r="G26" s="194"/>
+      <c r="H26" s="195"/>
       <c r="I26" s="7"/>
       <c r="J26" s="8"/>
       <c r="K26" s="8"/>
@@ -31722,17 +32133,17 @@
       <c r="A27" s="13">
         <v>3</v>
       </c>
-      <c r="B27" s="119" t="s">
+      <c r="B27" s="187" t="s">
         <v>49</v>
       </c>
-      <c r="C27" s="111"/>
-      <c r="D27" s="111"/>
-      <c r="E27" s="112"/>
-      <c r="F27" s="117">
+      <c r="C27" s="188"/>
+      <c r="D27" s="188"/>
+      <c r="E27" s="189"/>
+      <c r="F27" s="193">
         <v>65</v>
       </c>
-      <c r="G27" s="111"/>
-      <c r="H27" s="112"/>
+      <c r="G27" s="194"/>
+      <c r="H27" s="195"/>
       <c r="I27" s="7"/>
       <c r="J27" s="8"/>
       <c r="K27" s="8"/>
@@ -31756,17 +32167,17 @@
       <c r="A28" s="13">
         <v>2</v>
       </c>
-      <c r="B28" s="116" t="s">
+      <c r="B28" s="190" t="s">
         <v>19</v>
       </c>
-      <c r="C28" s="111"/>
-      <c r="D28" s="111"/>
-      <c r="E28" s="112"/>
-      <c r="F28" s="117">
+      <c r="C28" s="191"/>
+      <c r="D28" s="191"/>
+      <c r="E28" s="192"/>
+      <c r="F28" s="193">
         <v>50</v>
       </c>
-      <c r="G28" s="111"/>
-      <c r="H28" s="112"/>
+      <c r="G28" s="194"/>
+      <c r="H28" s="195"/>
       <c r="I28" s="7"/>
       <c r="J28" s="8"/>
       <c r="K28" s="8"/>
@@ -31790,17 +32201,17 @@
       <c r="A29" s="13">
         <v>1</v>
       </c>
-      <c r="B29" s="118" t="s">
+      <c r="B29" s="184" t="s">
         <v>20</v>
       </c>
-      <c r="C29" s="111"/>
-      <c r="D29" s="111"/>
-      <c r="E29" s="112"/>
-      <c r="F29" s="117">
+      <c r="C29" s="185"/>
+      <c r="D29" s="185"/>
+      <c r="E29" s="186"/>
+      <c r="F29" s="193">
         <v>30</v>
       </c>
-      <c r="G29" s="111"/>
-      <c r="H29" s="112"/>
+      <c r="G29" s="194"/>
+      <c r="H29" s="195"/>
       <c r="I29" s="7"/>
       <c r="J29" s="8"/>
       <c r="K29" s="8"/>
@@ -31889,16 +32300,16 @@
       <c r="D32" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="E32" s="146">
+      <c r="E32" s="182">
         <v>1</v>
       </c>
-      <c r="F32" s="146">
+      <c r="F32" s="182">
         <v>0</v>
       </c>
-      <c r="G32" s="147" t="s">
+      <c r="G32" s="164" t="s">
         <v>25</v>
       </c>
-      <c r="H32" s="149" t="s">
+      <c r="H32" s="166" t="s">
         <v>26</v>
       </c>
       <c r="I32" s="7"/>
@@ -31927,10 +32338,10 @@
       <c r="D33" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="E33" s="112"/>
-      <c r="F33" s="112"/>
-      <c r="G33" s="148"/>
-      <c r="H33" s="150"/>
+      <c r="E33" s="183"/>
+      <c r="F33" s="183"/>
+      <c r="G33" s="165"/>
+      <c r="H33" s="167"/>
       <c r="I33" s="7"/>
       <c r="J33" s="8"/>
       <c r="K33" s="8"/>
@@ -37780,6 +38191,41 @@
     <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="51">
+    <mergeCell ref="H11:J11"/>
+    <mergeCell ref="D11:G12"/>
+    <mergeCell ref="A11:C12"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="G32:G33"/>
+    <mergeCell ref="H32:H33"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A6:H6"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A9:H9"/>
     <mergeCell ref="B26:E26"/>
     <mergeCell ref="F26:H26"/>
     <mergeCell ref="B27:E27"/>
@@ -37796,41 +38242,6 @@
     <mergeCell ref="B22:C22"/>
     <mergeCell ref="D22:F22"/>
     <mergeCell ref="A13:A18"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A11:C12"/>
-    <mergeCell ref="D11:G12"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A6:H6"/>
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="A10:H10"/>
-    <mergeCell ref="H11:J11"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="F32:F33"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="B28:E28"/>
-    <mergeCell ref="F28:H28"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="F29:H29"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="G32:G33"/>
-    <mergeCell ref="H32:H33"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:F15"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
@@ -37857,16 +38268,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="151" t="s">
+      <c r="A1" s="144" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="152"/>
-      <c r="C1" s="152"/>
-      <c r="D1" s="152"/>
-      <c r="E1" s="152"/>
-      <c r="F1" s="152"/>
-      <c r="G1" s="152"/>
-      <c r="H1" s="153"/>
+      <c r="B1" s="145"/>
+      <c r="C1" s="145"/>
+      <c r="D1" s="145"/>
+      <c r="E1" s="145"/>
+      <c r="F1" s="145"/>
+      <c r="G1" s="145"/>
+      <c r="H1" s="146"/>
       <c r="I1" s="7"/>
       <c r="J1" s="8"/>
       <c r="K1" s="8"/>
@@ -37887,16 +38298,16 @@
       <c r="Z1" s="8"/>
     </row>
     <row r="2" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="159" t="s">
+      <c r="A2" s="152" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="160"/>
-      <c r="C2" s="160"/>
-      <c r="D2" s="160"/>
-      <c r="E2" s="160"/>
-      <c r="F2" s="160"/>
-      <c r="G2" s="160"/>
-      <c r="H2" s="161"/>
+      <c r="B2" s="153"/>
+      <c r="C2" s="153"/>
+      <c r="D2" s="153"/>
+      <c r="E2" s="153"/>
+      <c r="F2" s="153"/>
+      <c r="G2" s="153"/>
+      <c r="H2" s="154"/>
       <c r="I2" s="7"/>
       <c r="J2" s="8"/>
       <c r="K2" s="8"/>
@@ -37917,16 +38328,16 @@
       <c r="Z2" s="8"/>
     </row>
     <row r="3" spans="1:27" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="162" t="s">
-        <v>128</v>
+      <c r="A3" s="155" t="s">
+        <v>125</v>
       </c>
-      <c r="B3" s="162"/>
-      <c r="C3" s="162"/>
-      <c r="D3" s="162"/>
-      <c r="E3" s="162"/>
-      <c r="F3" s="162"/>
-      <c r="G3" s="162"/>
-      <c r="H3" s="162"/>
+      <c r="B3" s="155"/>
+      <c r="C3" s="155"/>
+      <c r="D3" s="155"/>
+      <c r="E3" s="155"/>
+      <c r="F3" s="155"/>
+      <c r="G3" s="155"/>
+      <c r="H3" s="155"/>
       <c r="I3" s="7"/>
       <c r="J3" s="8"/>
       <c r="K3" s="8"/>
@@ -37947,16 +38358,16 @@
       <c r="Z3" s="8"/>
     </row>
     <row r="4" spans="1:27" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="163" t="s">
+      <c r="A4" s="156" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="163"/>
-      <c r="C4" s="163"/>
-      <c r="D4" s="163"/>
-      <c r="E4" s="163"/>
-      <c r="F4" s="163"/>
-      <c r="G4" s="163"/>
-      <c r="H4" s="163"/>
+      <c r="B4" s="156"/>
+      <c r="C4" s="156"/>
+      <c r="D4" s="156"/>
+      <c r="E4" s="156"/>
+      <c r="F4" s="156"/>
+      <c r="G4" s="156"/>
+      <c r="H4" s="156"/>
       <c r="I4" s="7"/>
       <c r="J4" s="8"/>
       <c r="K4" s="8"/>
@@ -37977,16 +38388,16 @@
       <c r="Z4" s="8"/>
     </row>
     <row r="5" spans="1:27" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="162" t="s">
-        <v>129</v>
+      <c r="A5" s="155" t="s">
+        <v>126</v>
       </c>
-      <c r="B5" s="162"/>
-      <c r="C5" s="162"/>
-      <c r="D5" s="162"/>
-      <c r="E5" s="162"/>
-      <c r="F5" s="162"/>
-      <c r="G5" s="162"/>
-      <c r="H5" s="162"/>
+      <c r="B5" s="155"/>
+      <c r="C5" s="155"/>
+      <c r="D5" s="155"/>
+      <c r="E5" s="155"/>
+      <c r="F5" s="155"/>
+      <c r="G5" s="155"/>
+      <c r="H5" s="155"/>
       <c r="I5" s="7"/>
       <c r="J5" s="8"/>
       <c r="K5" s="8"/>
@@ -38007,14 +38418,14 @@
       <c r="Z5" s="8"/>
     </row>
     <row r="6" spans="1:27" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="164"/>
-      <c r="B6" s="164"/>
-      <c r="C6" s="164"/>
-      <c r="D6" s="164"/>
-      <c r="E6" s="164"/>
-      <c r="F6" s="164"/>
-      <c r="G6" s="164"/>
-      <c r="H6" s="164"/>
+      <c r="A6" s="157"/>
+      <c r="B6" s="157"/>
+      <c r="C6" s="157"/>
+      <c r="D6" s="157"/>
+      <c r="E6" s="157"/>
+      <c r="F6" s="157"/>
+      <c r="G6" s="157"/>
+      <c r="H6" s="157"/>
       <c r="J6" s="8"/>
       <c r="L6" s="8"/>
       <c r="M6" s="8"/>
@@ -38033,14 +38444,14 @@
       <c r="Z6" s="8"/>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A7" s="162"/>
-      <c r="B7" s="162"/>
-      <c r="C7" s="162"/>
-      <c r="D7" s="162"/>
-      <c r="E7" s="162"/>
-      <c r="F7" s="162"/>
-      <c r="G7" s="162"/>
-      <c r="H7" s="162"/>
+      <c r="A7" s="155"/>
+      <c r="B7" s="155"/>
+      <c r="C7" s="155"/>
+      <c r="D7" s="155"/>
+      <c r="E7" s="155"/>
+      <c r="F7" s="155"/>
+      <c r="G7" s="155"/>
+      <c r="H7" s="155"/>
       <c r="I7" s="7"/>
       <c r="J7" s="8"/>
       <c r="K7" s="8"/>
@@ -38061,16 +38472,16 @@
       <c r="Z7" s="8"/>
     </row>
     <row r="8" spans="1:27" ht="18" x14ac:dyDescent="0.25">
-      <c r="A8" s="163" t="s">
+      <c r="A8" s="156" t="s">
         <v>36</v>
       </c>
-      <c r="B8" s="165"/>
-      <c r="C8" s="165"/>
-      <c r="D8" s="165"/>
-      <c r="E8" s="165"/>
-      <c r="F8" s="165"/>
-      <c r="G8" s="165"/>
-      <c r="H8" s="165"/>
+      <c r="B8" s="158"/>
+      <c r="C8" s="158"/>
+      <c r="D8" s="158"/>
+      <c r="E8" s="158"/>
+      <c r="F8" s="158"/>
+      <c r="G8" s="158"/>
+      <c r="H8" s="158"/>
       <c r="I8" s="9"/>
       <c r="J8" s="10"/>
       <c r="K8" s="10"/>
@@ -38091,16 +38502,16 @@
       <c r="Z8" s="10"/>
     </row>
     <row r="9" spans="1:27" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="162" t="s">
-        <v>109</v>
+      <c r="A9" s="155" t="s">
+        <v>106</v>
       </c>
-      <c r="B9" s="162"/>
-      <c r="C9" s="162"/>
-      <c r="D9" s="162"/>
-      <c r="E9" s="162"/>
-      <c r="F9" s="162"/>
-      <c r="G9" s="162"/>
-      <c r="H9" s="162"/>
+      <c r="B9" s="155"/>
+      <c r="C9" s="155"/>
+      <c r="D9" s="155"/>
+      <c r="E9" s="155"/>
+      <c r="F9" s="155"/>
+      <c r="G9" s="155"/>
+      <c r="H9" s="155"/>
       <c r="J9" s="8"/>
       <c r="K9" s="8"/>
       <c r="L9" s="8"/>
@@ -38120,16 +38531,16 @@
       <c r="Z9" s="8"/>
     </row>
     <row r="10" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="166" t="s">
+      <c r="A10" s="159" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="167"/>
-      <c r="C10" s="167"/>
-      <c r="D10" s="167"/>
-      <c r="E10" s="167"/>
-      <c r="F10" s="167"/>
-      <c r="G10" s="167"/>
-      <c r="H10" s="168"/>
+      <c r="B10" s="160"/>
+      <c r="C10" s="160"/>
+      <c r="D10" s="160"/>
+      <c r="E10" s="160"/>
+      <c r="F10" s="160"/>
+      <c r="G10" s="160"/>
+      <c r="H10" s="161"/>
       <c r="I10" s="7"/>
       <c r="J10" s="8"/>
       <c r="K10" s="8"/>
@@ -38150,22 +38561,22 @@
       <c r="Z10" s="8"/>
     </row>
     <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="154" t="s">
+      <c r="A11" s="147" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="155"/>
-      <c r="C11" s="156"/>
-      <c r="D11" s="158" t="s">
+      <c r="B11" s="148"/>
+      <c r="C11" s="149"/>
+      <c r="D11" s="151" t="s">
         <v>11</v>
       </c>
-      <c r="E11" s="155"/>
-      <c r="F11" s="155"/>
-      <c r="G11" s="155"/>
-      <c r="H11" s="169" t="s">
+      <c r="E11" s="148"/>
+      <c r="F11" s="148"/>
+      <c r="G11" s="148"/>
+      <c r="H11" s="162" t="s">
         <v>12</v>
       </c>
-      <c r="I11" s="169"/>
-      <c r="J11" s="169"/>
+      <c r="I11" s="162"/>
+      <c r="J11" s="162"/>
       <c r="K11" s="8"/>
       <c r="L11" s="8"/>
       <c r="M11" s="8"/>
@@ -38184,13 +38595,13 @@
       <c r="Z11" s="8"/>
     </row>
     <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="157"/>
-      <c r="B12" s="111"/>
-      <c r="C12" s="112"/>
-      <c r="D12" s="111"/>
-      <c r="E12" s="111"/>
-      <c r="F12" s="111"/>
-      <c r="G12" s="111"/>
+      <c r="A12" s="150"/>
+      <c r="B12" s="61"/>
+      <c r="C12" s="62"/>
+      <c r="D12" s="61"/>
+      <c r="E12" s="61"/>
+      <c r="F12" s="61"/>
+      <c r="G12" s="61"/>
       <c r="H12" s="49" t="s">
         <v>13</v>
       </c>
@@ -38218,18 +38629,18 @@
       <c r="Z12" s="8"/>
     </row>
     <row r="13" spans="1:27" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="113" t="s">
+      <c r="A13" s="107" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="84" t="s">
-        <v>110</v>
+      <c r="B13" s="110" t="s">
+        <v>107</v>
       </c>
-      <c r="C13" s="85"/>
-      <c r="D13" s="86" t="s">
-        <v>114</v>
+      <c r="C13" s="111"/>
+      <c r="D13" s="112" t="s">
+        <v>111</v>
       </c>
-      <c r="E13" s="76"/>
-      <c r="F13" s="75"/>
+      <c r="E13" s="102"/>
+      <c r="F13" s="103"/>
       <c r="G13" s="50" t="s">
         <v>25</v>
       </c>
@@ -38255,16 +38666,16 @@
       <c r="AA13" s="1"/>
     </row>
     <row r="14" spans="1:27" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="114"/>
-      <c r="B14" s="84" t="s">
-        <v>111</v>
+      <c r="A14" s="108"/>
+      <c r="B14" s="110" t="s">
+        <v>108</v>
       </c>
-      <c r="C14" s="85"/>
-      <c r="D14" s="86" t="s">
-        <v>115</v>
+      <c r="C14" s="111"/>
+      <c r="D14" s="112" t="s">
+        <v>112</v>
       </c>
-      <c r="E14" s="76"/>
-      <c r="F14" s="75"/>
+      <c r="E14" s="102"/>
+      <c r="F14" s="103"/>
       <c r="G14" s="50" t="s">
         <v>25</v>
       </c>
@@ -38290,16 +38701,16 @@
       <c r="AA14" s="1"/>
     </row>
     <row r="15" spans="1:27" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="114"/>
-      <c r="B15" s="87" t="s">
-        <v>112</v>
+      <c r="A15" s="108"/>
+      <c r="B15" s="113" t="s">
+        <v>109</v>
       </c>
-      <c r="C15" s="88"/>
-      <c r="D15" s="89" t="s">
-        <v>116</v>
+      <c r="C15" s="114"/>
+      <c r="D15" s="101" t="s">
+        <v>113</v>
       </c>
-      <c r="E15" s="76"/>
-      <c r="F15" s="75"/>
+      <c r="E15" s="102"/>
+      <c r="F15" s="103"/>
       <c r="G15" s="50" t="s">
         <v>25</v>
       </c>
@@ -38325,16 +38736,16 @@
       <c r="AA15" s="1"/>
     </row>
     <row r="16" spans="1:27" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="114"/>
-      <c r="B16" s="90" t="s">
-        <v>113</v>
+      <c r="A16" s="108"/>
+      <c r="B16" s="78" t="s">
+        <v>110</v>
       </c>
-      <c r="C16" s="91"/>
-      <c r="D16" s="92" t="s">
-        <v>118</v>
+      <c r="C16" s="79"/>
+      <c r="D16" s="115" t="s">
+        <v>115</v>
       </c>
-      <c r="E16" s="93"/>
-      <c r="F16" s="94"/>
+      <c r="E16" s="116"/>
+      <c r="F16" s="117"/>
       <c r="G16" s="50" t="s">
         <v>25</v>
       </c>
@@ -38360,16 +38771,16 @@
       <c r="AA16" s="1"/>
     </row>
     <row r="17" spans="1:27" ht="50.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="114"/>
-      <c r="B17" s="90" t="s">
+      <c r="A17" s="108"/>
+      <c r="B17" s="78" t="s">
         <v>67</v>
       </c>
-      <c r="C17" s="91"/>
-      <c r="D17" s="100" t="s">
-        <v>119</v>
+      <c r="C17" s="79"/>
+      <c r="D17" s="96" t="s">
+        <v>116</v>
       </c>
-      <c r="E17" s="101"/>
-      <c r="F17" s="102"/>
+      <c r="E17" s="97"/>
+      <c r="F17" s="98"/>
       <c r="G17" s="50" t="s">
         <v>25</v>
       </c>
@@ -38395,16 +38806,16 @@
       <c r="AA17" s="1"/>
     </row>
     <row r="18" spans="1:27" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="115"/>
-      <c r="B18" s="103" t="s">
-        <v>90</v>
+      <c r="A18" s="109"/>
+      <c r="B18" s="99" t="s">
+        <v>88</v>
       </c>
-      <c r="C18" s="104"/>
-      <c r="D18" s="89" t="s">
-        <v>117</v>
+      <c r="C18" s="100"/>
+      <c r="D18" s="101" t="s">
+        <v>114</v>
       </c>
-      <c r="E18" s="76"/>
-      <c r="F18" s="75"/>
+      <c r="E18" s="102"/>
+      <c r="F18" s="103"/>
       <c r="G18" s="50" t="s">
         <v>25</v>
       </c>
@@ -38430,18 +38841,18 @@
       <c r="AA18" s="1"/>
     </row>
     <row r="19" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="105" t="s">
+      <c r="A19" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="B19" s="108" t="s">
+      <c r="B19" s="72" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="109"/>
-      <c r="D19" s="110" t="s">
-        <v>123</v>
+      <c r="C19" s="73"/>
+      <c r="D19" s="71" t="s">
+        <v>120</v>
       </c>
-      <c r="E19" s="111"/>
-      <c r="F19" s="112"/>
+      <c r="E19" s="61"/>
+      <c r="F19" s="62"/>
       <c r="G19" s="50" t="s">
         <v>25</v>
       </c>
@@ -38467,16 +38878,16 @@
       <c r="AA19" s="1"/>
     </row>
     <row r="20" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="106"/>
-      <c r="B20" s="108" t="s">
-        <v>120</v>
+      <c r="A20" s="105"/>
+      <c r="B20" s="72" t="s">
+        <v>117</v>
       </c>
-      <c r="C20" s="109"/>
-      <c r="D20" s="110" t="s">
-        <v>121</v>
+      <c r="C20" s="73"/>
+      <c r="D20" s="71" t="s">
+        <v>118</v>
       </c>
-      <c r="E20" s="111"/>
-      <c r="F20" s="112"/>
+      <c r="E20" s="61"/>
+      <c r="F20" s="62"/>
       <c r="G20" s="50" t="s">
         <v>25</v>
       </c>
@@ -38502,16 +38913,16 @@
       <c r="AA20" s="1"/>
     </row>
     <row r="21" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="106"/>
-      <c r="B21" s="108" t="s">
+      <c r="A21" s="105"/>
+      <c r="B21" s="72" t="s">
         <v>48</v>
       </c>
-      <c r="C21" s="109"/>
-      <c r="D21" s="110" t="s">
-        <v>122</v>
+      <c r="C21" s="73"/>
+      <c r="D21" s="71" t="s">
+        <v>119</v>
       </c>
-      <c r="E21" s="111"/>
-      <c r="F21" s="112"/>
+      <c r="E21" s="61"/>
+      <c r="F21" s="62"/>
       <c r="G21" s="50" t="s">
         <v>25</v>
       </c>
@@ -38537,16 +38948,16 @@
       <c r="AA21" s="1"/>
     </row>
     <row r="22" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="107"/>
-      <c r="B22" s="108" t="s">
+      <c r="A22" s="106"/>
+      <c r="B22" s="72" t="s">
         <v>15</v>
       </c>
-      <c r="C22" s="109"/>
-      <c r="D22" s="110" t="s">
-        <v>124</v>
+      <c r="C22" s="73"/>
+      <c r="D22" s="71" t="s">
+        <v>121</v>
       </c>
-      <c r="E22" s="111"/>
-      <c r="F22" s="112"/>
+      <c r="E22" s="61"/>
+      <c r="F22" s="62"/>
       <c r="G22" s="50" t="s">
         <v>25</v>
       </c>
@@ -38600,18 +39011,18 @@
       <c r="Z23" s="8"/>
     </row>
     <row r="24" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="95" t="s">
+      <c r="A24" s="91" t="s">
         <v>16</v>
       </c>
-      <c r="B24" s="96"/>
-      <c r="C24" s="96"/>
-      <c r="D24" s="96"/>
-      <c r="E24" s="97"/>
-      <c r="F24" s="98" t="s">
+      <c r="B24" s="92"/>
+      <c r="C24" s="92"/>
+      <c r="D24" s="92"/>
+      <c r="E24" s="93"/>
+      <c r="F24" s="94" t="s">
         <v>17</v>
       </c>
-      <c r="G24" s="96"/>
-      <c r="H24" s="97"/>
+      <c r="G24" s="92"/>
+      <c r="H24" s="93"/>
       <c r="I24" s="7"/>
       <c r="J24" s="8"/>
       <c r="K24" s="8"/>
@@ -38635,17 +39046,17 @@
       <c r="A25" s="13">
         <v>5</v>
       </c>
-      <c r="B25" s="118" t="s">
+      <c r="B25" s="60" t="s">
         <v>18</v>
       </c>
-      <c r="C25" s="111"/>
-      <c r="D25" s="111"/>
-      <c r="E25" s="112"/>
-      <c r="F25" s="117">
+      <c r="C25" s="61"/>
+      <c r="D25" s="61"/>
+      <c r="E25" s="62"/>
+      <c r="F25" s="63">
         <v>100</v>
       </c>
-      <c r="G25" s="111"/>
-      <c r="H25" s="112"/>
+      <c r="G25" s="61"/>
+      <c r="H25" s="62"/>
       <c r="I25" s="7"/>
       <c r="J25" s="8"/>
       <c r="K25" s="8"/>
@@ -38669,17 +39080,17 @@
       <c r="A26" s="13">
         <v>4</v>
       </c>
-      <c r="B26" s="119" t="s">
+      <c r="B26" s="90" t="s">
         <v>50</v>
       </c>
-      <c r="C26" s="111"/>
-      <c r="D26" s="111"/>
-      <c r="E26" s="112"/>
-      <c r="F26" s="117">
+      <c r="C26" s="61"/>
+      <c r="D26" s="61"/>
+      <c r="E26" s="62"/>
+      <c r="F26" s="63">
         <v>80</v>
       </c>
-      <c r="G26" s="111"/>
-      <c r="H26" s="112"/>
+      <c r="G26" s="61"/>
+      <c r="H26" s="62"/>
       <c r="I26" s="7"/>
       <c r="J26" s="8"/>
       <c r="K26" s="8"/>
@@ -38703,17 +39114,17 @@
       <c r="A27" s="13">
         <v>3</v>
       </c>
-      <c r="B27" s="119" t="s">
+      <c r="B27" s="90" t="s">
         <v>49</v>
       </c>
-      <c r="C27" s="111"/>
-      <c r="D27" s="111"/>
-      <c r="E27" s="112"/>
-      <c r="F27" s="117">
+      <c r="C27" s="61"/>
+      <c r="D27" s="61"/>
+      <c r="E27" s="62"/>
+      <c r="F27" s="63">
         <v>65</v>
       </c>
-      <c r="G27" s="111"/>
-      <c r="H27" s="112"/>
+      <c r="G27" s="61"/>
+      <c r="H27" s="62"/>
       <c r="I27" s="7"/>
       <c r="J27" s="8"/>
       <c r="K27" s="8"/>
@@ -38737,17 +39148,17 @@
       <c r="A28" s="13">
         <v>2</v>
       </c>
-      <c r="B28" s="116" t="s">
+      <c r="B28" s="89" t="s">
         <v>19</v>
       </c>
-      <c r="C28" s="111"/>
-      <c r="D28" s="111"/>
-      <c r="E28" s="112"/>
-      <c r="F28" s="117">
+      <c r="C28" s="61"/>
+      <c r="D28" s="61"/>
+      <c r="E28" s="62"/>
+      <c r="F28" s="63">
         <v>50</v>
       </c>
-      <c r="G28" s="111"/>
-      <c r="H28" s="112"/>
+      <c r="G28" s="61"/>
+      <c r="H28" s="62"/>
       <c r="I28" s="7"/>
       <c r="J28" s="8"/>
       <c r="K28" s="8"/>
@@ -38771,17 +39182,17 @@
       <c r="A29" s="13">
         <v>1</v>
       </c>
-      <c r="B29" s="118" t="s">
+      <c r="B29" s="60" t="s">
         <v>20</v>
       </c>
-      <c r="C29" s="111"/>
-      <c r="D29" s="111"/>
-      <c r="E29" s="112"/>
-      <c r="F29" s="117">
+      <c r="C29" s="61"/>
+      <c r="D29" s="61"/>
+      <c r="E29" s="62"/>
+      <c r="F29" s="63">
         <v>30</v>
       </c>
-      <c r="G29" s="111"/>
-      <c r="H29" s="112"/>
+      <c r="G29" s="61"/>
+      <c r="H29" s="62"/>
       <c r="I29" s="7"/>
       <c r="J29" s="8"/>
       <c r="K29" s="8"/>
@@ -38870,16 +39281,16 @@
       <c r="D32" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="E32" s="146">
+      <c r="E32" s="163">
         <v>1</v>
       </c>
-      <c r="F32" s="146">
+      <c r="F32" s="163">
         <v>0</v>
       </c>
-      <c r="G32" s="147" t="s">
+      <c r="G32" s="164" t="s">
         <v>25</v>
       </c>
-      <c r="H32" s="149" t="s">
+      <c r="H32" s="166" t="s">
         <v>26</v>
       </c>
       <c r="I32" s="7"/>
@@ -38908,10 +39319,10 @@
       <c r="D33" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="E33" s="112"/>
-      <c r="F33" s="112"/>
-      <c r="G33" s="148"/>
-      <c r="H33" s="150"/>
+      <c r="E33" s="62"/>
+      <c r="F33" s="62"/>
+      <c r="G33" s="165"/>
+      <c r="H33" s="167"/>
       <c r="I33" s="7"/>
       <c r="J33" s="8"/>
       <c r="K33" s="8"/>
@@ -44761,23 +45172,24 @@
     <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="51">
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="F29:H29"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="F32:F33"/>
-    <mergeCell ref="G32:G33"/>
-    <mergeCell ref="H32:H33"/>
-    <mergeCell ref="B26:E26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="B27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="B28:E28"/>
-    <mergeCell ref="F28:H28"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="A24:E24"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="B25:E25"/>
-    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="A6:H6"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A11:C12"/>
+    <mergeCell ref="D11:G12"/>
+    <mergeCell ref="H11:J11"/>
+    <mergeCell ref="D17:F17"/>
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="D18:F18"/>
     <mergeCell ref="A19:A22"/>
@@ -44794,24 +45206,23 @@
     <mergeCell ref="D14:F14"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="A10:H10"/>
-    <mergeCell ref="A11:C12"/>
-    <mergeCell ref="D11:G12"/>
-    <mergeCell ref="H11:J11"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="A6:H6"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="B27:E27"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="G32:G33"/>
+    <mergeCell ref="H32:H33"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
@@ -44821,7 +45232,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEEFD98D-80BA-4BED-874A-8974BC9361D4}">
-  <dimension ref="A1:AA978"/>
+  <dimension ref="A1:AA979"/>
   <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.125" customWidth="1"/>
@@ -44838,16 +45249,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="151" t="s">
+      <c r="A1" s="144" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="152"/>
-      <c r="C1" s="152"/>
-      <c r="D1" s="152"/>
-      <c r="E1" s="152"/>
-      <c r="F1" s="152"/>
-      <c r="G1" s="152"/>
-      <c r="H1" s="153"/>
+      <c r="B1" s="145"/>
+      <c r="C1" s="145"/>
+      <c r="D1" s="145"/>
+      <c r="E1" s="145"/>
+      <c r="F1" s="145"/>
+      <c r="G1" s="145"/>
+      <c r="H1" s="146"/>
       <c r="I1" s="7"/>
       <c r="J1" s="8"/>
       <c r="K1" s="8"/>
@@ -44868,16 +45279,16 @@
       <c r="Z1" s="8"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="159" t="s">
+      <c r="A2" s="152" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="160"/>
-      <c r="C2" s="160"/>
-      <c r="D2" s="160"/>
-      <c r="E2" s="160"/>
-      <c r="F2" s="160"/>
-      <c r="G2" s="160"/>
-      <c r="H2" s="161"/>
+      <c r="B2" s="153"/>
+      <c r="C2" s="153"/>
+      <c r="D2" s="153"/>
+      <c r="E2" s="153"/>
+      <c r="F2" s="153"/>
+      <c r="G2" s="153"/>
+      <c r="H2" s="154"/>
       <c r="I2" s="7"/>
       <c r="J2" s="8"/>
       <c r="K2" s="8"/>
@@ -44898,16 +45309,16 @@
       <c r="Z2" s="8"/>
     </row>
     <row r="3" spans="1:26" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="162" t="s">
-        <v>130</v>
+      <c r="A3" s="155" t="s">
+        <v>127</v>
       </c>
-      <c r="B3" s="162"/>
-      <c r="C3" s="162"/>
-      <c r="D3" s="162"/>
-      <c r="E3" s="162"/>
-      <c r="F3" s="162"/>
-      <c r="G3" s="162"/>
-      <c r="H3" s="162"/>
+      <c r="B3" s="155"/>
+      <c r="C3" s="155"/>
+      <c r="D3" s="155"/>
+      <c r="E3" s="155"/>
+      <c r="F3" s="155"/>
+      <c r="G3" s="155"/>
+      <c r="H3" s="155"/>
       <c r="I3" s="7"/>
       <c r="J3" s="8"/>
       <c r="K3" s="8"/>
@@ -44928,16 +45339,16 @@
       <c r="Z3" s="8"/>
     </row>
     <row r="4" spans="1:26" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="163" t="s">
+      <c r="A4" s="156" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="163"/>
-      <c r="C4" s="163"/>
-      <c r="D4" s="163"/>
-      <c r="E4" s="163"/>
-      <c r="F4" s="163"/>
-      <c r="G4" s="163"/>
-      <c r="H4" s="163"/>
+      <c r="B4" s="156"/>
+      <c r="C4" s="156"/>
+      <c r="D4" s="156"/>
+      <c r="E4" s="156"/>
+      <c r="F4" s="156"/>
+      <c r="G4" s="156"/>
+      <c r="H4" s="156"/>
       <c r="I4" s="7"/>
       <c r="J4" s="8"/>
       <c r="K4" s="8"/>
@@ -44958,16 +45369,16 @@
       <c r="Z4" s="8"/>
     </row>
     <row r="5" spans="1:26" ht="135" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="162" t="s">
-        <v>131</v>
+      <c r="A5" s="155" t="s">
+        <v>128</v>
       </c>
-      <c r="B5" s="162"/>
-      <c r="C5" s="162"/>
-      <c r="D5" s="162"/>
-      <c r="E5" s="162"/>
-      <c r="F5" s="162"/>
-      <c r="G5" s="162"/>
-      <c r="H5" s="162"/>
+      <c r="B5" s="155"/>
+      <c r="C5" s="155"/>
+      <c r="D5" s="155"/>
+      <c r="E5" s="155"/>
+      <c r="F5" s="155"/>
+      <c r="G5" s="155"/>
+      <c r="H5" s="155"/>
       <c r="I5" s="7"/>
       <c r="J5" s="8"/>
       <c r="K5" s="8"/>
@@ -44988,14 +45399,14 @@
       <c r="Z5" s="8"/>
     </row>
     <row r="6" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="164"/>
-      <c r="B6" s="164"/>
-      <c r="C6" s="164"/>
-      <c r="D6" s="164"/>
-      <c r="E6" s="164"/>
-      <c r="F6" s="164"/>
-      <c r="G6" s="164"/>
-      <c r="H6" s="164"/>
+      <c r="A6" s="157"/>
+      <c r="B6" s="157"/>
+      <c r="C6" s="157"/>
+      <c r="D6" s="157"/>
+      <c r="E6" s="157"/>
+      <c r="F6" s="157"/>
+      <c r="G6" s="157"/>
+      <c r="H6" s="157"/>
       <c r="J6" s="8"/>
       <c r="K6" s="8"/>
       <c r="L6" s="8"/>
@@ -45015,16 +45426,16 @@
       <c r="Z6" s="8"/>
     </row>
     <row r="7" spans="1:26" ht="192" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="162" t="s">
-        <v>132</v>
+      <c r="A7" s="155" t="s">
+        <v>129</v>
       </c>
-      <c r="B7" s="162"/>
-      <c r="C7" s="162"/>
-      <c r="D7" s="162"/>
-      <c r="E7" s="162"/>
-      <c r="F7" s="162"/>
-      <c r="G7" s="162"/>
-      <c r="H7" s="162"/>
+      <c r="B7" s="155"/>
+      <c r="C7" s="155"/>
+      <c r="D7" s="155"/>
+      <c r="E7" s="155"/>
+      <c r="F7" s="155"/>
+      <c r="G7" s="155"/>
+      <c r="H7" s="155"/>
       <c r="J7" s="8"/>
       <c r="K7" s="8"/>
       <c r="L7" s="8"/>
@@ -45044,14 +45455,14 @@
       <c r="Z7" s="8"/>
     </row>
     <row r="8" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="162"/>
-      <c r="B8" s="162"/>
-      <c r="C8" s="162"/>
-      <c r="D8" s="162"/>
-      <c r="E8" s="162"/>
-      <c r="F8" s="162"/>
-      <c r="G8" s="162"/>
-      <c r="H8" s="162"/>
+      <c r="A8" s="155"/>
+      <c r="B8" s="155"/>
+      <c r="C8" s="155"/>
+      <c r="D8" s="155"/>
+      <c r="E8" s="155"/>
+      <c r="F8" s="155"/>
+      <c r="G8" s="155"/>
+      <c r="H8" s="155"/>
       <c r="J8" s="8"/>
       <c r="K8" s="8"/>
       <c r="L8" s="8"/>
@@ -45071,16 +45482,16 @@
       <c r="Z8" s="8"/>
     </row>
     <row r="9" spans="1:26" ht="365.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="162" t="s">
-        <v>133</v>
+      <c r="A9" s="155" t="s">
+        <v>130</v>
       </c>
-      <c r="B9" s="162"/>
-      <c r="C9" s="162"/>
-      <c r="D9" s="162"/>
-      <c r="E9" s="162"/>
-      <c r="F9" s="162"/>
-      <c r="G9" s="162"/>
-      <c r="H9" s="162"/>
+      <c r="B9" s="155"/>
+      <c r="C9" s="155"/>
+      <c r="D9" s="155"/>
+      <c r="E9" s="155"/>
+      <c r="F9" s="155"/>
+      <c r="G9" s="155"/>
+      <c r="H9" s="155"/>
       <c r="I9" s="7"/>
       <c r="J9" s="8"/>
       <c r="K9" s="8"/>
@@ -45101,14 +45512,14 @@
       <c r="Z9" s="8"/>
     </row>
     <row r="10" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="170"/>
-      <c r="B10" s="171"/>
-      <c r="C10" s="171"/>
-      <c r="D10" s="171"/>
-      <c r="E10" s="171"/>
-      <c r="F10" s="171"/>
-      <c r="G10" s="171"/>
-      <c r="H10" s="172"/>
+      <c r="A10" s="168"/>
+      <c r="B10" s="169"/>
+      <c r="C10" s="169"/>
+      <c r="D10" s="169"/>
+      <c r="E10" s="169"/>
+      <c r="F10" s="169"/>
+      <c r="G10" s="169"/>
+      <c r="H10" s="170"/>
       <c r="J10" s="8"/>
       <c r="K10" s="8"/>
       <c r="L10" s="8"/>
@@ -45128,16 +45539,16 @@
       <c r="Z10" s="8"/>
     </row>
     <row r="11" spans="1:26" ht="240.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="173" t="s">
-        <v>134</v>
+      <c r="A11" s="171" t="s">
+        <v>131</v>
       </c>
-      <c r="B11" s="174"/>
-      <c r="C11" s="174"/>
-      <c r="D11" s="174"/>
-      <c r="E11" s="174"/>
-      <c r="F11" s="174"/>
-      <c r="G11" s="174"/>
-      <c r="H11" s="175"/>
+      <c r="B11" s="172"/>
+      <c r="C11" s="172"/>
+      <c r="D11" s="172"/>
+      <c r="E11" s="172"/>
+      <c r="F11" s="172"/>
+      <c r="G11" s="172"/>
+      <c r="H11" s="173"/>
       <c r="I11" s="7"/>
       <c r="J11" s="8"/>
       <c r="K11" s="8"/>
@@ -45158,16 +45569,16 @@
       <c r="Z11" s="8"/>
     </row>
     <row r="12" spans="1:26" ht="18" x14ac:dyDescent="0.25">
-      <c r="A12" s="163" t="s">
+      <c r="A12" s="156" t="s">
         <v>36</v>
       </c>
-      <c r="B12" s="165"/>
-      <c r="C12" s="165"/>
-      <c r="D12" s="165"/>
-      <c r="E12" s="165"/>
-      <c r="F12" s="165"/>
-      <c r="G12" s="165"/>
-      <c r="H12" s="165"/>
+      <c r="B12" s="158"/>
+      <c r="C12" s="158"/>
+      <c r="D12" s="158"/>
+      <c r="E12" s="158"/>
+      <c r="F12" s="158"/>
+      <c r="G12" s="158"/>
+      <c r="H12" s="158"/>
       <c r="I12" s="9"/>
       <c r="J12" s="10"/>
       <c r="K12" s="10"/>
@@ -45188,16 +45599,16 @@
       <c r="Z12" s="10"/>
     </row>
     <row r="13" spans="1:26" ht="246" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="162" t="s">
-        <v>135</v>
+      <c r="A13" s="155" t="s">
+        <v>132</v>
       </c>
-      <c r="B13" s="162"/>
-      <c r="C13" s="162"/>
-      <c r="D13" s="162"/>
-      <c r="E13" s="162"/>
-      <c r="F13" s="162"/>
-      <c r="G13" s="162"/>
-      <c r="H13" s="162"/>
+      <c r="B13" s="155"/>
+      <c r="C13" s="155"/>
+      <c r="D13" s="155"/>
+      <c r="E13" s="155"/>
+      <c r="F13" s="155"/>
+      <c r="G13" s="155"/>
+      <c r="H13" s="155"/>
       <c r="J13" s="8"/>
       <c r="K13" s="8"/>
       <c r="L13" s="8"/>
@@ -45217,16 +45628,16 @@
       <c r="Z13" s="8"/>
     </row>
     <row r="14" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="166" t="s">
+      <c r="A14" s="159" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="167"/>
-      <c r="C14" s="167"/>
-      <c r="D14" s="167"/>
-      <c r="E14" s="167"/>
-      <c r="F14" s="167"/>
-      <c r="G14" s="167"/>
-      <c r="H14" s="168"/>
+      <c r="B14" s="160"/>
+      <c r="C14" s="160"/>
+      <c r="D14" s="160"/>
+      <c r="E14" s="160"/>
+      <c r="F14" s="160"/>
+      <c r="G14" s="160"/>
+      <c r="H14" s="161"/>
       <c r="I14" s="7"/>
       <c r="J14" s="8"/>
       <c r="K14" s="8"/>
@@ -45247,22 +45658,22 @@
       <c r="Z14" s="8"/>
     </row>
     <row r="15" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="154" t="s">
+      <c r="A15" s="147" t="s">
         <v>10</v>
       </c>
-      <c r="B15" s="155"/>
-      <c r="C15" s="156"/>
-      <c r="D15" s="158" t="s">
+      <c r="B15" s="148"/>
+      <c r="C15" s="149"/>
+      <c r="D15" s="151" t="s">
         <v>11</v>
       </c>
-      <c r="E15" s="155"/>
-      <c r="F15" s="155"/>
-      <c r="G15" s="155"/>
-      <c r="H15" s="169" t="s">
+      <c r="E15" s="148"/>
+      <c r="F15" s="148"/>
+      <c r="G15" s="148"/>
+      <c r="H15" s="162" t="s">
         <v>12</v>
       </c>
-      <c r="I15" s="169"/>
-      <c r="J15" s="169"/>
+      <c r="I15" s="162"/>
+      <c r="J15" s="162"/>
       <c r="K15" s="8"/>
       <c r="L15" s="8"/>
       <c r="M15" s="8"/>
@@ -45281,13 +45692,13 @@
       <c r="Z15" s="8"/>
     </row>
     <row r="16" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="157"/>
-      <c r="B16" s="111"/>
-      <c r="C16" s="112"/>
-      <c r="D16" s="111"/>
-      <c r="E16" s="111"/>
-      <c r="F16" s="111"/>
-      <c r="G16" s="111"/>
+      <c r="A16" s="150"/>
+      <c r="B16" s="61"/>
+      <c r="C16" s="62"/>
+      <c r="D16" s="61"/>
+      <c r="E16" s="61"/>
+      <c r="F16" s="61"/>
+      <c r="G16" s="61"/>
       <c r="H16" s="49" t="s">
         <v>13</v>
       </c>
@@ -45315,18 +45726,18 @@
       <c r="Z16" s="8"/>
     </row>
     <row r="17" spans="1:27" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="113" t="s">
+      <c r="A17" s="107" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="84" t="s">
-        <v>110</v>
+      <c r="B17" s="110" t="s">
+        <v>107</v>
       </c>
-      <c r="C17" s="85"/>
-      <c r="D17" s="86" t="s">
-        <v>114</v>
+      <c r="C17" s="111"/>
+      <c r="D17" s="112" t="s">
+        <v>111</v>
       </c>
-      <c r="E17" s="76"/>
-      <c r="F17" s="75"/>
+      <c r="E17" s="102"/>
+      <c r="F17" s="103"/>
       <c r="G17" s="50" t="s">
         <v>25</v>
       </c>
@@ -45352,16 +45763,16 @@
       <c r="AA17" s="1"/>
     </row>
     <row r="18" spans="1:27" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="114"/>
-      <c r="B18" s="84" t="s">
-        <v>111</v>
+      <c r="A18" s="108"/>
+      <c r="B18" s="110" t="s">
+        <v>108</v>
       </c>
-      <c r="C18" s="85"/>
-      <c r="D18" s="86" t="s">
-        <v>115</v>
+      <c r="C18" s="111"/>
+      <c r="D18" s="112" t="s">
+        <v>112</v>
       </c>
-      <c r="E18" s="76"/>
-      <c r="F18" s="75"/>
+      <c r="E18" s="102"/>
+      <c r="F18" s="103"/>
       <c r="G18" s="50" t="s">
         <v>25</v>
       </c>
@@ -45387,16 +45798,16 @@
       <c r="AA18" s="1"/>
     </row>
     <row r="19" spans="1:27" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="114"/>
-      <c r="B19" s="87" t="s">
-        <v>112</v>
+      <c r="A19" s="108"/>
+      <c r="B19" s="113" t="s">
+        <v>109</v>
       </c>
-      <c r="C19" s="88"/>
-      <c r="D19" s="89" t="s">
-        <v>116</v>
+      <c r="C19" s="114"/>
+      <c r="D19" s="101" t="s">
+        <v>113</v>
       </c>
-      <c r="E19" s="76"/>
-      <c r="F19" s="75"/>
+      <c r="E19" s="102"/>
+      <c r="F19" s="103"/>
       <c r="G19" s="50" t="s">
         <v>25</v>
       </c>
@@ -45422,16 +45833,16 @@
       <c r="AA19" s="1"/>
     </row>
     <row r="20" spans="1:27" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="114"/>
-      <c r="B20" s="90" t="s">
-        <v>113</v>
+      <c r="A20" s="108"/>
+      <c r="B20" s="78" t="s">
+        <v>110</v>
       </c>
-      <c r="C20" s="91"/>
-      <c r="D20" s="92" t="s">
-        <v>118</v>
+      <c r="C20" s="79"/>
+      <c r="D20" s="115" t="s">
+        <v>140</v>
       </c>
-      <c r="E20" s="93"/>
-      <c r="F20" s="94"/>
+      <c r="E20" s="116"/>
+      <c r="F20" s="117"/>
       <c r="G20" s="50" t="s">
         <v>25</v>
       </c>
@@ -45457,16 +45868,16 @@
       <c r="AA20" s="1"/>
     </row>
     <row r="21" spans="1:27" ht="50.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="114"/>
-      <c r="B21" s="90" t="s">
+      <c r="A21" s="108"/>
+      <c r="B21" s="78" t="s">
         <v>67</v>
       </c>
-      <c r="C21" s="91"/>
-      <c r="D21" s="100" t="s">
-        <v>119</v>
+      <c r="C21" s="79"/>
+      <c r="D21" s="96" t="s">
+        <v>116</v>
       </c>
-      <c r="E21" s="101"/>
-      <c r="F21" s="102"/>
+      <c r="E21" s="97"/>
+      <c r="F21" s="98"/>
       <c r="G21" s="50" t="s">
         <v>25</v>
       </c>
@@ -45492,16 +45903,16 @@
       <c r="AA21" s="1"/>
     </row>
     <row r="22" spans="1:27" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="115"/>
-      <c r="B22" s="103" t="s">
-        <v>90</v>
+      <c r="A22" s="109"/>
+      <c r="B22" s="99" t="s">
+        <v>88</v>
       </c>
-      <c r="C22" s="104"/>
-      <c r="D22" s="89" t="s">
-        <v>117</v>
+      <c r="C22" s="100"/>
+      <c r="D22" s="101" t="s">
+        <v>114</v>
       </c>
-      <c r="E22" s="76"/>
-      <c r="F22" s="75"/>
+      <c r="E22" s="102"/>
+      <c r="F22" s="103"/>
       <c r="G22" s="50" t="s">
         <v>25</v>
       </c>
@@ -45527,18 +45938,18 @@
       <c r="AA22" s="1"/>
     </row>
     <row r="23" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="105" t="s">
+      <c r="A23" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="B23" s="108" t="s">
+      <c r="B23" s="72" t="s">
         <v>47</v>
       </c>
-      <c r="C23" s="109"/>
-      <c r="D23" s="110" t="s">
-        <v>123</v>
+      <c r="C23" s="73"/>
+      <c r="D23" s="71" t="s">
+        <v>120</v>
       </c>
-      <c r="E23" s="111"/>
-      <c r="F23" s="112"/>
+      <c r="E23" s="61"/>
+      <c r="F23" s="62"/>
       <c r="G23" s="50" t="s">
         <v>25</v>
       </c>
@@ -45564,16 +45975,16 @@
       <c r="AA23" s="1"/>
     </row>
     <row r="24" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="106"/>
-      <c r="B24" s="108" t="s">
-        <v>120</v>
+      <c r="A24" s="105"/>
+      <c r="B24" s="72" t="s">
+        <v>117</v>
       </c>
-      <c r="C24" s="109"/>
-      <c r="D24" s="110" t="s">
-        <v>121</v>
+      <c r="C24" s="73"/>
+      <c r="D24" s="71" t="s">
+        <v>118</v>
       </c>
-      <c r="E24" s="111"/>
-      <c r="F24" s="112"/>
+      <c r="E24" s="61"/>
+      <c r="F24" s="62"/>
       <c r="G24" s="50" t="s">
         <v>25</v>
       </c>
@@ -45599,16 +46010,16 @@
       <c r="AA24" s="1"/>
     </row>
     <row r="25" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="106"/>
-      <c r="B25" s="108" t="s">
+      <c r="A25" s="105"/>
+      <c r="B25" s="72" t="s">
         <v>48</v>
       </c>
-      <c r="C25" s="109"/>
-      <c r="D25" s="110" t="s">
-        <v>122</v>
+      <c r="C25" s="73"/>
+      <c r="D25" s="71" t="s">
+        <v>119</v>
       </c>
-      <c r="E25" s="111"/>
-      <c r="F25" s="112"/>
+      <c r="E25" s="61"/>
+      <c r="F25" s="62"/>
       <c r="G25" s="50" t="s">
         <v>25</v>
       </c>
@@ -45634,16 +46045,16 @@
       <c r="AA25" s="1"/>
     </row>
     <row r="26" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="107"/>
-      <c r="B26" s="108" t="s">
+      <c r="A26" s="106"/>
+      <c r="B26" s="72" t="s">
         <v>15</v>
       </c>
-      <c r="C26" s="109"/>
-      <c r="D26" s="110" t="s">
-        <v>124</v>
+      <c r="C26" s="73"/>
+      <c r="D26" s="71" t="s">
+        <v>121</v>
       </c>
-      <c r="E26" s="111"/>
-      <c r="F26" s="112"/>
+      <c r="E26" s="61"/>
+      <c r="F26" s="62"/>
       <c r="G26" s="50" t="s">
         <v>25</v>
       </c>
@@ -45697,18 +46108,18 @@
       <c r="Z27" s="8"/>
     </row>
     <row r="28" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="95" t="s">
+      <c r="A28" s="91" t="s">
         <v>16</v>
       </c>
-      <c r="B28" s="96"/>
-      <c r="C28" s="96"/>
-      <c r="D28" s="96"/>
-      <c r="E28" s="97"/>
-      <c r="F28" s="98" t="s">
+      <c r="B28" s="92"/>
+      <c r="C28" s="92"/>
+      <c r="D28" s="92"/>
+      <c r="E28" s="93"/>
+      <c r="F28" s="94" t="s">
         <v>17</v>
       </c>
-      <c r="G28" s="96"/>
-      <c r="H28" s="97"/>
+      <c r="G28" s="92"/>
+      <c r="H28" s="93"/>
       <c r="I28" s="7"/>
       <c r="J28" s="8"/>
       <c r="K28" s="8"/>
@@ -45732,17 +46143,17 @@
       <c r="A29" s="13">
         <v>5</v>
       </c>
-      <c r="B29" s="118" t="s">
+      <c r="B29" s="60" t="s">
         <v>18</v>
       </c>
-      <c r="C29" s="111"/>
-      <c r="D29" s="111"/>
-      <c r="E29" s="112"/>
-      <c r="F29" s="117">
+      <c r="C29" s="61"/>
+      <c r="D29" s="61"/>
+      <c r="E29" s="62"/>
+      <c r="F29" s="63">
         <v>100</v>
       </c>
-      <c r="G29" s="111"/>
-      <c r="H29" s="112"/>
+      <c r="G29" s="61"/>
+      <c r="H29" s="62"/>
       <c r="I29" s="7"/>
       <c r="J29" s="8"/>
       <c r="K29" s="8"/>
@@ -45764,19 +46175,19 @@
     </row>
     <row r="30" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="13">
-        <v>4</v>
+        <v>5</v>
       </c>
-      <c r="B30" s="119" t="s">
-        <v>50</v>
+      <c r="B30" s="90" t="s">
+        <v>139</v>
       </c>
-      <c r="C30" s="111"/>
-      <c r="D30" s="111"/>
-      <c r="E30" s="112"/>
-      <c r="F30" s="117">
+      <c r="C30" s="61"/>
+      <c r="D30" s="61"/>
+      <c r="E30" s="62"/>
+      <c r="F30" s="63">
         <v>80</v>
       </c>
-      <c r="G30" s="111"/>
-      <c r="H30" s="112"/>
+      <c r="G30" s="61"/>
+      <c r="H30" s="62"/>
       <c r="I30" s="7"/>
       <c r="J30" s="8"/>
       <c r="K30" s="8"/>
@@ -45798,19 +46209,19 @@
     </row>
     <row r="31" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="13">
-        <v>3</v>
+        <v>4</v>
       </c>
-      <c r="B31" s="119" t="s">
-        <v>49</v>
+      <c r="B31" s="90" t="s">
+        <v>50</v>
       </c>
-      <c r="C31" s="111"/>
-      <c r="D31" s="111"/>
-      <c r="E31" s="112"/>
-      <c r="F31" s="117">
-        <v>65</v>
+      <c r="C31" s="61"/>
+      <c r="D31" s="61"/>
+      <c r="E31" s="62"/>
+      <c r="F31" s="63">
+        <v>70</v>
       </c>
-      <c r="G31" s="111"/>
-      <c r="H31" s="112"/>
+      <c r="G31" s="61"/>
+      <c r="H31" s="62"/>
       <c r="I31" s="7"/>
       <c r="J31" s="8"/>
       <c r="K31" s="8"/>
@@ -45832,19 +46243,19 @@
     </row>
     <row r="32" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
-      <c r="B32" s="116" t="s">
-        <v>19</v>
+      <c r="B32" s="90" t="s">
+        <v>49</v>
       </c>
-      <c r="C32" s="111"/>
-      <c r="D32" s="111"/>
-      <c r="E32" s="112"/>
-      <c r="F32" s="117">
-        <v>50</v>
+      <c r="C32" s="61"/>
+      <c r="D32" s="61"/>
+      <c r="E32" s="62"/>
+      <c r="F32" s="63">
+        <v>65</v>
       </c>
-      <c r="G32" s="111"/>
-      <c r="H32" s="112"/>
+      <c r="G32" s="61"/>
+      <c r="H32" s="62"/>
       <c r="I32" s="7"/>
       <c r="J32" s="8"/>
       <c r="K32" s="8"/>
@@ -45866,19 +46277,19 @@
     </row>
     <row r="33" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
-      <c r="B33" s="118" t="s">
-        <v>20</v>
+      <c r="B33" s="89" t="s">
+        <v>19</v>
       </c>
-      <c r="C33" s="111"/>
-      <c r="D33" s="111"/>
-      <c r="E33" s="112"/>
-      <c r="F33" s="117">
-        <v>30</v>
+      <c r="C33" s="61"/>
+      <c r="D33" s="61"/>
+      <c r="E33" s="62"/>
+      <c r="F33" s="63">
+        <v>50</v>
       </c>
-      <c r="G33" s="111"/>
-      <c r="H33" s="112"/>
+      <c r="G33" s="61"/>
+      <c r="H33" s="62"/>
       <c r="I33" s="7"/>
       <c r="J33" s="8"/>
       <c r="K33" s="8"/>
@@ -45899,14 +46310,20 @@
       <c r="Z33" s="8"/>
     </row>
     <row r="34" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="14"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="15"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="16"/>
-      <c r="G34" s="17"/>
-      <c r="H34" s="17"/>
+      <c r="A34" s="13">
+        <v>1</v>
+      </c>
+      <c r="B34" s="60" t="s">
+        <v>20</v>
+      </c>
+      <c r="C34" s="61"/>
+      <c r="D34" s="61"/>
+      <c r="E34" s="62"/>
+      <c r="F34" s="63">
+        <v>30</v>
+      </c>
+      <c r="G34" s="61"/>
+      <c r="H34" s="62"/>
       <c r="I34" s="7"/>
       <c r="J34" s="8"/>
       <c r="K34" s="8"/>
@@ -45927,20 +46344,14 @@
       <c r="Z34" s="8"/>
     </row>
     <row r="35" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="17"/>
-      <c r="B35" s="17"/>
-      <c r="C35" s="18"/>
-      <c r="D35" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="E35" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="F35" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="G35" s="16"/>
-      <c r="H35" s="16"/>
+      <c r="A35" s="14"/>
+      <c r="B35" s="14"/>
+      <c r="C35" s="14"/>
+      <c r="D35" s="15"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="17"/>
+      <c r="H35" s="17"/>
       <c r="I35" s="7"/>
       <c r="J35" s="8"/>
       <c r="K35" s="8"/>
@@ -45964,21 +46375,17 @@
       <c r="A36" s="17"/>
       <c r="B36" s="17"/>
       <c r="C36" s="18"/>
-      <c r="D36" s="20" t="s">
-        <v>24</v>
+      <c r="D36" s="19" t="s">
+        <v>21</v>
       </c>
-      <c r="E36" s="146">
-        <v>1</v>
+      <c r="E36" s="19" t="s">
+        <v>22</v>
       </c>
-      <c r="F36" s="146">
-        <v>0</v>
+      <c r="F36" s="19" t="s">
+        <v>23</v>
       </c>
-      <c r="G36" s="147" t="s">
-        <v>25</v>
-      </c>
-      <c r="H36" s="149" t="s">
-        <v>26</v>
-      </c>
+      <c r="G36" s="16"/>
+      <c r="H36" s="16"/>
       <c r="I36" s="7"/>
       <c r="J36" s="8"/>
       <c r="K36" s="8"/>
@@ -46002,13 +46409,21 @@
       <c r="A37" s="17"/>
       <c r="B37" s="17"/>
       <c r="C37" s="18"/>
-      <c r="D37" s="21" t="s">
-        <v>27</v>
+      <c r="D37" s="20" t="s">
+        <v>24</v>
       </c>
-      <c r="E37" s="112"/>
-      <c r="F37" s="112"/>
-      <c r="G37" s="148"/>
-      <c r="H37" s="150"/>
+      <c r="E37" s="163">
+        <v>1</v>
+      </c>
+      <c r="F37" s="163">
+        <v>0</v>
+      </c>
+      <c r="G37" s="164" t="s">
+        <v>25</v>
+      </c>
+      <c r="H37" s="166" t="s">
+        <v>26</v>
+      </c>
       <c r="I37" s="7"/>
       <c r="J37" s="8"/>
       <c r="K37" s="8"/>
@@ -46029,14 +46444,16 @@
       <c r="Z37" s="8"/>
     </row>
     <row r="38" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="16"/>
-      <c r="B38" s="16"/>
-      <c r="C38" s="16"/>
-      <c r="D38" s="16"/>
-      <c r="E38" s="16"/>
-      <c r="F38" s="16"/>
-      <c r="G38" s="16"/>
-      <c r="H38" s="16"/>
+      <c r="A38" s="17"/>
+      <c r="B38" s="17"/>
+      <c r="C38" s="18"/>
+      <c r="D38" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="E38" s="62"/>
+      <c r="F38" s="62"/>
+      <c r="G38" s="165"/>
+      <c r="H38" s="167"/>
       <c r="I38" s="7"/>
       <c r="J38" s="8"/>
       <c r="K38" s="8"/>
@@ -46057,14 +46474,14 @@
       <c r="Z38" s="8"/>
     </row>
     <row r="39" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="8"/>
-      <c r="B39" s="8"/>
-      <c r="C39" s="8"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="8"/>
-      <c r="G39" s="8"/>
-      <c r="H39" s="8"/>
+      <c r="A39" s="16"/>
+      <c r="B39" s="16"/>
+      <c r="C39" s="16"/>
+      <c r="D39" s="16"/>
+      <c r="E39" s="16"/>
+      <c r="F39" s="16"/>
+      <c r="G39" s="16"/>
+      <c r="H39" s="16"/>
       <c r="I39" s="7"/>
       <c r="J39" s="8"/>
       <c r="K39" s="8"/>
@@ -51096,7 +51513,34 @@
       <c r="Y218" s="8"/>
       <c r="Z218" s="8"/>
     </row>
-    <row r="219" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="219" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A219" s="8"/>
+      <c r="B219" s="8"/>
+      <c r="C219" s="8"/>
+      <c r="D219" s="8"/>
+      <c r="E219" s="8"/>
+      <c r="F219" s="8"/>
+      <c r="G219" s="8"/>
+      <c r="H219" s="8"/>
+      <c r="I219" s="7"/>
+      <c r="J219" s="8"/>
+      <c r="K219" s="8"/>
+      <c r="L219" s="8"/>
+      <c r="M219" s="8"/>
+      <c r="N219" s="8"/>
+      <c r="O219" s="8"/>
+      <c r="P219" s="8"/>
+      <c r="Q219" s="8"/>
+      <c r="R219" s="8"/>
+      <c r="S219" s="8"/>
+      <c r="T219" s="8"/>
+      <c r="U219" s="8"/>
+      <c r="V219" s="8"/>
+      <c r="W219" s="8"/>
+      <c r="X219" s="8"/>
+      <c r="Y219" s="8"/>
+      <c r="Z219" s="8"/>
+    </row>
     <row r="220" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="221" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="222" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -51856,14 +52300,56 @@
     <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <mergeCells count="55">
+  <mergeCells count="57">
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="A6:H6"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A15:C16"/>
+    <mergeCell ref="D15:G16"/>
+    <mergeCell ref="H15:J15"/>
+    <mergeCell ref="A17:A22"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="E37:E38"/>
+    <mergeCell ref="F37:F38"/>
+    <mergeCell ref="G37:G38"/>
+    <mergeCell ref="H37:H38"/>
+    <mergeCell ref="B31:E31"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="F33:H33"/>
     <mergeCell ref="A8:H8"/>
     <mergeCell ref="A7:H7"/>
     <mergeCell ref="A10:H10"/>
     <mergeCell ref="A11:H11"/>
-    <mergeCell ref="B33:E33"/>
-    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="B34:E34"/>
+    <mergeCell ref="F34:H34"/>
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="D26:F26"/>
     <mergeCell ref="A28:E28"/>
@@ -51874,45 +52360,6 @@
     <mergeCell ref="B22:C22"/>
     <mergeCell ref="D22:F22"/>
     <mergeCell ref="A23:A26"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="H36:H37"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="F30:H30"/>
-    <mergeCell ref="B31:E31"/>
-    <mergeCell ref="F31:H31"/>
-    <mergeCell ref="B32:E32"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="A17:A22"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="A12:H12"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A15:C16"/>
-    <mergeCell ref="D15:G16"/>
-    <mergeCell ref="H15:J15"/>
-    <mergeCell ref="A6:H6"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A5:H5"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId1"/>

--- a/ds/planejamento/3semestre/planos/Plano_de_Ensino_PPDM.xlsx
+++ b/ds/planejamento/3semestre/planos/Plano_de_Ensino_PPDM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aluno\Desktop\senai2026\ds\planejamento\3semestre\planos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DESENVOLVIMENTO\Desktop\senai2026\ds\planejamento\3semestre\planos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5A30AE9-F57E-4844-94FA-3D7BA87C8402}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A958F3A-8241-44D4-8B2B-749E54CFB26D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,6 +28,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId10" roundtripDataChecksum="h9gkGl1sfnRHyr05LFfZmsKJ7cUyj85gDjaHNauDRX4="/>
@@ -863,6 +866,7 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="10"/>
       <color theme="10"/>
       <name val="Arial"/>
@@ -1585,214 +1589,41 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="34" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1824,277 +1655,220 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -2103,6 +1877,12 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2126,23 +1906,247 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2211,7 +2215,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>1190625</xdr:colOff>
+      <xdr:colOff>1358713</xdr:colOff>
       <xdr:row>26</xdr:row>
       <xdr:rowOff>5138016</xdr:rowOff>
     </xdr:to>
@@ -2333,7 +2337,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>438150</xdr:colOff>
+      <xdr:colOff>23532</xdr:colOff>
       <xdr:row>26</xdr:row>
       <xdr:rowOff>5119338</xdr:rowOff>
     </xdr:to>
@@ -3157,10 +3161,11 @@
   <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.125" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="6.75" customWidth="1"/>
     <col min="3" max="3" width="22.625" customWidth="1"/>
-    <col min="4" max="4" width="29" customWidth="1"/>
-    <col min="5" max="6" width="20.625" customWidth="1"/>
+    <col min="4" max="4" width="34.375" customWidth="1"/>
+    <col min="5" max="5" width="20.625" customWidth="1"/>
+    <col min="6" max="6" width="19.875" customWidth="1"/>
     <col min="7" max="7" width="10.5" customWidth="1"/>
     <col min="8" max="8" width="10.125" customWidth="1"/>
     <col min="9" max="9" width="9.375" customWidth="1"/>
@@ -3170,134 +3175,134 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:27" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="139" t="s">
+      <c r="A2" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="139"/>
-      <c r="C2" s="139"/>
-      <c r="D2" s="139"/>
-      <c r="E2" s="139"/>
-      <c r="F2" s="139"/>
-      <c r="G2" s="139"/>
-      <c r="H2" s="139"/>
-      <c r="I2" s="139"/>
-      <c r="J2" s="139"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="57"/>
     </row>
     <row r="3" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="136" t="s">
+      <c r="A3" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="137"/>
-      <c r="C3" s="140" t="s">
+      <c r="B3" s="72"/>
+      <c r="C3" s="58" t="s">
         <v>54</v>
       </c>
-      <c r="D3" s="141"/>
-      <c r="E3" s="130" t="s">
+      <c r="D3" s="59"/>
+      <c r="E3" s="65" t="s">
         <v>133</v>
       </c>
-      <c r="F3" s="131"/>
-      <c r="G3" s="138" t="s">
+      <c r="F3" s="66"/>
+      <c r="G3" s="56" t="s">
         <v>30</v>
       </c>
-      <c r="H3" s="138"/>
-      <c r="I3" s="138" t="s">
+      <c r="H3" s="56"/>
+      <c r="I3" s="56" t="s">
         <v>31</v>
       </c>
-      <c r="J3" s="138"/>
+      <c r="J3" s="56"/>
     </row>
     <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="136"/>
-      <c r="B4" s="137"/>
-      <c r="C4" s="142"/>
-      <c r="D4" s="143"/>
-      <c r="E4" s="134" t="s">
+      <c r="A4" s="71"/>
+      <c r="B4" s="72"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="61"/>
+      <c r="E4" s="69" t="s">
         <v>134</v>
       </c>
-      <c r="F4" s="135"/>
-      <c r="G4" s="120" t="s">
+      <c r="F4" s="70"/>
+      <c r="G4" s="55" t="s">
         <v>135</v>
       </c>
-      <c r="H4" s="120"/>
-      <c r="I4" s="121"/>
-      <c r="J4" s="121"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="62"/>
     </row>
     <row r="5" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="122" t="s">
+      <c r="A5" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="103"/>
-      <c r="C5" s="121" t="s">
+      <c r="B5" s="79"/>
+      <c r="C5" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="D5" s="121"/>
-      <c r="E5" s="126" t="s">
+      <c r="D5" s="62"/>
+      <c r="E5" s="86" t="s">
         <v>57</v>
       </c>
-      <c r="F5" s="127"/>
-      <c r="G5" s="120" t="s">
+      <c r="F5" s="87"/>
+      <c r="G5" s="55" t="s">
         <v>32</v>
       </c>
-      <c r="H5" s="120"/>
-      <c r="I5" s="120"/>
-      <c r="J5" s="120"/>
+      <c r="H5" s="55"/>
+      <c r="I5" s="55"/>
+      <c r="J5" s="55"/>
     </row>
     <row r="6" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="103"/>
-      <c r="B6" s="102"/>
-      <c r="C6" s="121"/>
-      <c r="D6" s="121"/>
-      <c r="E6" s="128" t="s">
+      <c r="A6" s="79"/>
+      <c r="B6" s="80"/>
+      <c r="C6" s="62"/>
+      <c r="D6" s="62"/>
+      <c r="E6" s="63" t="s">
         <v>43</v>
       </c>
-      <c r="F6" s="129"/>
-      <c r="G6" s="121"/>
-      <c r="H6" s="121"/>
-      <c r="I6" s="121"/>
-      <c r="J6" s="121"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="62"/>
     </row>
     <row r="7" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="122" t="s">
+      <c r="A7" s="78" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="103"/>
-      <c r="C7" s="123" t="s">
+      <c r="B7" s="79"/>
+      <c r="C7" s="81" t="s">
         <v>56</v>
       </c>
-      <c r="D7" s="123"/>
-      <c r="E7" s="132" t="s">
+      <c r="D7" s="81"/>
+      <c r="E7" s="67" t="s">
         <v>58</v>
       </c>
-      <c r="F7" s="133"/>
-      <c r="G7" s="121"/>
-      <c r="H7" s="121"/>
-      <c r="I7" s="121"/>
-      <c r="J7" s="121"/>
-    </row>
-    <row r="8" spans="1:27" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="103"/>
-      <c r="B8" s="102"/>
-      <c r="C8" s="123"/>
-      <c r="D8" s="123"/>
-      <c r="E8" s="132"/>
-      <c r="F8" s="133"/>
-      <c r="G8" s="121"/>
-      <c r="H8" s="121"/>
-      <c r="I8" s="121"/>
-      <c r="J8" s="121"/>
+      <c r="F7" s="68"/>
+      <c r="G7" s="62"/>
+      <c r="H7" s="62"/>
+      <c r="I7" s="62"/>
+      <c r="J7" s="62"/>
+    </row>
+    <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="79"/>
+      <c r="B8" s="80"/>
+      <c r="C8" s="81"/>
+      <c r="D8" s="81"/>
+      <c r="E8" s="67"/>
+      <c r="F8" s="68"/>
+      <c r="G8" s="62"/>
+      <c r="H8" s="62"/>
+      <c r="I8" s="62"/>
+      <c r="J8" s="62"/>
     </row>
     <row r="9" spans="1:27" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="124" t="s">
+      <c r="A9" s="82" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="124"/>
-      <c r="C9" s="124"/>
-      <c r="D9" s="124"/>
-      <c r="E9" s="124"/>
-      <c r="F9" s="124"/>
-      <c r="G9" s="124"/>
-      <c r="H9" s="124"/>
-      <c r="I9" s="124"/>
-      <c r="J9" s="124"/>
+      <c r="B9" s="82"/>
+      <c r="C9" s="82"/>
+      <c r="D9" s="82"/>
+      <c r="E9" s="82"/>
+      <c r="F9" s="82"/>
+      <c r="G9" s="82"/>
+      <c r="H9" s="82"/>
+      <c r="I9" s="82"/>
+      <c r="J9" s="82"/>
     </row>
     <row r="10" spans="1:27" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="33" t="s">
@@ -3318,14 +3323,14 @@
       <c r="F10" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="G10" s="125" t="s">
+      <c r="G10" s="83" t="s">
         <v>8</v>
       </c>
-      <c r="H10" s="125"/>
-      <c r="I10" s="125" t="s">
+      <c r="H10" s="83"/>
+      <c r="I10" s="83" t="s">
         <v>9</v>
       </c>
-      <c r="J10" s="125"/>
+      <c r="J10" s="83"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -3344,7 +3349,7 @@
       <c r="Z10" s="1"/>
       <c r="AA10" s="1"/>
     </row>
-    <row r="11" spans="1:27" ht="127.5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A11" s="36" t="s">
         <v>44</v>
       </c>
@@ -3360,17 +3365,17 @@
       <c r="E11" s="40" t="s">
         <v>62</v>
       </c>
-      <c r="F11" s="174" t="s">
+      <c r="F11" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="G11" s="51" t="s">
+      <c r="G11" s="84" t="s">
         <v>64</v>
       </c>
-      <c r="H11" s="52"/>
-      <c r="I11" s="51" t="s">
+      <c r="H11" s="85"/>
+      <c r="I11" s="84" t="s">
         <v>65</v>
       </c>
-      <c r="J11" s="52"/>
+      <c r="J11" s="85"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
@@ -3405,15 +3410,15 @@
       <c r="E12" s="42" t="s">
         <v>68</v>
       </c>
-      <c r="F12" s="175"/>
-      <c r="G12" s="51" t="s">
+      <c r="F12" s="52"/>
+      <c r="G12" s="84" t="s">
         <v>69</v>
       </c>
-      <c r="H12" s="52"/>
-      <c r="I12" s="53" t="s">
+      <c r="H12" s="85"/>
+      <c r="I12" s="76" t="s">
         <v>137</v>
       </c>
-      <c r="J12" s="54"/>
+      <c r="J12" s="77"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
@@ -3432,7 +3437,7 @@
       <c r="Z12" s="3"/>
       <c r="AA12" s="3"/>
     </row>
-    <row r="13" spans="1:27" ht="114.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A13" s="36" t="s">
         <v>46</v>
       </c>
@@ -3448,15 +3453,15 @@
       <c r="E13" s="42" t="s">
         <v>68</v>
       </c>
-      <c r="F13" s="176"/>
-      <c r="G13" s="51" t="s">
+      <c r="F13" s="53"/>
+      <c r="G13" s="84" t="s">
         <v>70</v>
       </c>
-      <c r="H13" s="52"/>
-      <c r="I13" s="53" t="s">
+      <c r="H13" s="85"/>
+      <c r="I13" s="76" t="s">
         <v>136</v>
       </c>
-      <c r="J13" s="54"/>
+      <c r="J13" s="77"/>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
@@ -3491,17 +3496,17 @@
       <c r="E14" s="44" t="s">
         <v>68</v>
       </c>
-      <c r="F14" s="177" t="s">
+      <c r="F14" s="54" t="s">
         <v>74</v>
       </c>
-      <c r="G14" s="51" t="s">
+      <c r="G14" s="84" t="s">
         <v>71</v>
       </c>
-      <c r="H14" s="52"/>
-      <c r="I14" s="53" t="s">
+      <c r="H14" s="85"/>
+      <c r="I14" s="76" t="s">
         <v>138</v>
       </c>
-      <c r="J14" s="54"/>
+      <c r="J14" s="77"/>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
@@ -3520,7 +3525,7 @@
       <c r="Z14" s="3"/>
       <c r="AA14" s="3"/>
     </row>
-    <row r="15" spans="1:27" ht="140.25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" ht="102" x14ac:dyDescent="0.2">
       <c r="A15" s="36" t="s">
         <v>86</v>
       </c>
@@ -3536,15 +3541,15 @@
       <c r="E15" s="44" t="s">
         <v>68</v>
       </c>
-      <c r="F15" s="175"/>
-      <c r="G15" s="51" t="s">
+      <c r="F15" s="52"/>
+      <c r="G15" s="84" t="s">
         <v>75</v>
       </c>
-      <c r="H15" s="52"/>
-      <c r="I15" s="53" t="s">
+      <c r="H15" s="85"/>
+      <c r="I15" s="76" t="s">
         <v>72</v>
       </c>
-      <c r="J15" s="54"/>
+      <c r="J15" s="77"/>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
@@ -3563,7 +3568,7 @@
       <c r="Z15" s="3"/>
       <c r="AA15" s="3"/>
     </row>
-    <row r="16" spans="1:27" ht="102" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" ht="102" x14ac:dyDescent="0.2">
       <c r="A16" s="37" t="s">
         <v>87</v>
       </c>
@@ -3579,15 +3584,15 @@
       <c r="E16" s="44" t="s">
         <v>68</v>
       </c>
-      <c r="F16" s="175"/>
-      <c r="G16" s="51" t="s">
+      <c r="F16" s="52"/>
+      <c r="G16" s="84" t="s">
         <v>78</v>
       </c>
-      <c r="H16" s="52"/>
-      <c r="I16" s="178" t="s">
+      <c r="H16" s="85"/>
+      <c r="I16" s="244" t="s">
         <v>72</v>
       </c>
-      <c r="J16" s="179"/>
+      <c r="J16" s="245"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
@@ -3622,13 +3627,13 @@
       <c r="E17" s="44" t="s">
         <v>68</v>
       </c>
-      <c r="F17" s="175"/>
-      <c r="G17" s="51" t="s">
+      <c r="F17" s="52"/>
+      <c r="G17" s="84" t="s">
         <v>79</v>
       </c>
-      <c r="H17" s="52"/>
-      <c r="I17" s="180"/>
-      <c r="J17" s="181"/>
+      <c r="H17" s="85"/>
+      <c r="I17" s="246"/>
+      <c r="J17" s="247"/>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
@@ -3647,7 +3652,7 @@
       <c r="Z17" s="3"/>
       <c r="AA17" s="3"/>
     </row>
-    <row r="18" spans="1:27" ht="242.25" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:27" ht="204" x14ac:dyDescent="0.2">
       <c r="A18" s="37" t="s">
         <v>59</v>
       </c>
@@ -3663,15 +3668,15 @@
       <c r="E18" s="44" t="s">
         <v>82</v>
       </c>
-      <c r="F18" s="175"/>
-      <c r="G18" s="51" t="s">
+      <c r="F18" s="52"/>
+      <c r="G18" s="84" t="s">
         <v>83</v>
       </c>
-      <c r="H18" s="52"/>
-      <c r="I18" s="178" t="s">
+      <c r="H18" s="85"/>
+      <c r="I18" s="244" t="s">
         <v>80</v>
       </c>
-      <c r="J18" s="179"/>
+      <c r="J18" s="245"/>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
@@ -3690,7 +3695,7 @@
       <c r="Z18" s="3"/>
       <c r="AA18" s="3"/>
     </row>
-    <row r="19" spans="1:27" ht="242.25" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:27" ht="204" x14ac:dyDescent="0.2">
       <c r="A19" s="36" t="s">
         <v>98</v>
       </c>
@@ -3706,13 +3711,13 @@
       <c r="E19" s="44" t="s">
         <v>92</v>
       </c>
-      <c r="F19" s="176"/>
-      <c r="G19" s="51" t="s">
+      <c r="F19" s="53"/>
+      <c r="G19" s="84" t="s">
         <v>93</v>
       </c>
-      <c r="H19" s="52"/>
-      <c r="I19" s="180"/>
-      <c r="J19" s="181"/>
+      <c r="H19" s="85"/>
+      <c r="I19" s="246"/>
+      <c r="J19" s="247"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
@@ -3750,14 +3755,14 @@
       <c r="F20" s="32" t="s">
         <v>101</v>
       </c>
-      <c r="G20" s="51" t="s">
+      <c r="G20" s="84" t="s">
         <v>102</v>
       </c>
-      <c r="H20" s="52"/>
-      <c r="I20" s="178" t="s">
+      <c r="H20" s="85"/>
+      <c r="I20" s="244" t="s">
         <v>72</v>
       </c>
-      <c r="J20" s="179"/>
+      <c r="J20" s="245"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
@@ -3776,7 +3781,7 @@
       <c r="Z20" s="1"/>
       <c r="AA20" s="1"/>
     </row>
-    <row r="21" spans="1:27" ht="76.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:27" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A21" s="37" t="s">
         <v>104</v>
       </c>
@@ -3795,12 +3800,12 @@
       <c r="F21" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="G21" s="51" t="s">
+      <c r="G21" s="84" t="s">
         <v>103</v>
       </c>
-      <c r="H21" s="52"/>
-      <c r="I21" s="180"/>
-      <c r="J21" s="181"/>
+      <c r="H21" s="85"/>
+      <c r="I21" s="246"/>
+      <c r="J21" s="247"/>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
@@ -3831,10 +3836,10 @@
       <c r="D22" s="22"/>
       <c r="E22" s="22"/>
       <c r="F22" s="23"/>
-      <c r="G22" s="55"/>
-      <c r="H22" s="56"/>
-      <c r="I22" s="57"/>
-      <c r="J22" s="58"/>
+      <c r="G22" s="148"/>
+      <c r="H22" s="149"/>
+      <c r="I22" s="150"/>
+      <c r="J22" s="151"/>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
@@ -3854,18 +3859,18 @@
       <c r="AA22" s="1"/>
     </row>
     <row r="23" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="74" t="s">
+      <c r="A23" s="129" t="s">
         <v>51</v>
       </c>
-      <c r="B23" s="75"/>
-      <c r="C23" s="75"/>
-      <c r="D23" s="75"/>
-      <c r="E23" s="75"/>
-      <c r="F23" s="75"/>
-      <c r="G23" s="75"/>
-      <c r="H23" s="75"/>
-      <c r="I23" s="75"/>
-      <c r="J23" s="76"/>
+      <c r="B23" s="130"/>
+      <c r="C23" s="130"/>
+      <c r="D23" s="130"/>
+      <c r="E23" s="130"/>
+      <c r="F23" s="130"/>
+      <c r="G23" s="130"/>
+      <c r="H23" s="130"/>
+      <c r="I23" s="130"/>
+      <c r="J23" s="131"/>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
@@ -3885,18 +3890,18 @@
       <c r="AA23" s="1"/>
     </row>
     <row r="24" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="77" t="s">
+      <c r="A24" s="132" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="77"/>
-      <c r="C24" s="77"/>
-      <c r="D24" s="77"/>
-      <c r="E24" s="77"/>
-      <c r="F24" s="77"/>
-      <c r="G24" s="77"/>
-      <c r="H24" s="77"/>
-      <c r="I24" s="77"/>
-      <c r="J24" s="77"/>
+      <c r="B24" s="132"/>
+      <c r="C24" s="132"/>
+      <c r="D24" s="132"/>
+      <c r="E24" s="132"/>
+      <c r="F24" s="132"/>
+      <c r="G24" s="132"/>
+      <c r="H24" s="132"/>
+      <c r="I24" s="132"/>
+      <c r="J24" s="132"/>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
@@ -3916,18 +3921,18 @@
       <c r="AA24" s="1"/>
     </row>
     <row r="25" spans="1:27" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="70" t="s">
+      <c r="A25" s="128" t="s">
         <v>122</v>
       </c>
-      <c r="B25" s="70"/>
-      <c r="C25" s="70"/>
-      <c r="D25" s="70"/>
-      <c r="E25" s="70"/>
-      <c r="F25" s="70"/>
-      <c r="G25" s="70"/>
-      <c r="H25" s="70"/>
-      <c r="I25" s="70"/>
-      <c r="J25" s="70"/>
+      <c r="B25" s="128"/>
+      <c r="C25" s="128"/>
+      <c r="D25" s="128"/>
+      <c r="E25" s="128"/>
+      <c r="F25" s="128"/>
+      <c r="G25" s="128"/>
+      <c r="H25" s="128"/>
+      <c r="I25" s="128"/>
+      <c r="J25" s="128"/>
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
@@ -3947,18 +3952,18 @@
       <c r="AA25" s="1"/>
     </row>
     <row r="26" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="77" t="s">
+      <c r="A26" s="132" t="s">
         <v>35</v>
       </c>
-      <c r="B26" s="77"/>
-      <c r="C26" s="77"/>
-      <c r="D26" s="77"/>
-      <c r="E26" s="77"/>
-      <c r="F26" s="77"/>
-      <c r="G26" s="77"/>
-      <c r="H26" s="77"/>
-      <c r="I26" s="77"/>
-      <c r="J26" s="77"/>
+      <c r="B26" s="132"/>
+      <c r="C26" s="132"/>
+      <c r="D26" s="132"/>
+      <c r="E26" s="132"/>
+      <c r="F26" s="132"/>
+      <c r="G26" s="132"/>
+      <c r="H26" s="132"/>
+      <c r="I26" s="132"/>
+      <c r="J26" s="132"/>
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
@@ -3978,18 +3983,18 @@
       <c r="AA26" s="1"/>
     </row>
     <row r="27" spans="1:27" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="70" t="s">
+      <c r="A27" s="128" t="s">
         <v>105</v>
       </c>
-      <c r="B27" s="70"/>
-      <c r="C27" s="70"/>
-      <c r="D27" s="70"/>
-      <c r="E27" s="70"/>
-      <c r="F27" s="70"/>
-      <c r="G27" s="70"/>
-      <c r="H27" s="70"/>
-      <c r="I27" s="70"/>
-      <c r="J27" s="70"/>
+      <c r="B27" s="128"/>
+      <c r="C27" s="128"/>
+      <c r="D27" s="128"/>
+      <c r="E27" s="128"/>
+      <c r="F27" s="128"/>
+      <c r="G27" s="128"/>
+      <c r="H27" s="128"/>
+      <c r="I27" s="128"/>
+      <c r="J27" s="128"/>
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
@@ -4006,18 +4011,18 @@
       <c r="AA27" s="1"/>
     </row>
     <row r="28" spans="1:27" ht="18" x14ac:dyDescent="0.2">
-      <c r="A28" s="77" t="s">
+      <c r="A28" s="132" t="s">
         <v>36</v>
       </c>
-      <c r="B28" s="77"/>
-      <c r="C28" s="77"/>
-      <c r="D28" s="77"/>
-      <c r="E28" s="77"/>
-      <c r="F28" s="77"/>
-      <c r="G28" s="77"/>
-      <c r="H28" s="77"/>
-      <c r="I28" s="77"/>
-      <c r="J28" s="77"/>
+      <c r="B28" s="132"/>
+      <c r="C28" s="132"/>
+      <c r="D28" s="132"/>
+      <c r="E28" s="132"/>
+      <c r="F28" s="132"/>
+      <c r="G28" s="132"/>
+      <c r="H28" s="132"/>
+      <c r="I28" s="132"/>
+      <c r="J28" s="132"/>
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
@@ -4037,18 +4042,18 @@
       <c r="AA28" s="1"/>
     </row>
     <row r="29" spans="1:27" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="70" t="s">
+      <c r="A29" s="128" t="s">
         <v>106</v>
       </c>
-      <c r="B29" s="70"/>
-      <c r="C29" s="70"/>
-      <c r="D29" s="70"/>
-      <c r="E29" s="70"/>
-      <c r="F29" s="70"/>
-      <c r="G29" s="70"/>
-      <c r="H29" s="70"/>
-      <c r="I29" s="70"/>
-      <c r="J29" s="70"/>
+      <c r="B29" s="128"/>
+      <c r="C29" s="128"/>
+      <c r="D29" s="128"/>
+      <c r="E29" s="128"/>
+      <c r="F29" s="128"/>
+      <c r="G29" s="128"/>
+      <c r="H29" s="128"/>
+      <c r="I29" s="128"/>
+      <c r="J29" s="128"/>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
@@ -4068,16 +4073,16 @@
       <c r="AA29" s="1"/>
     </row>
     <row r="30" spans="1:27" ht="18" x14ac:dyDescent="0.2">
-      <c r="A30" s="83"/>
-      <c r="B30" s="84"/>
-      <c r="C30" s="84"/>
-      <c r="D30" s="84"/>
-      <c r="E30" s="84"/>
-      <c r="F30" s="84"/>
-      <c r="G30" s="84"/>
-      <c r="H30" s="84"/>
-      <c r="I30" s="84"/>
-      <c r="J30" s="85"/>
+      <c r="A30" s="136"/>
+      <c r="B30" s="137"/>
+      <c r="C30" s="137"/>
+      <c r="D30" s="137"/>
+      <c r="E30" s="137"/>
+      <c r="F30" s="137"/>
+      <c r="G30" s="137"/>
+      <c r="H30" s="137"/>
+      <c r="I30" s="137"/>
+      <c r="J30" s="138"/>
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
@@ -4097,16 +4102,16 @@
       <c r="AA30" s="1"/>
     </row>
     <row r="31" spans="1:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="86"/>
-      <c r="B31" s="87"/>
-      <c r="C31" s="87"/>
-      <c r="D31" s="87"/>
-      <c r="E31" s="87"/>
-      <c r="F31" s="87"/>
-      <c r="G31" s="87"/>
-      <c r="H31" s="87"/>
-      <c r="I31" s="87"/>
-      <c r="J31" s="88"/>
+      <c r="A31" s="139"/>
+      <c r="B31" s="140"/>
+      <c r="C31" s="140"/>
+      <c r="D31" s="140"/>
+      <c r="E31" s="140"/>
+      <c r="F31" s="140"/>
+      <c r="G31" s="140"/>
+      <c r="H31" s="140"/>
+      <c r="I31" s="140"/>
+      <c r="J31" s="141"/>
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
@@ -4126,18 +4131,18 @@
       <c r="AA31" s="1"/>
     </row>
     <row r="32" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="118" t="s">
+      <c r="A32" s="73" t="s">
         <v>37</v>
       </c>
-      <c r="B32" s="118"/>
-      <c r="C32" s="118"/>
-      <c r="D32" s="118"/>
-      <c r="E32" s="118"/>
-      <c r="F32" s="118"/>
-      <c r="G32" s="118"/>
-      <c r="H32" s="118"/>
-      <c r="I32" s="118"/>
-      <c r="J32" s="118"/>
+      <c r="B32" s="73"/>
+      <c r="C32" s="73"/>
+      <c r="D32" s="73"/>
+      <c r="E32" s="73"/>
+      <c r="F32" s="73"/>
+      <c r="G32" s="73"/>
+      <c r="H32" s="73"/>
+      <c r="I32" s="73"/>
+      <c r="J32" s="73"/>
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
@@ -4157,22 +4162,22 @@
       <c r="AA32" s="1"/>
     </row>
     <row r="33" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="80" t="s">
+      <c r="A33" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="B33" s="81"/>
-      <c r="C33" s="81"/>
-      <c r="D33" s="82" t="s">
+      <c r="B33" s="134"/>
+      <c r="C33" s="134"/>
+      <c r="D33" s="135" t="s">
         <v>11</v>
       </c>
-      <c r="E33" s="82"/>
-      <c r="F33" s="82"/>
-      <c r="G33" s="119" t="s">
+      <c r="E33" s="135"/>
+      <c r="F33" s="135"/>
+      <c r="G33" s="74" t="s">
         <v>40</v>
       </c>
-      <c r="H33" s="66"/>
-      <c r="I33" s="66"/>
-      <c r="J33" s="66"/>
+      <c r="H33" s="75"/>
+      <c r="I33" s="75"/>
+      <c r="J33" s="75"/>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
@@ -4192,12 +4197,12 @@
       <c r="AA33" s="1"/>
     </row>
     <row r="34" spans="1:27" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="81"/>
-      <c r="B34" s="81"/>
-      <c r="C34" s="81"/>
-      <c r="D34" s="82"/>
-      <c r="E34" s="82"/>
-      <c r="F34" s="82"/>
+      <c r="A34" s="134"/>
+      <c r="B34" s="134"/>
+      <c r="C34" s="134"/>
+      <c r="D34" s="135"/>
+      <c r="E34" s="135"/>
+      <c r="F34" s="135"/>
       <c r="G34" s="29">
         <v>1</v>
       </c>
@@ -4229,18 +4234,18 @@
       <c r="AA34" s="1"/>
     </row>
     <row r="35" spans="1:27" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="107" t="s">
+      <c r="A35" s="121" t="s">
         <v>14</v>
       </c>
-      <c r="B35" s="110" t="s">
+      <c r="B35" s="88" t="s">
         <v>107</v>
       </c>
-      <c r="C35" s="111"/>
-      <c r="D35" s="112" t="s">
+      <c r="C35" s="89"/>
+      <c r="D35" s="90" t="s">
         <v>111</v>
       </c>
-      <c r="E35" s="102"/>
-      <c r="F35" s="103"/>
+      <c r="E35" s="80"/>
+      <c r="F35" s="79"/>
       <c r="G35" s="12"/>
       <c r="H35" s="26"/>
       <c r="I35" s="27"/>
@@ -4264,16 +4269,16 @@
       <c r="AA35" s="1"/>
     </row>
     <row r="36" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="108"/>
-      <c r="B36" s="110" t="s">
+      <c r="A36" s="122"/>
+      <c r="B36" s="88" t="s">
         <v>108</v>
       </c>
-      <c r="C36" s="111"/>
-      <c r="D36" s="112" t="s">
+      <c r="C36" s="89"/>
+      <c r="D36" s="90" t="s">
         <v>112</v>
       </c>
-      <c r="E36" s="102"/>
-      <c r="F36" s="103"/>
+      <c r="E36" s="80"/>
+      <c r="F36" s="79"/>
       <c r="G36" s="12"/>
       <c r="H36" s="26"/>
       <c r="I36" s="22"/>
@@ -4297,16 +4302,16 @@
       <c r="AA36" s="1"/>
     </row>
     <row r="37" spans="1:27" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="108"/>
-      <c r="B37" s="242" t="s">
+      <c r="A37" s="122"/>
+      <c r="B37" s="97" t="s">
         <v>109</v>
       </c>
-      <c r="C37" s="243"/>
-      <c r="D37" s="246" t="s">
+      <c r="C37" s="98"/>
+      <c r="D37" s="101" t="s">
         <v>142</v>
       </c>
-      <c r="E37" s="121"/>
-      <c r="F37" s="247"/>
+      <c r="E37" s="62"/>
+      <c r="F37" s="102"/>
       <c r="G37" s="12"/>
       <c r="H37" s="26"/>
       <c r="I37" s="22"/>
@@ -4330,14 +4335,14 @@
       <c r="AA37" s="1"/>
     </row>
     <row r="38" spans="1:27" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="108"/>
-      <c r="B38" s="244"/>
-      <c r="C38" s="245"/>
-      <c r="D38" s="101" t="s">
+      <c r="A38" s="122"/>
+      <c r="B38" s="99"/>
+      <c r="C38" s="100"/>
+      <c r="D38" s="91" t="s">
         <v>143</v>
       </c>
-      <c r="E38" s="102"/>
-      <c r="F38" s="103"/>
+      <c r="E38" s="80"/>
+      <c r="F38" s="79"/>
       <c r="G38" s="12"/>
       <c r="H38" s="26"/>
       <c r="I38" s="22"/>
@@ -4361,16 +4366,16 @@
       <c r="AA38" s="1"/>
     </row>
     <row r="39" spans="1:27" ht="69" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="108"/>
-      <c r="B39" s="78" t="s">
+      <c r="A39" s="122"/>
+      <c r="B39" s="92" t="s">
         <v>110</v>
       </c>
-      <c r="C39" s="79"/>
-      <c r="D39" s="115" t="s">
+      <c r="C39" s="93"/>
+      <c r="D39" s="94" t="s">
         <v>141</v>
       </c>
-      <c r="E39" s="116"/>
-      <c r="F39" s="117"/>
+      <c r="E39" s="95"/>
+      <c r="F39" s="96"/>
       <c r="G39" s="12"/>
       <c r="H39" s="26"/>
       <c r="I39" s="22"/>
@@ -4394,16 +4399,16 @@
       <c r="AA39" s="1"/>
     </row>
     <row r="40" spans="1:27" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="108"/>
-      <c r="B40" s="78" t="s">
+      <c r="A40" s="122"/>
+      <c r="B40" s="92" t="s">
         <v>67</v>
       </c>
-      <c r="C40" s="79"/>
-      <c r="D40" s="96" t="s">
+      <c r="C40" s="93"/>
+      <c r="D40" s="108" t="s">
         <v>116</v>
       </c>
-      <c r="E40" s="97"/>
-      <c r="F40" s="98"/>
+      <c r="E40" s="109"/>
+      <c r="F40" s="110"/>
       <c r="G40" s="12"/>
       <c r="H40" s="26"/>
       <c r="I40" s="22"/>
@@ -4427,16 +4432,16 @@
       <c r="AA40" s="1"/>
     </row>
     <row r="41" spans="1:27" ht="84" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="109"/>
-      <c r="B41" s="99" t="s">
+      <c r="A41" s="123"/>
+      <c r="B41" s="111" t="s">
         <v>88</v>
       </c>
-      <c r="C41" s="100"/>
-      <c r="D41" s="101" t="s">
+      <c r="C41" s="112"/>
+      <c r="D41" s="91" t="s">
         <v>114</v>
       </c>
-      <c r="E41" s="102"/>
-      <c r="F41" s="103"/>
+      <c r="E41" s="80"/>
+      <c r="F41" s="79"/>
       <c r="G41" s="12"/>
       <c r="H41" s="26"/>
       <c r="I41" s="22"/>
@@ -4460,18 +4465,18 @@
       <c r="AA41" s="1"/>
     </row>
     <row r="42" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="104" t="s">
+      <c r="A42" s="113" t="s">
         <v>33</v>
       </c>
-      <c r="B42" s="72" t="s">
+      <c r="B42" s="116" t="s">
         <v>47</v>
       </c>
-      <c r="C42" s="73"/>
-      <c r="D42" s="71" t="s">
+      <c r="C42" s="117"/>
+      <c r="D42" s="118" t="s">
         <v>120</v>
       </c>
-      <c r="E42" s="61"/>
-      <c r="F42" s="62"/>
+      <c r="E42" s="119"/>
+      <c r="F42" s="120"/>
       <c r="G42" s="12"/>
       <c r="H42" s="26"/>
       <c r="I42" s="22"/>
@@ -4495,16 +4500,16 @@
       <c r="AA42" s="1"/>
     </row>
     <row r="43" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="105"/>
-      <c r="B43" s="72" t="s">
+      <c r="A43" s="114"/>
+      <c r="B43" s="116" t="s">
         <v>117</v>
       </c>
-      <c r="C43" s="73"/>
-      <c r="D43" s="71" t="s">
+      <c r="C43" s="117"/>
+      <c r="D43" s="118" t="s">
         <v>118</v>
       </c>
-      <c r="E43" s="61"/>
-      <c r="F43" s="62"/>
+      <c r="E43" s="119"/>
+      <c r="F43" s="120"/>
       <c r="G43" s="12"/>
       <c r="H43" s="26"/>
       <c r="I43" s="22"/>
@@ -4528,16 +4533,16 @@
       <c r="AA43" s="1"/>
     </row>
     <row r="44" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="105"/>
-      <c r="B44" s="72" t="s">
+      <c r="A44" s="114"/>
+      <c r="B44" s="116" t="s">
         <v>48</v>
       </c>
-      <c r="C44" s="73"/>
-      <c r="D44" s="71" t="s">
+      <c r="C44" s="117"/>
+      <c r="D44" s="118" t="s">
         <v>119</v>
       </c>
-      <c r="E44" s="61"/>
-      <c r="F44" s="62"/>
+      <c r="E44" s="119"/>
+      <c r="F44" s="120"/>
       <c r="G44" s="12"/>
       <c r="H44" s="26"/>
       <c r="I44" s="22"/>
@@ -4561,16 +4566,16 @@
       <c r="AA44" s="1"/>
     </row>
     <row r="45" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="106"/>
-      <c r="B45" s="72" t="s">
+      <c r="A45" s="115"/>
+      <c r="B45" s="116" t="s">
         <v>15</v>
       </c>
-      <c r="C45" s="73"/>
-      <c r="D45" s="71" t="s">
+      <c r="C45" s="117"/>
+      <c r="D45" s="118" t="s">
         <v>121</v>
       </c>
-      <c r="E45" s="61"/>
-      <c r="F45" s="62"/>
+      <c r="E45" s="119"/>
+      <c r="F45" s="120"/>
       <c r="G45" s="12"/>
       <c r="H45" s="26"/>
       <c r="I45" s="22"/>
@@ -4594,14 +4599,14 @@
       <c r="AA45" s="1"/>
     </row>
     <row r="46" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="95"/>
-      <c r="B46" s="95"/>
-      <c r="C46" s="95"/>
-      <c r="D46" s="95"/>
-      <c r="E46" s="95"/>
-      <c r="F46" s="95"/>
-      <c r="G46" s="95"/>
-      <c r="H46" s="95"/>
+      <c r="A46" s="107"/>
+      <c r="B46" s="107"/>
+      <c r="C46" s="107"/>
+      <c r="D46" s="107"/>
+      <c r="E46" s="107"/>
+      <c r="F46" s="107"/>
+      <c r="G46" s="107"/>
+      <c r="H46" s="107"/>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
       <c r="K46" s="1"/>
@@ -4623,18 +4628,18 @@
       <c r="AA46" s="1"/>
     </row>
     <row r="47" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="91" t="s">
+      <c r="A47" s="103" t="s">
         <v>16</v>
       </c>
-      <c r="B47" s="92"/>
-      <c r="C47" s="92"/>
-      <c r="D47" s="92"/>
-      <c r="E47" s="93"/>
-      <c r="F47" s="94" t="s">
+      <c r="B47" s="104"/>
+      <c r="C47" s="104"/>
+      <c r="D47" s="104"/>
+      <c r="E47" s="105"/>
+      <c r="F47" s="106" t="s">
         <v>17</v>
       </c>
-      <c r="G47" s="92"/>
-      <c r="H47" s="93"/>
+      <c r="G47" s="104"/>
+      <c r="H47" s="105"/>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
       <c r="K47" s="1"/>
@@ -4659,17 +4664,17 @@
       <c r="A48" s="13">
         <v>5</v>
       </c>
-      <c r="B48" s="60" t="s">
+      <c r="B48" s="126" t="s">
         <v>18</v>
       </c>
-      <c r="C48" s="61"/>
-      <c r="D48" s="61"/>
-      <c r="E48" s="62"/>
-      <c r="F48" s="63">
+      <c r="C48" s="119"/>
+      <c r="D48" s="119"/>
+      <c r="E48" s="120"/>
+      <c r="F48" s="125">
         <v>100</v>
       </c>
-      <c r="G48" s="61"/>
-      <c r="H48" s="62"/>
+      <c r="G48" s="119"/>
+      <c r="H48" s="120"/>
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
@@ -4694,17 +4699,17 @@
       <c r="A49" s="13">
         <v>4</v>
       </c>
-      <c r="B49" s="90" t="s">
+      <c r="B49" s="127" t="s">
         <v>50</v>
       </c>
-      <c r="C49" s="61"/>
-      <c r="D49" s="61"/>
-      <c r="E49" s="62"/>
-      <c r="F49" s="63">
+      <c r="C49" s="119"/>
+      <c r="D49" s="119"/>
+      <c r="E49" s="120"/>
+      <c r="F49" s="125">
         <v>80</v>
       </c>
-      <c r="G49" s="61"/>
-      <c r="H49" s="62"/>
+      <c r="G49" s="119"/>
+      <c r="H49" s="120"/>
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
@@ -4729,17 +4734,17 @@
       <c r="A50" s="13">
         <v>3</v>
       </c>
-      <c r="B50" s="90" t="s">
+      <c r="B50" s="127" t="s">
         <v>49</v>
       </c>
-      <c r="C50" s="61"/>
-      <c r="D50" s="61"/>
-      <c r="E50" s="62"/>
-      <c r="F50" s="63">
+      <c r="C50" s="119"/>
+      <c r="D50" s="119"/>
+      <c r="E50" s="120"/>
+      <c r="F50" s="125">
         <v>65</v>
       </c>
-      <c r="G50" s="61"/>
-      <c r="H50" s="62"/>
+      <c r="G50" s="119"/>
+      <c r="H50" s="120"/>
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
       <c r="K50" s="1"/>
@@ -4764,17 +4769,17 @@
       <c r="A51" s="13">
         <v>2</v>
       </c>
-      <c r="B51" s="89" t="s">
+      <c r="B51" s="124" t="s">
         <v>19</v>
       </c>
-      <c r="C51" s="61"/>
-      <c r="D51" s="61"/>
-      <c r="E51" s="62"/>
-      <c r="F51" s="63">
+      <c r="C51" s="119"/>
+      <c r="D51" s="119"/>
+      <c r="E51" s="120"/>
+      <c r="F51" s="125">
         <v>50</v>
       </c>
-      <c r="G51" s="61"/>
-      <c r="H51" s="62"/>
+      <c r="G51" s="119"/>
+      <c r="H51" s="120"/>
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
@@ -4799,17 +4804,17 @@
       <c r="A52" s="13">
         <v>1</v>
       </c>
-      <c r="B52" s="60" t="s">
+      <c r="B52" s="126" t="s">
         <v>20</v>
       </c>
-      <c r="C52" s="61"/>
-      <c r="D52" s="61"/>
-      <c r="E52" s="62"/>
-      <c r="F52" s="63">
+      <c r="C52" s="119"/>
+      <c r="D52" s="119"/>
+      <c r="E52" s="120"/>
+      <c r="F52" s="125">
         <v>30</v>
       </c>
-      <c r="G52" s="61"/>
-      <c r="H52" s="62"/>
+      <c r="G52" s="119"/>
+      <c r="H52" s="120"/>
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
@@ -4901,16 +4906,16 @@
       <c r="D55" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="E55" s="64">
+      <c r="E55" s="143">
         <v>1</v>
       </c>
-      <c r="F55" s="64">
+      <c r="F55" s="143">
         <v>0</v>
       </c>
-      <c r="G55" s="66" t="s">
+      <c r="G55" s="75" t="s">
         <v>25</v>
       </c>
-      <c r="H55" s="68" t="s">
+      <c r="H55" s="146" t="s">
         <v>26</v>
       </c>
       <c r="I55" s="1"/>
@@ -4940,10 +4945,10 @@
       <c r="D56" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="E56" s="65"/>
-      <c r="F56" s="65"/>
-      <c r="G56" s="67"/>
-      <c r="H56" s="69"/>
+      <c r="E56" s="144"/>
+      <c r="F56" s="144"/>
+      <c r="G56" s="145"/>
+      <c r="H56" s="147"/>
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
       <c r="K56" s="1"/>
@@ -4965,18 +4970,18 @@
       <c r="AA56" s="1"/>
     </row>
     <row r="57" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="59" t="s">
+      <c r="A57" s="142" t="s">
         <v>42</v>
       </c>
-      <c r="B57" s="59"/>
-      <c r="C57" s="59"/>
-      <c r="D57" s="59"/>
-      <c r="E57" s="59"/>
-      <c r="F57" s="59"/>
-      <c r="G57" s="59"/>
-      <c r="H57" s="59"/>
-      <c r="I57" s="59"/>
-      <c r="J57" s="59"/>
+      <c r="B57" s="142"/>
+      <c r="C57" s="142"/>
+      <c r="D57" s="142"/>
+      <c r="E57" s="142"/>
+      <c r="F57" s="142"/>
+      <c r="G57" s="142"/>
+      <c r="H57" s="142"/>
+      <c r="I57" s="142"/>
+      <c r="J57" s="142"/>
       <c r="K57" s="1"/>
       <c r="L57" s="1"/>
       <c r="M57" s="1"/>
@@ -4996,16 +5001,16 @@
       <c r="AA57" s="1"/>
     </row>
     <row r="58" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="59"/>
-      <c r="B58" s="59"/>
-      <c r="C58" s="59"/>
-      <c r="D58" s="59"/>
-      <c r="E58" s="59"/>
-      <c r="F58" s="59"/>
-      <c r="G58" s="59"/>
-      <c r="H58" s="59"/>
-      <c r="I58" s="59"/>
-      <c r="J58" s="59"/>
+      <c r="A58" s="142"/>
+      <c r="B58" s="142"/>
+      <c r="C58" s="142"/>
+      <c r="D58" s="142"/>
+      <c r="E58" s="142"/>
+      <c r="F58" s="142"/>
+      <c r="G58" s="142"/>
+      <c r="H58" s="142"/>
+      <c r="I58" s="142"/>
+      <c r="J58" s="142"/>
       <c r="K58" s="1"/>
       <c r="L58" s="1"/>
       <c r="M58" s="1"/>
@@ -31155,22 +31160,64 @@
     </row>
   </sheetData>
   <mergeCells count="98">
-    <mergeCell ref="F11:F13"/>
-    <mergeCell ref="F14:F19"/>
-    <mergeCell ref="I18:J19"/>
-    <mergeCell ref="I20:J21"/>
-    <mergeCell ref="I16:J17"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="C3:D4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="E7:F8"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="A3:B4"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="A57:J58"/>
+    <mergeCell ref="B52:E52"/>
+    <mergeCell ref="F52:H52"/>
+    <mergeCell ref="E55:E56"/>
+    <mergeCell ref="F55:F56"/>
+    <mergeCell ref="G55:G56"/>
+    <mergeCell ref="H55:H56"/>
+    <mergeCell ref="A27:J27"/>
+    <mergeCell ref="D45:F45"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="A23:J23"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A26:J26"/>
+    <mergeCell ref="A28:J28"/>
+    <mergeCell ref="A25:J25"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="A33:C34"/>
+    <mergeCell ref="D33:F34"/>
+    <mergeCell ref="A30:J30"/>
+    <mergeCell ref="A31:J31"/>
+    <mergeCell ref="A29:J29"/>
+    <mergeCell ref="B51:E51"/>
+    <mergeCell ref="F51:H51"/>
+    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="F48:H48"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="F49:H49"/>
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="F50:H50"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="F47:H47"/>
+    <mergeCell ref="A46:H46"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="A42:A45"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="A35:A41"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="B37:C38"/>
+    <mergeCell ref="D37:F37"/>
     <mergeCell ref="A32:J32"/>
     <mergeCell ref="G33:J33"/>
     <mergeCell ref="G5:J5"/>
@@ -31187,64 +31234,22 @@
     <mergeCell ref="G11:H11"/>
     <mergeCell ref="G12:H12"/>
     <mergeCell ref="E5:F5"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="B37:C38"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="A47:E47"/>
-    <mergeCell ref="F47:H47"/>
-    <mergeCell ref="A46:H46"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="A42:A45"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="D42:F42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="D44:F44"/>
-    <mergeCell ref="A35:A41"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="B51:E51"/>
-    <mergeCell ref="F51:H51"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="F48:H48"/>
-    <mergeCell ref="B49:E49"/>
-    <mergeCell ref="F49:H49"/>
-    <mergeCell ref="B50:E50"/>
-    <mergeCell ref="F50:H50"/>
-    <mergeCell ref="A27:J27"/>
-    <mergeCell ref="D45:F45"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="A23:J23"/>
-    <mergeCell ref="A24:J24"/>
-    <mergeCell ref="A26:J26"/>
-    <mergeCell ref="A28:J28"/>
-    <mergeCell ref="A25:J25"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="A33:C34"/>
-    <mergeCell ref="D33:F34"/>
-    <mergeCell ref="A30:J30"/>
-    <mergeCell ref="A31:J31"/>
-    <mergeCell ref="A29:J29"/>
-    <mergeCell ref="A57:J58"/>
-    <mergeCell ref="B52:E52"/>
-    <mergeCell ref="F52:H52"/>
-    <mergeCell ref="E55:E56"/>
-    <mergeCell ref="F55:F56"/>
-    <mergeCell ref="G55:G56"/>
-    <mergeCell ref="H55:H56"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="E7:F8"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="A3:B4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="C3:D4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="F11:F13"/>
+    <mergeCell ref="F14:F19"/>
+    <mergeCell ref="I18:J19"/>
+    <mergeCell ref="I20:J21"/>
+    <mergeCell ref="I16:J17"/>
     <mergeCell ref="G16:H16"/>
     <mergeCell ref="G17:H17"/>
     <mergeCell ref="I13:J13"/>
@@ -31261,8 +31266,12 @@
     <hyperlink ref="I20:J21" location="'Situação Avaliação Formativa 4'!A1" display="Situação de aprendizagem formativa. A partir de um protótipo, codificar a interface de um aplicativo." xr:uid="{1E94F7A5-0AB2-4FEB-985D-8D18F717F9A5}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965" bottom="0.78740157480314965" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="83" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="59" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <rowBreaks count="2" manualBreakCount="2">
+    <brk id="18" max="9" man="1"/>
+    <brk id="22" max="16383" man="1"/>
+  </rowBreaks>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -31286,16 +31295,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="144" t="s">
+      <c r="A1" s="202" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="145"/>
-      <c r="C1" s="145"/>
-      <c r="D1" s="145"/>
-      <c r="E1" s="145"/>
-      <c r="F1" s="145"/>
-      <c r="G1" s="145"/>
-      <c r="H1" s="146"/>
+      <c r="B1" s="203"/>
+      <c r="C1" s="203"/>
+      <c r="D1" s="203"/>
+      <c r="E1" s="203"/>
+      <c r="F1" s="203"/>
+      <c r="G1" s="203"/>
+      <c r="H1" s="204"/>
       <c r="I1" s="7"/>
       <c r="J1" s="8"/>
       <c r="K1" s="8"/>
@@ -31316,16 +31325,16 @@
       <c r="Z1" s="8"/>
     </row>
     <row r="2" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="152" t="s">
+      <c r="A2" s="205" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="153"/>
-      <c r="C2" s="153"/>
-      <c r="D2" s="153"/>
-      <c r="E2" s="153"/>
-      <c r="F2" s="153"/>
-      <c r="G2" s="153"/>
-      <c r="H2" s="154"/>
+      <c r="B2" s="206"/>
+      <c r="C2" s="206"/>
+      <c r="D2" s="206"/>
+      <c r="E2" s="206"/>
+      <c r="F2" s="206"/>
+      <c r="G2" s="206"/>
+      <c r="H2" s="207"/>
       <c r="I2" s="7"/>
       <c r="J2" s="8"/>
       <c r="K2" s="8"/>
@@ -31346,16 +31355,16 @@
       <c r="Z2" s="8"/>
     </row>
     <row r="3" spans="1:27" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="155" t="s">
+      <c r="A3" s="208" t="s">
         <v>123</v>
       </c>
-      <c r="B3" s="155"/>
-      <c r="C3" s="155"/>
-      <c r="D3" s="155"/>
-      <c r="E3" s="155"/>
-      <c r="F3" s="155"/>
-      <c r="G3" s="155"/>
-      <c r="H3" s="155"/>
+      <c r="B3" s="208"/>
+      <c r="C3" s="208"/>
+      <c r="D3" s="208"/>
+      <c r="E3" s="208"/>
+      <c r="F3" s="208"/>
+      <c r="G3" s="208"/>
+      <c r="H3" s="208"/>
       <c r="I3" s="7"/>
       <c r="J3" s="8"/>
       <c r="K3" s="8"/>
@@ -31376,16 +31385,16 @@
       <c r="Z3" s="8"/>
     </row>
     <row r="4" spans="1:27" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="156" t="s">
+      <c r="A4" s="209" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="156"/>
-      <c r="C4" s="156"/>
-      <c r="D4" s="156"/>
-      <c r="E4" s="156"/>
-      <c r="F4" s="156"/>
-      <c r="G4" s="156"/>
-      <c r="H4" s="156"/>
+      <c r="B4" s="209"/>
+      <c r="C4" s="209"/>
+      <c r="D4" s="209"/>
+      <c r="E4" s="209"/>
+      <c r="F4" s="209"/>
+      <c r="G4" s="209"/>
+      <c r="H4" s="209"/>
       <c r="I4" s="7"/>
       <c r="J4" s="8"/>
       <c r="K4" s="8"/>
@@ -31406,16 +31415,16 @@
       <c r="Z4" s="8"/>
     </row>
     <row r="5" spans="1:27" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="155" t="s">
+      <c r="A5" s="208" t="s">
         <v>124</v>
       </c>
-      <c r="B5" s="155"/>
-      <c r="C5" s="155"/>
-      <c r="D5" s="155"/>
-      <c r="E5" s="155"/>
-      <c r="F5" s="155"/>
-      <c r="G5" s="155"/>
-      <c r="H5" s="155"/>
+      <c r="B5" s="208"/>
+      <c r="C5" s="208"/>
+      <c r="D5" s="208"/>
+      <c r="E5" s="208"/>
+      <c r="F5" s="208"/>
+      <c r="G5" s="208"/>
+      <c r="H5" s="208"/>
       <c r="I5" s="7"/>
       <c r="J5" s="8"/>
       <c r="K5" s="8"/>
@@ -31436,14 +31445,14 @@
       <c r="Z5" s="8"/>
     </row>
     <row r="6" spans="1:27" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="157"/>
-      <c r="B6" s="157"/>
-      <c r="C6" s="157"/>
-      <c r="D6" s="157"/>
-      <c r="E6" s="157"/>
-      <c r="F6" s="157"/>
-      <c r="G6" s="157"/>
-      <c r="H6" s="157"/>
+      <c r="A6" s="210"/>
+      <c r="B6" s="210"/>
+      <c r="C6" s="210"/>
+      <c r="D6" s="210"/>
+      <c r="E6" s="210"/>
+      <c r="F6" s="210"/>
+      <c r="G6" s="210"/>
+      <c r="H6" s="210"/>
       <c r="J6" s="8"/>
       <c r="K6" s="8"/>
       <c r="L6" s="8"/>
@@ -31463,14 +31472,14 @@
       <c r="Z6" s="8"/>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A7" s="155"/>
-      <c r="B7" s="155"/>
-      <c r="C7" s="155"/>
-      <c r="D7" s="155"/>
-      <c r="E7" s="155"/>
-      <c r="F7" s="155"/>
-      <c r="G7" s="155"/>
-      <c r="H7" s="155"/>
+      <c r="A7" s="208"/>
+      <c r="B7" s="208"/>
+      <c r="C7" s="208"/>
+      <c r="D7" s="208"/>
+      <c r="E7" s="208"/>
+      <c r="F7" s="208"/>
+      <c r="G7" s="208"/>
+      <c r="H7" s="208"/>
       <c r="I7" s="7"/>
       <c r="J7" s="8"/>
       <c r="K7" s="8"/>
@@ -31491,16 +31500,16 @@
       <c r="Z7" s="8"/>
     </row>
     <row r="8" spans="1:27" ht="18" x14ac:dyDescent="0.25">
-      <c r="A8" s="156" t="s">
+      <c r="A8" s="209" t="s">
         <v>36</v>
       </c>
-      <c r="B8" s="158"/>
-      <c r="C8" s="158"/>
-      <c r="D8" s="158"/>
-      <c r="E8" s="158"/>
-      <c r="F8" s="158"/>
-      <c r="G8" s="158"/>
-      <c r="H8" s="158"/>
+      <c r="B8" s="211"/>
+      <c r="C8" s="211"/>
+      <c r="D8" s="211"/>
+      <c r="E8" s="211"/>
+      <c r="F8" s="211"/>
+      <c r="G8" s="211"/>
+      <c r="H8" s="211"/>
       <c r="I8" s="9"/>
       <c r="J8" s="10"/>
       <c r="K8" s="10"/>
@@ -31521,16 +31530,16 @@
       <c r="Z8" s="10"/>
     </row>
     <row r="9" spans="1:27" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="155" t="s">
+      <c r="A9" s="208" t="s">
         <v>106</v>
       </c>
-      <c r="B9" s="155"/>
-      <c r="C9" s="155"/>
-      <c r="D9" s="155"/>
-      <c r="E9" s="155"/>
-      <c r="F9" s="155"/>
-      <c r="G9" s="155"/>
-      <c r="H9" s="155"/>
+      <c r="B9" s="208"/>
+      <c r="C9" s="208"/>
+      <c r="D9" s="208"/>
+      <c r="E9" s="208"/>
+      <c r="F9" s="208"/>
+      <c r="G9" s="208"/>
+      <c r="H9" s="208"/>
       <c r="J9" s="8"/>
       <c r="K9" s="8"/>
       <c r="L9" s="8"/>
@@ -31550,16 +31559,16 @@
       <c r="Z9" s="8"/>
     </row>
     <row r="10" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="241" t="s">
+      <c r="A10" s="163" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="241"/>
-      <c r="C10" s="241"/>
-      <c r="D10" s="241"/>
-      <c r="E10" s="241"/>
-      <c r="F10" s="241"/>
-      <c r="G10" s="241"/>
-      <c r="H10" s="241"/>
+      <c r="B10" s="163"/>
+      <c r="C10" s="163"/>
+      <c r="D10" s="163"/>
+      <c r="E10" s="163"/>
+      <c r="F10" s="163"/>
+      <c r="G10" s="163"/>
+      <c r="H10" s="163"/>
       <c r="I10" s="7"/>
       <c r="J10" s="8"/>
       <c r="K10" s="8"/>
@@ -31580,22 +31589,22 @@
       <c r="Z10" s="8"/>
     </row>
     <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="147" t="s">
+      <c r="A11" s="155" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="151"/>
-      <c r="C11" s="239"/>
-      <c r="D11" s="147" t="s">
+      <c r="B11" s="156"/>
+      <c r="C11" s="161"/>
+      <c r="D11" s="155" t="s">
         <v>11</v>
       </c>
-      <c r="E11" s="151"/>
-      <c r="F11" s="151"/>
-      <c r="G11" s="235"/>
-      <c r="H11" s="232" t="s">
+      <c r="E11" s="156"/>
+      <c r="F11" s="156"/>
+      <c r="G11" s="157"/>
+      <c r="H11" s="152" t="s">
         <v>12</v>
       </c>
-      <c r="I11" s="233"/>
-      <c r="J11" s="234"/>
+      <c r="I11" s="153"/>
+      <c r="J11" s="154"/>
       <c r="K11" s="8"/>
       <c r="L11" s="8"/>
       <c r="M11" s="8"/>
@@ -31614,13 +31623,13 @@
       <c r="Z11" s="8"/>
     </row>
     <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="236"/>
-      <c r="B12" s="237"/>
-      <c r="C12" s="240"/>
-      <c r="D12" s="236"/>
-      <c r="E12" s="237"/>
-      <c r="F12" s="237"/>
-      <c r="G12" s="238"/>
+      <c r="A12" s="158"/>
+      <c r="B12" s="159"/>
+      <c r="C12" s="162"/>
+      <c r="D12" s="158"/>
+      <c r="E12" s="159"/>
+      <c r="F12" s="159"/>
+      <c r="G12" s="160"/>
       <c r="H12" s="49" t="s">
         <v>13</v>
       </c>
@@ -31648,18 +31657,18 @@
       <c r="Z12" s="8"/>
     </row>
     <row r="13" spans="1:27" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="197" t="s">
+      <c r="A13" s="225" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="214" t="s">
+      <c r="B13" s="164" t="s">
         <v>107</v>
       </c>
-      <c r="C13" s="215"/>
-      <c r="D13" s="229" t="s">
+      <c r="C13" s="165"/>
+      <c r="D13" s="166" t="s">
         <v>111</v>
       </c>
-      <c r="E13" s="230"/>
-      <c r="F13" s="231"/>
+      <c r="E13" s="167"/>
+      <c r="F13" s="168"/>
       <c r="G13" s="50" t="s">
         <v>25</v>
       </c>
@@ -31685,16 +31694,16 @@
       <c r="AA13" s="1"/>
     </row>
     <row r="14" spans="1:27" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="198"/>
-      <c r="B14" s="110" t="s">
+      <c r="A14" s="226"/>
+      <c r="B14" s="88" t="s">
         <v>108</v>
       </c>
-      <c r="C14" s="228"/>
-      <c r="D14" s="225" t="s">
+      <c r="C14" s="169"/>
+      <c r="D14" s="170" t="s">
         <v>112</v>
       </c>
-      <c r="E14" s="226"/>
-      <c r="F14" s="227"/>
+      <c r="E14" s="171"/>
+      <c r="F14" s="172"/>
       <c r="G14" s="50" t="s">
         <v>25</v>
       </c>
@@ -31720,16 +31729,16 @@
       <c r="AA14" s="1"/>
     </row>
     <row r="15" spans="1:27" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="198"/>
-      <c r="B15" s="223" t="s">
+      <c r="A15" s="226"/>
+      <c r="B15" s="173" t="s">
         <v>109</v>
       </c>
-      <c r="C15" s="224"/>
-      <c r="D15" s="96" t="s">
+      <c r="C15" s="174"/>
+      <c r="D15" s="108" t="s">
         <v>113</v>
       </c>
-      <c r="E15" s="212"/>
-      <c r="F15" s="213"/>
+      <c r="E15" s="175"/>
+      <c r="F15" s="176"/>
       <c r="G15" s="50" t="s">
         <v>25</v>
       </c>
@@ -31755,16 +31764,16 @@
       <c r="AA15" s="1"/>
     </row>
     <row r="16" spans="1:27" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="198"/>
-      <c r="B16" s="221" t="s">
+      <c r="A16" s="226"/>
+      <c r="B16" s="177" t="s">
         <v>110</v>
       </c>
-      <c r="C16" s="222"/>
-      <c r="D16" s="218" t="s">
+      <c r="C16" s="178"/>
+      <c r="D16" s="179" t="s">
         <v>115</v>
       </c>
-      <c r="E16" s="219"/>
-      <c r="F16" s="220"/>
+      <c r="E16" s="180"/>
+      <c r="F16" s="181"/>
       <c r="G16" s="50" t="s">
         <v>25</v>
       </c>
@@ -31790,16 +31799,16 @@
       <c r="AA16" s="1"/>
     </row>
     <row r="17" spans="1:27" ht="50.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="198"/>
-      <c r="B17" s="214" t="s">
+      <c r="A17" s="226"/>
+      <c r="B17" s="164" t="s">
         <v>67</v>
       </c>
-      <c r="C17" s="215"/>
-      <c r="D17" s="96" t="s">
+      <c r="C17" s="165"/>
+      <c r="D17" s="108" t="s">
         <v>116</v>
       </c>
-      <c r="E17" s="212"/>
-      <c r="F17" s="213"/>
+      <c r="E17" s="175"/>
+      <c r="F17" s="176"/>
       <c r="G17" s="50" t="s">
         <v>25</v>
       </c>
@@ -31825,16 +31834,16 @@
       <c r="AA17" s="1"/>
     </row>
     <row r="18" spans="1:27" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="199"/>
-      <c r="B18" s="110" t="s">
+      <c r="A18" s="227"/>
+      <c r="B18" s="88" t="s">
         <v>88</v>
       </c>
-      <c r="C18" s="217"/>
-      <c r="D18" s="216" t="s">
+      <c r="C18" s="182"/>
+      <c r="D18" s="183" t="s">
         <v>114</v>
       </c>
-      <c r="E18" s="212"/>
-      <c r="F18" s="213"/>
+      <c r="E18" s="175"/>
+      <c r="F18" s="176"/>
       <c r="G18" s="50" t="s">
         <v>25</v>
       </c>
@@ -31860,18 +31869,18 @@
       <c r="AA18" s="1"/>
     </row>
     <row r="19" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="210" t="s">
+      <c r="A19" s="218" t="s">
         <v>33</v>
       </c>
-      <c r="B19" s="208" t="s">
+      <c r="B19" s="220" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="209"/>
-      <c r="D19" s="205" t="s">
+      <c r="C19" s="221"/>
+      <c r="D19" s="222" t="s">
         <v>120</v>
       </c>
-      <c r="E19" s="206"/>
-      <c r="F19" s="207"/>
+      <c r="E19" s="223"/>
+      <c r="F19" s="224"/>
       <c r="G19" s="50" t="s">
         <v>25</v>
       </c>
@@ -31897,16 +31906,16 @@
       <c r="AA19" s="1"/>
     </row>
     <row r="20" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="104"/>
-      <c r="B20" s="203" t="s">
+      <c r="A20" s="113"/>
+      <c r="B20" s="200" t="s">
         <v>117</v>
       </c>
-      <c r="C20" s="204"/>
-      <c r="D20" s="200" t="s">
+      <c r="C20" s="201"/>
+      <c r="D20" s="215" t="s">
         <v>118</v>
       </c>
-      <c r="E20" s="201"/>
-      <c r="F20" s="202"/>
+      <c r="E20" s="216"/>
+      <c r="F20" s="217"/>
       <c r="G20" s="50" t="s">
         <v>25</v>
       </c>
@@ -31932,16 +31941,16 @@
       <c r="AA20" s="1"/>
     </row>
     <row r="21" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="104"/>
-      <c r="B21" s="203" t="s">
+      <c r="A21" s="113"/>
+      <c r="B21" s="200" t="s">
         <v>48</v>
       </c>
-      <c r="C21" s="204"/>
-      <c r="D21" s="200" t="s">
+      <c r="C21" s="201"/>
+      <c r="D21" s="215" t="s">
         <v>119</v>
       </c>
-      <c r="E21" s="201"/>
-      <c r="F21" s="202"/>
+      <c r="E21" s="216"/>
+      <c r="F21" s="217"/>
       <c r="G21" s="50" t="s">
         <v>25</v>
       </c>
@@ -31967,16 +31976,16 @@
       <c r="AA21" s="1"/>
     </row>
     <row r="22" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="211"/>
-      <c r="B22" s="203" t="s">
+      <c r="A22" s="219"/>
+      <c r="B22" s="200" t="s">
         <v>15</v>
       </c>
-      <c r="C22" s="204"/>
-      <c r="D22" s="200" t="s">
+      <c r="C22" s="201"/>
+      <c r="D22" s="215" t="s">
         <v>121</v>
       </c>
-      <c r="E22" s="201"/>
-      <c r="F22" s="202"/>
+      <c r="E22" s="216"/>
+      <c r="F22" s="217"/>
       <c r="G22" s="50" t="s">
         <v>25</v>
       </c>
@@ -32030,18 +32039,18 @@
       <c r="Z23" s="8"/>
     </row>
     <row r="24" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="91" t="s">
+      <c r="A24" s="103" t="s">
         <v>16</v>
       </c>
-      <c r="B24" s="94"/>
-      <c r="C24" s="94"/>
-      <c r="D24" s="94"/>
-      <c r="E24" s="196"/>
-      <c r="F24" s="91" t="s">
+      <c r="B24" s="106"/>
+      <c r="C24" s="106"/>
+      <c r="D24" s="106"/>
+      <c r="E24" s="186"/>
+      <c r="F24" s="103" t="s">
         <v>17</v>
       </c>
-      <c r="G24" s="94"/>
-      <c r="H24" s="196"/>
+      <c r="G24" s="106"/>
+      <c r="H24" s="186"/>
       <c r="I24" s="7"/>
       <c r="J24" s="8"/>
       <c r="K24" s="8"/>
@@ -32065,17 +32074,17 @@
       <c r="A25" s="13">
         <v>5</v>
       </c>
-      <c r="B25" s="184" t="s">
+      <c r="B25" s="193" t="s">
         <v>18</v>
       </c>
-      <c r="C25" s="185"/>
-      <c r="D25" s="185"/>
-      <c r="E25" s="186"/>
-      <c r="F25" s="193">
+      <c r="C25" s="194"/>
+      <c r="D25" s="194"/>
+      <c r="E25" s="195"/>
+      <c r="F25" s="187">
         <v>100</v>
       </c>
-      <c r="G25" s="194"/>
-      <c r="H25" s="195"/>
+      <c r="G25" s="188"/>
+      <c r="H25" s="189"/>
       <c r="I25" s="7"/>
       <c r="J25" s="8"/>
       <c r="K25" s="8"/>
@@ -32099,17 +32108,17 @@
       <c r="A26" s="13">
         <v>4</v>
       </c>
-      <c r="B26" s="187" t="s">
+      <c r="B26" s="212" t="s">
         <v>50</v>
       </c>
-      <c r="C26" s="188"/>
-      <c r="D26" s="188"/>
-      <c r="E26" s="189"/>
-      <c r="F26" s="193">
+      <c r="C26" s="213"/>
+      <c r="D26" s="213"/>
+      <c r="E26" s="214"/>
+      <c r="F26" s="187">
         <v>80</v>
       </c>
-      <c r="G26" s="194"/>
-      <c r="H26" s="195"/>
+      <c r="G26" s="188"/>
+      <c r="H26" s="189"/>
       <c r="I26" s="7"/>
       <c r="J26" s="8"/>
       <c r="K26" s="8"/>
@@ -32133,17 +32142,17 @@
       <c r="A27" s="13">
         <v>3</v>
       </c>
-      <c r="B27" s="187" t="s">
+      <c r="B27" s="212" t="s">
         <v>49</v>
       </c>
-      <c r="C27" s="188"/>
-      <c r="D27" s="188"/>
-      <c r="E27" s="189"/>
-      <c r="F27" s="193">
+      <c r="C27" s="213"/>
+      <c r="D27" s="213"/>
+      <c r="E27" s="214"/>
+      <c r="F27" s="187">
         <v>65</v>
       </c>
-      <c r="G27" s="194"/>
-      <c r="H27" s="195"/>
+      <c r="G27" s="188"/>
+      <c r="H27" s="189"/>
       <c r="I27" s="7"/>
       <c r="J27" s="8"/>
       <c r="K27" s="8"/>
@@ -32173,11 +32182,11 @@
       <c r="C28" s="191"/>
       <c r="D28" s="191"/>
       <c r="E28" s="192"/>
-      <c r="F28" s="193">
+      <c r="F28" s="187">
         <v>50</v>
       </c>
-      <c r="G28" s="194"/>
-      <c r="H28" s="195"/>
+      <c r="G28" s="188"/>
+      <c r="H28" s="189"/>
       <c r="I28" s="7"/>
       <c r="J28" s="8"/>
       <c r="K28" s="8"/>
@@ -32201,17 +32210,17 @@
       <c r="A29" s="13">
         <v>1</v>
       </c>
-      <c r="B29" s="184" t="s">
+      <c r="B29" s="193" t="s">
         <v>20</v>
       </c>
-      <c r="C29" s="185"/>
-      <c r="D29" s="185"/>
-      <c r="E29" s="186"/>
-      <c r="F29" s="193">
+      <c r="C29" s="194"/>
+      <c r="D29" s="194"/>
+      <c r="E29" s="195"/>
+      <c r="F29" s="187">
         <v>30</v>
       </c>
-      <c r="G29" s="194"/>
-      <c r="H29" s="195"/>
+      <c r="G29" s="188"/>
+      <c r="H29" s="189"/>
       <c r="I29" s="7"/>
       <c r="J29" s="8"/>
       <c r="K29" s="8"/>
@@ -32300,16 +32309,16 @@
       <c r="D32" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="E32" s="182">
+      <c r="E32" s="184">
         <v>1</v>
       </c>
-      <c r="F32" s="182">
+      <c r="F32" s="184">
         <v>0</v>
       </c>
-      <c r="G32" s="164" t="s">
+      <c r="G32" s="196" t="s">
         <v>25</v>
       </c>
-      <c r="H32" s="166" t="s">
+      <c r="H32" s="198" t="s">
         <v>26</v>
       </c>
       <c r="I32" s="7"/>
@@ -32338,10 +32347,10 @@
       <c r="D33" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="E33" s="183"/>
-      <c r="F33" s="183"/>
-      <c r="G33" s="165"/>
-      <c r="H33" s="167"/>
+      <c r="E33" s="185"/>
+      <c r="F33" s="185"/>
+      <c r="G33" s="197"/>
+      <c r="H33" s="199"/>
       <c r="I33" s="7"/>
       <c r="J33" s="8"/>
       <c r="K33" s="8"/>
@@ -38191,28 +38200,18 @@
     <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="51">
-    <mergeCell ref="H11:J11"/>
-    <mergeCell ref="D11:G12"/>
-    <mergeCell ref="A11:C12"/>
-    <mergeCell ref="A10:H10"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="F32:F33"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="B28:E28"/>
-    <mergeCell ref="F28:H28"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="A19:A22"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="A13:A18"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="G32:G33"/>
     <mergeCell ref="H32:H33"/>
@@ -38229,19 +38228,29 @@
     <mergeCell ref="B26:E26"/>
     <mergeCell ref="F26:H26"/>
     <mergeCell ref="B27:E27"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="F29:H29"/>
     <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="A24:E24"/>
-    <mergeCell ref="B25:E25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="A19:A22"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="A13:A18"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="H11:J11"/>
+    <mergeCell ref="D11:G12"/>
+    <mergeCell ref="A11:C12"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:F13"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
@@ -38268,16 +38277,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="144" t="s">
+      <c r="A1" s="202" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="145"/>
-      <c r="C1" s="145"/>
-      <c r="D1" s="145"/>
-      <c r="E1" s="145"/>
-      <c r="F1" s="145"/>
-      <c r="G1" s="145"/>
-      <c r="H1" s="146"/>
+      <c r="B1" s="203"/>
+      <c r="C1" s="203"/>
+      <c r="D1" s="203"/>
+      <c r="E1" s="203"/>
+      <c r="F1" s="203"/>
+      <c r="G1" s="203"/>
+      <c r="H1" s="204"/>
       <c r="I1" s="7"/>
       <c r="J1" s="8"/>
       <c r="K1" s="8"/>
@@ -38298,16 +38307,16 @@
       <c r="Z1" s="8"/>
     </row>
     <row r="2" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="152" t="s">
+      <c r="A2" s="205" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="153"/>
-      <c r="C2" s="153"/>
-      <c r="D2" s="153"/>
-      <c r="E2" s="153"/>
-      <c r="F2" s="153"/>
-      <c r="G2" s="153"/>
-      <c r="H2" s="154"/>
+      <c r="B2" s="206"/>
+      <c r="C2" s="206"/>
+      <c r="D2" s="206"/>
+      <c r="E2" s="206"/>
+      <c r="F2" s="206"/>
+      <c r="G2" s="206"/>
+      <c r="H2" s="207"/>
       <c r="I2" s="7"/>
       <c r="J2" s="8"/>
       <c r="K2" s="8"/>
@@ -38328,16 +38337,16 @@
       <c r="Z2" s="8"/>
     </row>
     <row r="3" spans="1:27" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="155" t="s">
+      <c r="A3" s="208" t="s">
         <v>125</v>
       </c>
-      <c r="B3" s="155"/>
-      <c r="C3" s="155"/>
-      <c r="D3" s="155"/>
-      <c r="E3" s="155"/>
-      <c r="F3" s="155"/>
-      <c r="G3" s="155"/>
-      <c r="H3" s="155"/>
+      <c r="B3" s="208"/>
+      <c r="C3" s="208"/>
+      <c r="D3" s="208"/>
+      <c r="E3" s="208"/>
+      <c r="F3" s="208"/>
+      <c r="G3" s="208"/>
+      <c r="H3" s="208"/>
       <c r="I3" s="7"/>
       <c r="J3" s="8"/>
       <c r="K3" s="8"/>
@@ -38358,16 +38367,16 @@
       <c r="Z3" s="8"/>
     </row>
     <row r="4" spans="1:27" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="156" t="s">
+      <c r="A4" s="209" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="156"/>
-      <c r="C4" s="156"/>
-      <c r="D4" s="156"/>
-      <c r="E4" s="156"/>
-      <c r="F4" s="156"/>
-      <c r="G4" s="156"/>
-      <c r="H4" s="156"/>
+      <c r="B4" s="209"/>
+      <c r="C4" s="209"/>
+      <c r="D4" s="209"/>
+      <c r="E4" s="209"/>
+      <c r="F4" s="209"/>
+      <c r="G4" s="209"/>
+      <c r="H4" s="209"/>
       <c r="I4" s="7"/>
       <c r="J4" s="8"/>
       <c r="K4" s="8"/>
@@ -38388,16 +38397,16 @@
       <c r="Z4" s="8"/>
     </row>
     <row r="5" spans="1:27" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="155" t="s">
+      <c r="A5" s="208" t="s">
         <v>126</v>
       </c>
-      <c r="B5" s="155"/>
-      <c r="C5" s="155"/>
-      <c r="D5" s="155"/>
-      <c r="E5" s="155"/>
-      <c r="F5" s="155"/>
-      <c r="G5" s="155"/>
-      <c r="H5" s="155"/>
+      <c r="B5" s="208"/>
+      <c r="C5" s="208"/>
+      <c r="D5" s="208"/>
+      <c r="E5" s="208"/>
+      <c r="F5" s="208"/>
+      <c r="G5" s="208"/>
+      <c r="H5" s="208"/>
       <c r="I5" s="7"/>
       <c r="J5" s="8"/>
       <c r="K5" s="8"/>
@@ -38418,14 +38427,14 @@
       <c r="Z5" s="8"/>
     </row>
     <row r="6" spans="1:27" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="157"/>
-      <c r="B6" s="157"/>
-      <c r="C6" s="157"/>
-      <c r="D6" s="157"/>
-      <c r="E6" s="157"/>
-      <c r="F6" s="157"/>
-      <c r="G6" s="157"/>
-      <c r="H6" s="157"/>
+      <c r="A6" s="210"/>
+      <c r="B6" s="210"/>
+      <c r="C6" s="210"/>
+      <c r="D6" s="210"/>
+      <c r="E6" s="210"/>
+      <c r="F6" s="210"/>
+      <c r="G6" s="210"/>
+      <c r="H6" s="210"/>
       <c r="J6" s="8"/>
       <c r="L6" s="8"/>
       <c r="M6" s="8"/>
@@ -38444,14 +38453,14 @@
       <c r="Z6" s="8"/>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A7" s="155"/>
-      <c r="B7" s="155"/>
-      <c r="C7" s="155"/>
-      <c r="D7" s="155"/>
-      <c r="E7" s="155"/>
-      <c r="F7" s="155"/>
-      <c r="G7" s="155"/>
-      <c r="H7" s="155"/>
+      <c r="A7" s="208"/>
+      <c r="B7" s="208"/>
+      <c r="C7" s="208"/>
+      <c r="D7" s="208"/>
+      <c r="E7" s="208"/>
+      <c r="F7" s="208"/>
+      <c r="G7" s="208"/>
+      <c r="H7" s="208"/>
       <c r="I7" s="7"/>
       <c r="J7" s="8"/>
       <c r="K7" s="8"/>
@@ -38472,16 +38481,16 @@
       <c r="Z7" s="8"/>
     </row>
     <row r="8" spans="1:27" ht="18" x14ac:dyDescent="0.25">
-      <c r="A8" s="156" t="s">
+      <c r="A8" s="209" t="s">
         <v>36</v>
       </c>
-      <c r="B8" s="158"/>
-      <c r="C8" s="158"/>
-      <c r="D8" s="158"/>
-      <c r="E8" s="158"/>
-      <c r="F8" s="158"/>
-      <c r="G8" s="158"/>
-      <c r="H8" s="158"/>
+      <c r="B8" s="211"/>
+      <c r="C8" s="211"/>
+      <c r="D8" s="211"/>
+      <c r="E8" s="211"/>
+      <c r="F8" s="211"/>
+      <c r="G8" s="211"/>
+      <c r="H8" s="211"/>
       <c r="I8" s="9"/>
       <c r="J8" s="10"/>
       <c r="K8" s="10"/>
@@ -38502,16 +38511,16 @@
       <c r="Z8" s="10"/>
     </row>
     <row r="9" spans="1:27" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="155" t="s">
+      <c r="A9" s="208" t="s">
         <v>106</v>
       </c>
-      <c r="B9" s="155"/>
-      <c r="C9" s="155"/>
-      <c r="D9" s="155"/>
-      <c r="E9" s="155"/>
-      <c r="F9" s="155"/>
-      <c r="G9" s="155"/>
-      <c r="H9" s="155"/>
+      <c r="B9" s="208"/>
+      <c r="C9" s="208"/>
+      <c r="D9" s="208"/>
+      <c r="E9" s="208"/>
+      <c r="F9" s="208"/>
+      <c r="G9" s="208"/>
+      <c r="H9" s="208"/>
       <c r="J9" s="8"/>
       <c r="K9" s="8"/>
       <c r="L9" s="8"/>
@@ -38531,16 +38540,16 @@
       <c r="Z9" s="8"/>
     </row>
     <row r="10" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="159" t="s">
+      <c r="A10" s="228" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="160"/>
-      <c r="C10" s="160"/>
-      <c r="D10" s="160"/>
-      <c r="E10" s="160"/>
-      <c r="F10" s="160"/>
-      <c r="G10" s="160"/>
-      <c r="H10" s="161"/>
+      <c r="B10" s="229"/>
+      <c r="C10" s="229"/>
+      <c r="D10" s="229"/>
+      <c r="E10" s="229"/>
+      <c r="F10" s="229"/>
+      <c r="G10" s="229"/>
+      <c r="H10" s="230"/>
       <c r="I10" s="7"/>
       <c r="J10" s="8"/>
       <c r="K10" s="8"/>
@@ -38561,22 +38570,22 @@
       <c r="Z10" s="8"/>
     </row>
     <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="147" t="s">
+      <c r="A11" s="155" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="148"/>
-      <c r="C11" s="149"/>
-      <c r="D11" s="151" t="s">
+      <c r="B11" s="231"/>
+      <c r="C11" s="232"/>
+      <c r="D11" s="156" t="s">
         <v>11</v>
       </c>
-      <c r="E11" s="148"/>
-      <c r="F11" s="148"/>
-      <c r="G11" s="148"/>
-      <c r="H11" s="162" t="s">
+      <c r="E11" s="231"/>
+      <c r="F11" s="231"/>
+      <c r="G11" s="231"/>
+      <c r="H11" s="234" t="s">
         <v>12</v>
       </c>
-      <c r="I11" s="162"/>
-      <c r="J11" s="162"/>
+      <c r="I11" s="234"/>
+      <c r="J11" s="234"/>
       <c r="K11" s="8"/>
       <c r="L11" s="8"/>
       <c r="M11" s="8"/>
@@ -38595,13 +38604,13 @@
       <c r="Z11" s="8"/>
     </row>
     <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="150"/>
-      <c r="B12" s="61"/>
-      <c r="C12" s="62"/>
-      <c r="D12" s="61"/>
-      <c r="E12" s="61"/>
-      <c r="F12" s="61"/>
-      <c r="G12" s="61"/>
+      <c r="A12" s="233"/>
+      <c r="B12" s="119"/>
+      <c r="C12" s="120"/>
+      <c r="D12" s="119"/>
+      <c r="E12" s="119"/>
+      <c r="F12" s="119"/>
+      <c r="G12" s="119"/>
       <c r="H12" s="49" t="s">
         <v>13</v>
       </c>
@@ -38629,18 +38638,18 @@
       <c r="Z12" s="8"/>
     </row>
     <row r="13" spans="1:27" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="107" t="s">
+      <c r="A13" s="121" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="110" t="s">
+      <c r="B13" s="88" t="s">
         <v>107</v>
       </c>
-      <c r="C13" s="111"/>
-      <c r="D13" s="112" t="s">
+      <c r="C13" s="89"/>
+      <c r="D13" s="90" t="s">
         <v>111</v>
       </c>
-      <c r="E13" s="102"/>
-      <c r="F13" s="103"/>
+      <c r="E13" s="80"/>
+      <c r="F13" s="79"/>
       <c r="G13" s="50" t="s">
         <v>25</v>
       </c>
@@ -38666,16 +38675,16 @@
       <c r="AA13" s="1"/>
     </row>
     <row r="14" spans="1:27" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="108"/>
-      <c r="B14" s="110" t="s">
+      <c r="A14" s="122"/>
+      <c r="B14" s="88" t="s">
         <v>108</v>
       </c>
-      <c r="C14" s="111"/>
-      <c r="D14" s="112" t="s">
+      <c r="C14" s="89"/>
+      <c r="D14" s="90" t="s">
         <v>112</v>
       </c>
-      <c r="E14" s="102"/>
-      <c r="F14" s="103"/>
+      <c r="E14" s="80"/>
+      <c r="F14" s="79"/>
       <c r="G14" s="50" t="s">
         <v>25</v>
       </c>
@@ -38701,16 +38710,16 @@
       <c r="AA14" s="1"/>
     </row>
     <row r="15" spans="1:27" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="108"/>
-      <c r="B15" s="113" t="s">
+      <c r="A15" s="122"/>
+      <c r="B15" s="235" t="s">
         <v>109</v>
       </c>
-      <c r="C15" s="114"/>
-      <c r="D15" s="101" t="s">
+      <c r="C15" s="236"/>
+      <c r="D15" s="91" t="s">
         <v>113</v>
       </c>
-      <c r="E15" s="102"/>
-      <c r="F15" s="103"/>
+      <c r="E15" s="80"/>
+      <c r="F15" s="79"/>
       <c r="G15" s="50" t="s">
         <v>25</v>
       </c>
@@ -38736,16 +38745,16 @@
       <c r="AA15" s="1"/>
     </row>
     <row r="16" spans="1:27" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="108"/>
-      <c r="B16" s="78" t="s">
+      <c r="A16" s="122"/>
+      <c r="B16" s="92" t="s">
         <v>110</v>
       </c>
-      <c r="C16" s="79"/>
-      <c r="D16" s="115" t="s">
+      <c r="C16" s="93"/>
+      <c r="D16" s="94" t="s">
         <v>115</v>
       </c>
-      <c r="E16" s="116"/>
-      <c r="F16" s="117"/>
+      <c r="E16" s="95"/>
+      <c r="F16" s="96"/>
       <c r="G16" s="50" t="s">
         <v>25</v>
       </c>
@@ -38771,16 +38780,16 @@
       <c r="AA16" s="1"/>
     </row>
     <row r="17" spans="1:27" ht="50.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="108"/>
-      <c r="B17" s="78" t="s">
+      <c r="A17" s="122"/>
+      <c r="B17" s="92" t="s">
         <v>67</v>
       </c>
-      <c r="C17" s="79"/>
-      <c r="D17" s="96" t="s">
+      <c r="C17" s="93"/>
+      <c r="D17" s="108" t="s">
         <v>116</v>
       </c>
-      <c r="E17" s="97"/>
-      <c r="F17" s="98"/>
+      <c r="E17" s="109"/>
+      <c r="F17" s="110"/>
       <c r="G17" s="50" t="s">
         <v>25</v>
       </c>
@@ -38806,16 +38815,16 @@
       <c r="AA17" s="1"/>
     </row>
     <row r="18" spans="1:27" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="109"/>
-      <c r="B18" s="99" t="s">
+      <c r="A18" s="123"/>
+      <c r="B18" s="111" t="s">
         <v>88</v>
       </c>
-      <c r="C18" s="100"/>
-      <c r="D18" s="101" t="s">
+      <c r="C18" s="112"/>
+      <c r="D18" s="91" t="s">
         <v>114</v>
       </c>
-      <c r="E18" s="102"/>
-      <c r="F18" s="103"/>
+      <c r="E18" s="80"/>
+      <c r="F18" s="79"/>
       <c r="G18" s="50" t="s">
         <v>25</v>
       </c>
@@ -38841,18 +38850,18 @@
       <c r="AA18" s="1"/>
     </row>
     <row r="19" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="104" t="s">
+      <c r="A19" s="113" t="s">
         <v>33</v>
       </c>
-      <c r="B19" s="72" t="s">
+      <c r="B19" s="116" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="73"/>
-      <c r="D19" s="71" t="s">
+      <c r="C19" s="117"/>
+      <c r="D19" s="118" t="s">
         <v>120</v>
       </c>
-      <c r="E19" s="61"/>
-      <c r="F19" s="62"/>
+      <c r="E19" s="119"/>
+      <c r="F19" s="120"/>
       <c r="G19" s="50" t="s">
         <v>25</v>
       </c>
@@ -38878,16 +38887,16 @@
       <c r="AA19" s="1"/>
     </row>
     <row r="20" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="105"/>
-      <c r="B20" s="72" t="s">
+      <c r="A20" s="114"/>
+      <c r="B20" s="116" t="s">
         <v>117</v>
       </c>
-      <c r="C20" s="73"/>
-      <c r="D20" s="71" t="s">
+      <c r="C20" s="117"/>
+      <c r="D20" s="118" t="s">
         <v>118</v>
       </c>
-      <c r="E20" s="61"/>
-      <c r="F20" s="62"/>
+      <c r="E20" s="119"/>
+      <c r="F20" s="120"/>
       <c r="G20" s="50" t="s">
         <v>25</v>
       </c>
@@ -38913,16 +38922,16 @@
       <c r="AA20" s="1"/>
     </row>
     <row r="21" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="105"/>
-      <c r="B21" s="72" t="s">
+      <c r="A21" s="114"/>
+      <c r="B21" s="116" t="s">
         <v>48</v>
       </c>
-      <c r="C21" s="73"/>
-      <c r="D21" s="71" t="s">
+      <c r="C21" s="117"/>
+      <c r="D21" s="118" t="s">
         <v>119</v>
       </c>
-      <c r="E21" s="61"/>
-      <c r="F21" s="62"/>
+      <c r="E21" s="119"/>
+      <c r="F21" s="120"/>
       <c r="G21" s="50" t="s">
         <v>25</v>
       </c>
@@ -38948,16 +38957,16 @@
       <c r="AA21" s="1"/>
     </row>
     <row r="22" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="106"/>
-      <c r="B22" s="72" t="s">
+      <c r="A22" s="115"/>
+      <c r="B22" s="116" t="s">
         <v>15</v>
       </c>
-      <c r="C22" s="73"/>
-      <c r="D22" s="71" t="s">
+      <c r="C22" s="117"/>
+      <c r="D22" s="118" t="s">
         <v>121</v>
       </c>
-      <c r="E22" s="61"/>
-      <c r="F22" s="62"/>
+      <c r="E22" s="119"/>
+      <c r="F22" s="120"/>
       <c r="G22" s="50" t="s">
         <v>25</v>
       </c>
@@ -39011,18 +39020,18 @@
       <c r="Z23" s="8"/>
     </row>
     <row r="24" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="91" t="s">
+      <c r="A24" s="103" t="s">
         <v>16</v>
       </c>
-      <c r="B24" s="92"/>
-      <c r="C24" s="92"/>
-      <c r="D24" s="92"/>
-      <c r="E24" s="93"/>
-      <c r="F24" s="94" t="s">
+      <c r="B24" s="104"/>
+      <c r="C24" s="104"/>
+      <c r="D24" s="104"/>
+      <c r="E24" s="105"/>
+      <c r="F24" s="106" t="s">
         <v>17</v>
       </c>
-      <c r="G24" s="92"/>
-      <c r="H24" s="93"/>
+      <c r="G24" s="104"/>
+      <c r="H24" s="105"/>
       <c r="I24" s="7"/>
       <c r="J24" s="8"/>
       <c r="K24" s="8"/>
@@ -39046,17 +39055,17 @@
       <c r="A25" s="13">
         <v>5</v>
       </c>
-      <c r="B25" s="60" t="s">
+      <c r="B25" s="126" t="s">
         <v>18</v>
       </c>
-      <c r="C25" s="61"/>
-      <c r="D25" s="61"/>
-      <c r="E25" s="62"/>
-      <c r="F25" s="63">
+      <c r="C25" s="119"/>
+      <c r="D25" s="119"/>
+      <c r="E25" s="120"/>
+      <c r="F25" s="125">
         <v>100</v>
       </c>
-      <c r="G25" s="61"/>
-      <c r="H25" s="62"/>
+      <c r="G25" s="119"/>
+      <c r="H25" s="120"/>
       <c r="I25" s="7"/>
       <c r="J25" s="8"/>
       <c r="K25" s="8"/>
@@ -39080,17 +39089,17 @@
       <c r="A26" s="13">
         <v>4</v>
       </c>
-      <c r="B26" s="90" t="s">
+      <c r="B26" s="127" t="s">
         <v>50</v>
       </c>
-      <c r="C26" s="61"/>
-      <c r="D26" s="61"/>
-      <c r="E26" s="62"/>
-      <c r="F26" s="63">
+      <c r="C26" s="119"/>
+      <c r="D26" s="119"/>
+      <c r="E26" s="120"/>
+      <c r="F26" s="125">
         <v>80</v>
       </c>
-      <c r="G26" s="61"/>
-      <c r="H26" s="62"/>
+      <c r="G26" s="119"/>
+      <c r="H26" s="120"/>
       <c r="I26" s="7"/>
       <c r="J26" s="8"/>
       <c r="K26" s="8"/>
@@ -39114,17 +39123,17 @@
       <c r="A27" s="13">
         <v>3</v>
       </c>
-      <c r="B27" s="90" t="s">
+      <c r="B27" s="127" t="s">
         <v>49</v>
       </c>
-      <c r="C27" s="61"/>
-      <c r="D27" s="61"/>
-      <c r="E27" s="62"/>
-      <c r="F27" s="63">
+      <c r="C27" s="119"/>
+      <c r="D27" s="119"/>
+      <c r="E27" s="120"/>
+      <c r="F27" s="125">
         <v>65</v>
       </c>
-      <c r="G27" s="61"/>
-      <c r="H27" s="62"/>
+      <c r="G27" s="119"/>
+      <c r="H27" s="120"/>
       <c r="I27" s="7"/>
       <c r="J27" s="8"/>
       <c r="K27" s="8"/>
@@ -39148,17 +39157,17 @@
       <c r="A28" s="13">
         <v>2</v>
       </c>
-      <c r="B28" s="89" t="s">
+      <c r="B28" s="124" t="s">
         <v>19</v>
       </c>
-      <c r="C28" s="61"/>
-      <c r="D28" s="61"/>
-      <c r="E28" s="62"/>
-      <c r="F28" s="63">
+      <c r="C28" s="119"/>
+      <c r="D28" s="119"/>
+      <c r="E28" s="120"/>
+      <c r="F28" s="125">
         <v>50</v>
       </c>
-      <c r="G28" s="61"/>
-      <c r="H28" s="62"/>
+      <c r="G28" s="119"/>
+      <c r="H28" s="120"/>
       <c r="I28" s="7"/>
       <c r="J28" s="8"/>
       <c r="K28" s="8"/>
@@ -39182,17 +39191,17 @@
       <c r="A29" s="13">
         <v>1</v>
       </c>
-      <c r="B29" s="60" t="s">
+      <c r="B29" s="126" t="s">
         <v>20</v>
       </c>
-      <c r="C29" s="61"/>
-      <c r="D29" s="61"/>
-      <c r="E29" s="62"/>
-      <c r="F29" s="63">
+      <c r="C29" s="119"/>
+      <c r="D29" s="119"/>
+      <c r="E29" s="120"/>
+      <c r="F29" s="125">
         <v>30</v>
       </c>
-      <c r="G29" s="61"/>
-      <c r="H29" s="62"/>
+      <c r="G29" s="119"/>
+      <c r="H29" s="120"/>
       <c r="I29" s="7"/>
       <c r="J29" s="8"/>
       <c r="K29" s="8"/>
@@ -39281,16 +39290,16 @@
       <c r="D32" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="E32" s="163">
+      <c r="E32" s="237">
         <v>1</v>
       </c>
-      <c r="F32" s="163">
+      <c r="F32" s="237">
         <v>0</v>
       </c>
-      <c r="G32" s="164" t="s">
+      <c r="G32" s="196" t="s">
         <v>25</v>
       </c>
-      <c r="H32" s="166" t="s">
+      <c r="H32" s="198" t="s">
         <v>26</v>
       </c>
       <c r="I32" s="7"/>
@@ -39319,10 +39328,10 @@
       <c r="D33" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="E33" s="62"/>
-      <c r="F33" s="62"/>
-      <c r="G33" s="165"/>
-      <c r="H33" s="167"/>
+      <c r="E33" s="120"/>
+      <c r="F33" s="120"/>
+      <c r="G33" s="197"/>
+      <c r="H33" s="199"/>
       <c r="I33" s="7"/>
       <c r="J33" s="8"/>
       <c r="K33" s="8"/>
@@ -45172,24 +45181,23 @@
     <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="51">
-    <mergeCell ref="A6:H6"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="A10:H10"/>
-    <mergeCell ref="A11:C12"/>
-    <mergeCell ref="D11:G12"/>
-    <mergeCell ref="H11:J11"/>
-    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="G32:G33"/>
+    <mergeCell ref="H32:H33"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="B27:E27"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="F25:H25"/>
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="D18:F18"/>
     <mergeCell ref="A19:A22"/>
@@ -45206,23 +45214,24 @@
     <mergeCell ref="D14:F14"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="A24:E24"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="B25:E25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="B26:E26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="B27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="B28:E28"/>
-    <mergeCell ref="F28:H28"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="F29:H29"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="F32:F33"/>
-    <mergeCell ref="G32:G33"/>
-    <mergeCell ref="H32:H33"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A11:C12"/>
+    <mergeCell ref="D11:G12"/>
+    <mergeCell ref="H11:J11"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="A6:H6"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A5:H5"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
@@ -45249,16 +45258,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="144" t="s">
+      <c r="A1" s="202" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="145"/>
-      <c r="C1" s="145"/>
-      <c r="D1" s="145"/>
-      <c r="E1" s="145"/>
-      <c r="F1" s="145"/>
-      <c r="G1" s="145"/>
-      <c r="H1" s="146"/>
+      <c r="B1" s="203"/>
+      <c r="C1" s="203"/>
+      <c r="D1" s="203"/>
+      <c r="E1" s="203"/>
+      <c r="F1" s="203"/>
+      <c r="G1" s="203"/>
+      <c r="H1" s="204"/>
       <c r="I1" s="7"/>
       <c r="J1" s="8"/>
       <c r="K1" s="8"/>
@@ -45279,16 +45288,16 @@
       <c r="Z1" s="8"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="152" t="s">
+      <c r="A2" s="205" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="153"/>
-      <c r="C2" s="153"/>
-      <c r="D2" s="153"/>
-      <c r="E2" s="153"/>
-      <c r="F2" s="153"/>
-      <c r="G2" s="153"/>
-      <c r="H2" s="154"/>
+      <c r="B2" s="206"/>
+      <c r="C2" s="206"/>
+      <c r="D2" s="206"/>
+      <c r="E2" s="206"/>
+      <c r="F2" s="206"/>
+      <c r="G2" s="206"/>
+      <c r="H2" s="207"/>
       <c r="I2" s="7"/>
       <c r="J2" s="8"/>
       <c r="K2" s="8"/>
@@ -45309,16 +45318,16 @@
       <c r="Z2" s="8"/>
     </row>
     <row r="3" spans="1:26" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="155" t="s">
+      <c r="A3" s="208" t="s">
         <v>127</v>
       </c>
-      <c r="B3" s="155"/>
-      <c r="C3" s="155"/>
-      <c r="D3" s="155"/>
-      <c r="E3" s="155"/>
-      <c r="F3" s="155"/>
-      <c r="G3" s="155"/>
-      <c r="H3" s="155"/>
+      <c r="B3" s="208"/>
+      <c r="C3" s="208"/>
+      <c r="D3" s="208"/>
+      <c r="E3" s="208"/>
+      <c r="F3" s="208"/>
+      <c r="G3" s="208"/>
+      <c r="H3" s="208"/>
       <c r="I3" s="7"/>
       <c r="J3" s="8"/>
       <c r="K3" s="8"/>
@@ -45339,16 +45348,16 @@
       <c r="Z3" s="8"/>
     </row>
     <row r="4" spans="1:26" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="156" t="s">
+      <c r="A4" s="209" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="156"/>
-      <c r="C4" s="156"/>
-      <c r="D4" s="156"/>
-      <c r="E4" s="156"/>
-      <c r="F4" s="156"/>
-      <c r="G4" s="156"/>
-      <c r="H4" s="156"/>
+      <c r="B4" s="209"/>
+      <c r="C4" s="209"/>
+      <c r="D4" s="209"/>
+      <c r="E4" s="209"/>
+      <c r="F4" s="209"/>
+      <c r="G4" s="209"/>
+      <c r="H4" s="209"/>
       <c r="I4" s="7"/>
       <c r="J4" s="8"/>
       <c r="K4" s="8"/>
@@ -45369,16 +45378,16 @@
       <c r="Z4" s="8"/>
     </row>
     <row r="5" spans="1:26" ht="135" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="155" t="s">
+      <c r="A5" s="208" t="s">
         <v>128</v>
       </c>
-      <c r="B5" s="155"/>
-      <c r="C5" s="155"/>
-      <c r="D5" s="155"/>
-      <c r="E5" s="155"/>
-      <c r="F5" s="155"/>
-      <c r="G5" s="155"/>
-      <c r="H5" s="155"/>
+      <c r="B5" s="208"/>
+      <c r="C5" s="208"/>
+      <c r="D5" s="208"/>
+      <c r="E5" s="208"/>
+      <c r="F5" s="208"/>
+      <c r="G5" s="208"/>
+      <c r="H5" s="208"/>
       <c r="I5" s="7"/>
       <c r="J5" s="8"/>
       <c r="K5" s="8"/>
@@ -45399,14 +45408,14 @@
       <c r="Z5" s="8"/>
     </row>
     <row r="6" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="157"/>
-      <c r="B6" s="157"/>
-      <c r="C6" s="157"/>
-      <c r="D6" s="157"/>
-      <c r="E6" s="157"/>
-      <c r="F6" s="157"/>
-      <c r="G6" s="157"/>
-      <c r="H6" s="157"/>
+      <c r="A6" s="210"/>
+      <c r="B6" s="210"/>
+      <c r="C6" s="210"/>
+      <c r="D6" s="210"/>
+      <c r="E6" s="210"/>
+      <c r="F6" s="210"/>
+      <c r="G6" s="210"/>
+      <c r="H6" s="210"/>
       <c r="J6" s="8"/>
       <c r="K6" s="8"/>
       <c r="L6" s="8"/>
@@ -45426,16 +45435,16 @@
       <c r="Z6" s="8"/>
     </row>
     <row r="7" spans="1:26" ht="192" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="155" t="s">
+      <c r="A7" s="208" t="s">
         <v>129</v>
       </c>
-      <c r="B7" s="155"/>
-      <c r="C7" s="155"/>
-      <c r="D7" s="155"/>
-      <c r="E7" s="155"/>
-      <c r="F7" s="155"/>
-      <c r="G7" s="155"/>
-      <c r="H7" s="155"/>
+      <c r="B7" s="208"/>
+      <c r="C7" s="208"/>
+      <c r="D7" s="208"/>
+      <c r="E7" s="208"/>
+      <c r="F7" s="208"/>
+      <c r="G7" s="208"/>
+      <c r="H7" s="208"/>
       <c r="J7" s="8"/>
       <c r="K7" s="8"/>
       <c r="L7" s="8"/>
@@ -45455,14 +45464,14 @@
       <c r="Z7" s="8"/>
     </row>
     <row r="8" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="155"/>
-      <c r="B8" s="155"/>
-      <c r="C8" s="155"/>
-      <c r="D8" s="155"/>
-      <c r="E8" s="155"/>
-      <c r="F8" s="155"/>
-      <c r="G8" s="155"/>
-      <c r="H8" s="155"/>
+      <c r="A8" s="208"/>
+      <c r="B8" s="208"/>
+      <c r="C8" s="208"/>
+      <c r="D8" s="208"/>
+      <c r="E8" s="208"/>
+      <c r="F8" s="208"/>
+      <c r="G8" s="208"/>
+      <c r="H8" s="208"/>
       <c r="J8" s="8"/>
       <c r="K8" s="8"/>
       <c r="L8" s="8"/>
@@ -45482,16 +45491,16 @@
       <c r="Z8" s="8"/>
     </row>
     <row r="9" spans="1:26" ht="365.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="155" t="s">
+      <c r="A9" s="208" t="s">
         <v>130</v>
       </c>
-      <c r="B9" s="155"/>
-      <c r="C9" s="155"/>
-      <c r="D9" s="155"/>
-      <c r="E9" s="155"/>
-      <c r="F9" s="155"/>
-      <c r="G9" s="155"/>
-      <c r="H9" s="155"/>
+      <c r="B9" s="208"/>
+      <c r="C9" s="208"/>
+      <c r="D9" s="208"/>
+      <c r="E9" s="208"/>
+      <c r="F9" s="208"/>
+      <c r="G9" s="208"/>
+      <c r="H9" s="208"/>
       <c r="I9" s="7"/>
       <c r="J9" s="8"/>
       <c r="K9" s="8"/>
@@ -45512,14 +45521,14 @@
       <c r="Z9" s="8"/>
     </row>
     <row r="10" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="168"/>
-      <c r="B10" s="169"/>
-      <c r="C10" s="169"/>
-      <c r="D10" s="169"/>
-      <c r="E10" s="169"/>
-      <c r="F10" s="169"/>
-      <c r="G10" s="169"/>
-      <c r="H10" s="170"/>
+      <c r="A10" s="238"/>
+      <c r="B10" s="239"/>
+      <c r="C10" s="239"/>
+      <c r="D10" s="239"/>
+      <c r="E10" s="239"/>
+      <c r="F10" s="239"/>
+      <c r="G10" s="239"/>
+      <c r="H10" s="240"/>
       <c r="J10" s="8"/>
       <c r="K10" s="8"/>
       <c r="L10" s="8"/>
@@ -45539,16 +45548,16 @@
       <c r="Z10" s="8"/>
     </row>
     <row r="11" spans="1:26" ht="240.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="171" t="s">
+      <c r="A11" s="241" t="s">
         <v>131</v>
       </c>
-      <c r="B11" s="172"/>
-      <c r="C11" s="172"/>
-      <c r="D11" s="172"/>
-      <c r="E11" s="172"/>
-      <c r="F11" s="172"/>
-      <c r="G11" s="172"/>
-      <c r="H11" s="173"/>
+      <c r="B11" s="242"/>
+      <c r="C11" s="242"/>
+      <c r="D11" s="242"/>
+      <c r="E11" s="242"/>
+      <c r="F11" s="242"/>
+      <c r="G11" s="242"/>
+      <c r="H11" s="243"/>
       <c r="I11" s="7"/>
       <c r="J11" s="8"/>
       <c r="K11" s="8"/>
@@ -45569,16 +45578,16 @@
       <c r="Z11" s="8"/>
     </row>
     <row r="12" spans="1:26" ht="18" x14ac:dyDescent="0.25">
-      <c r="A12" s="156" t="s">
+      <c r="A12" s="209" t="s">
         <v>36</v>
       </c>
-      <c r="B12" s="158"/>
-      <c r="C12" s="158"/>
-      <c r="D12" s="158"/>
-      <c r="E12" s="158"/>
-      <c r="F12" s="158"/>
-      <c r="G12" s="158"/>
-      <c r="H12" s="158"/>
+      <c r="B12" s="211"/>
+      <c r="C12" s="211"/>
+      <c r="D12" s="211"/>
+      <c r="E12" s="211"/>
+      <c r="F12" s="211"/>
+      <c r="G12" s="211"/>
+      <c r="H12" s="211"/>
       <c r="I12" s="9"/>
       <c r="J12" s="10"/>
       <c r="K12" s="10"/>
@@ -45599,16 +45608,16 @@
       <c r="Z12" s="10"/>
     </row>
     <row r="13" spans="1:26" ht="246" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="155" t="s">
+      <c r="A13" s="208" t="s">
         <v>132</v>
       </c>
-      <c r="B13" s="155"/>
-      <c r="C13" s="155"/>
-      <c r="D13" s="155"/>
-      <c r="E13" s="155"/>
-      <c r="F13" s="155"/>
-      <c r="G13" s="155"/>
-      <c r="H13" s="155"/>
+      <c r="B13" s="208"/>
+      <c r="C13" s="208"/>
+      <c r="D13" s="208"/>
+      <c r="E13" s="208"/>
+      <c r="F13" s="208"/>
+      <c r="G13" s="208"/>
+      <c r="H13" s="208"/>
       <c r="J13" s="8"/>
       <c r="K13" s="8"/>
       <c r="L13" s="8"/>
@@ -45628,16 +45637,16 @@
       <c r="Z13" s="8"/>
     </row>
     <row r="14" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="159" t="s">
+      <c r="A14" s="228" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="160"/>
-      <c r="C14" s="160"/>
-      <c r="D14" s="160"/>
-      <c r="E14" s="160"/>
-      <c r="F14" s="160"/>
-      <c r="G14" s="160"/>
-      <c r="H14" s="161"/>
+      <c r="B14" s="229"/>
+      <c r="C14" s="229"/>
+      <c r="D14" s="229"/>
+      <c r="E14" s="229"/>
+      <c r="F14" s="229"/>
+      <c r="G14" s="229"/>
+      <c r="H14" s="230"/>
       <c r="I14" s="7"/>
       <c r="J14" s="8"/>
       <c r="K14" s="8"/>
@@ -45658,22 +45667,22 @@
       <c r="Z14" s="8"/>
     </row>
     <row r="15" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="147" t="s">
+      <c r="A15" s="155" t="s">
         <v>10</v>
       </c>
-      <c r="B15" s="148"/>
-      <c r="C15" s="149"/>
-      <c r="D15" s="151" t="s">
+      <c r="B15" s="231"/>
+      <c r="C15" s="232"/>
+      <c r="D15" s="156" t="s">
         <v>11</v>
       </c>
-      <c r="E15" s="148"/>
-      <c r="F15" s="148"/>
-      <c r="G15" s="148"/>
-      <c r="H15" s="162" t="s">
+      <c r="E15" s="231"/>
+      <c r="F15" s="231"/>
+      <c r="G15" s="231"/>
+      <c r="H15" s="234" t="s">
         <v>12</v>
       </c>
-      <c r="I15" s="162"/>
-      <c r="J15" s="162"/>
+      <c r="I15" s="234"/>
+      <c r="J15" s="234"/>
       <c r="K15" s="8"/>
       <c r="L15" s="8"/>
       <c r="M15" s="8"/>
@@ -45692,13 +45701,13 @@
       <c r="Z15" s="8"/>
     </row>
     <row r="16" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="150"/>
-      <c r="B16" s="61"/>
-      <c r="C16" s="62"/>
-      <c r="D16" s="61"/>
-      <c r="E16" s="61"/>
-      <c r="F16" s="61"/>
-      <c r="G16" s="61"/>
+      <c r="A16" s="233"/>
+      <c r="B16" s="119"/>
+      <c r="C16" s="120"/>
+      <c r="D16" s="119"/>
+      <c r="E16" s="119"/>
+      <c r="F16" s="119"/>
+      <c r="G16" s="119"/>
       <c r="H16" s="49" t="s">
         <v>13</v>
       </c>
@@ -45726,18 +45735,18 @@
       <c r="Z16" s="8"/>
     </row>
     <row r="17" spans="1:27" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="107" t="s">
+      <c r="A17" s="121" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="110" t="s">
+      <c r="B17" s="88" t="s">
         <v>107</v>
       </c>
-      <c r="C17" s="111"/>
-      <c r="D17" s="112" t="s">
+      <c r="C17" s="89"/>
+      <c r="D17" s="90" t="s">
         <v>111</v>
       </c>
-      <c r="E17" s="102"/>
-      <c r="F17" s="103"/>
+      <c r="E17" s="80"/>
+      <c r="F17" s="79"/>
       <c r="G17" s="50" t="s">
         <v>25</v>
       </c>
@@ -45763,16 +45772,16 @@
       <c r="AA17" s="1"/>
     </row>
     <row r="18" spans="1:27" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="108"/>
-      <c r="B18" s="110" t="s">
+      <c r="A18" s="122"/>
+      <c r="B18" s="88" t="s">
         <v>108</v>
       </c>
-      <c r="C18" s="111"/>
-      <c r="D18" s="112" t="s">
+      <c r="C18" s="89"/>
+      <c r="D18" s="90" t="s">
         <v>112</v>
       </c>
-      <c r="E18" s="102"/>
-      <c r="F18" s="103"/>
+      <c r="E18" s="80"/>
+      <c r="F18" s="79"/>
       <c r="G18" s="50" t="s">
         <v>25</v>
       </c>
@@ -45798,16 +45807,16 @@
       <c r="AA18" s="1"/>
     </row>
     <row r="19" spans="1:27" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="108"/>
-      <c r="B19" s="113" t="s">
+      <c r="A19" s="122"/>
+      <c r="B19" s="235" t="s">
         <v>109</v>
       </c>
-      <c r="C19" s="114"/>
-      <c r="D19" s="101" t="s">
+      <c r="C19" s="236"/>
+      <c r="D19" s="91" t="s">
         <v>113</v>
       </c>
-      <c r="E19" s="102"/>
-      <c r="F19" s="103"/>
+      <c r="E19" s="80"/>
+      <c r="F19" s="79"/>
       <c r="G19" s="50" t="s">
         <v>25</v>
       </c>
@@ -45833,16 +45842,16 @@
       <c r="AA19" s="1"/>
     </row>
     <row r="20" spans="1:27" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="108"/>
-      <c r="B20" s="78" t="s">
+      <c r="A20" s="122"/>
+      <c r="B20" s="92" t="s">
         <v>110</v>
       </c>
-      <c r="C20" s="79"/>
-      <c r="D20" s="115" t="s">
+      <c r="C20" s="93"/>
+      <c r="D20" s="94" t="s">
         <v>140</v>
       </c>
-      <c r="E20" s="116"/>
-      <c r="F20" s="117"/>
+      <c r="E20" s="95"/>
+      <c r="F20" s="96"/>
       <c r="G20" s="50" t="s">
         <v>25</v>
       </c>
@@ -45868,16 +45877,16 @@
       <c r="AA20" s="1"/>
     </row>
     <row r="21" spans="1:27" ht="50.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="108"/>
-      <c r="B21" s="78" t="s">
+      <c r="A21" s="122"/>
+      <c r="B21" s="92" t="s">
         <v>67</v>
       </c>
-      <c r="C21" s="79"/>
-      <c r="D21" s="96" t="s">
+      <c r="C21" s="93"/>
+      <c r="D21" s="108" t="s">
         <v>116</v>
       </c>
-      <c r="E21" s="97"/>
-      <c r="F21" s="98"/>
+      <c r="E21" s="109"/>
+      <c r="F21" s="110"/>
       <c r="G21" s="50" t="s">
         <v>25</v>
       </c>
@@ -45903,16 +45912,16 @@
       <c r="AA21" s="1"/>
     </row>
     <row r="22" spans="1:27" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="109"/>
-      <c r="B22" s="99" t="s">
+      <c r="A22" s="123"/>
+      <c r="B22" s="111" t="s">
         <v>88</v>
       </c>
-      <c r="C22" s="100"/>
-      <c r="D22" s="101" t="s">
+      <c r="C22" s="112"/>
+      <c r="D22" s="91" t="s">
         <v>114</v>
       </c>
-      <c r="E22" s="102"/>
-      <c r="F22" s="103"/>
+      <c r="E22" s="80"/>
+      <c r="F22" s="79"/>
       <c r="G22" s="50" t="s">
         <v>25</v>
       </c>
@@ -45938,18 +45947,18 @@
       <c r="AA22" s="1"/>
     </row>
     <row r="23" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="104" t="s">
+      <c r="A23" s="113" t="s">
         <v>33</v>
       </c>
-      <c r="B23" s="72" t="s">
+      <c r="B23" s="116" t="s">
         <v>47</v>
       </c>
-      <c r="C23" s="73"/>
-      <c r="D23" s="71" t="s">
+      <c r="C23" s="117"/>
+      <c r="D23" s="118" t="s">
         <v>120</v>
       </c>
-      <c r="E23" s="61"/>
-      <c r="F23" s="62"/>
+      <c r="E23" s="119"/>
+      <c r="F23" s="120"/>
       <c r="G23" s="50" t="s">
         <v>25</v>
       </c>
@@ -45975,16 +45984,16 @@
       <c r="AA23" s="1"/>
     </row>
     <row r="24" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="105"/>
-      <c r="B24" s="72" t="s">
+      <c r="A24" s="114"/>
+      <c r="B24" s="116" t="s">
         <v>117</v>
       </c>
-      <c r="C24" s="73"/>
-      <c r="D24" s="71" t="s">
+      <c r="C24" s="117"/>
+      <c r="D24" s="118" t="s">
         <v>118</v>
       </c>
-      <c r="E24" s="61"/>
-      <c r="F24" s="62"/>
+      <c r="E24" s="119"/>
+      <c r="F24" s="120"/>
       <c r="G24" s="50" t="s">
         <v>25</v>
       </c>
@@ -46010,16 +46019,16 @@
       <c r="AA24" s="1"/>
     </row>
     <row r="25" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="105"/>
-      <c r="B25" s="72" t="s">
+      <c r="A25" s="114"/>
+      <c r="B25" s="116" t="s">
         <v>48</v>
       </c>
-      <c r="C25" s="73"/>
-      <c r="D25" s="71" t="s">
+      <c r="C25" s="117"/>
+      <c r="D25" s="118" t="s">
         <v>119</v>
       </c>
-      <c r="E25" s="61"/>
-      <c r="F25" s="62"/>
+      <c r="E25" s="119"/>
+      <c r="F25" s="120"/>
       <c r="G25" s="50" t="s">
         <v>25</v>
       </c>
@@ -46045,16 +46054,16 @@
       <c r="AA25" s="1"/>
     </row>
     <row r="26" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="106"/>
-      <c r="B26" s="72" t="s">
+      <c r="A26" s="115"/>
+      <c r="B26" s="116" t="s">
         <v>15</v>
       </c>
-      <c r="C26" s="73"/>
-      <c r="D26" s="71" t="s">
+      <c r="C26" s="117"/>
+      <c r="D26" s="118" t="s">
         <v>121</v>
       </c>
-      <c r="E26" s="61"/>
-      <c r="F26" s="62"/>
+      <c r="E26" s="119"/>
+      <c r="F26" s="120"/>
       <c r="G26" s="50" t="s">
         <v>25</v>
       </c>
@@ -46108,18 +46117,18 @@
       <c r="Z27" s="8"/>
     </row>
     <row r="28" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="91" t="s">
+      <c r="A28" s="103" t="s">
         <v>16</v>
       </c>
-      <c r="B28" s="92"/>
-      <c r="C28" s="92"/>
-      <c r="D28" s="92"/>
-      <c r="E28" s="93"/>
-      <c r="F28" s="94" t="s">
+      <c r="B28" s="104"/>
+      <c r="C28" s="104"/>
+      <c r="D28" s="104"/>
+      <c r="E28" s="105"/>
+      <c r="F28" s="106" t="s">
         <v>17</v>
       </c>
-      <c r="G28" s="92"/>
-      <c r="H28" s="93"/>
+      <c r="G28" s="104"/>
+      <c r="H28" s="105"/>
       <c r="I28" s="7"/>
       <c r="J28" s="8"/>
       <c r="K28" s="8"/>
@@ -46143,17 +46152,17 @@
       <c r="A29" s="13">
         <v>5</v>
       </c>
-      <c r="B29" s="60" t="s">
+      <c r="B29" s="126" t="s">
         <v>18</v>
       </c>
-      <c r="C29" s="61"/>
-      <c r="D29" s="61"/>
-      <c r="E29" s="62"/>
-      <c r="F29" s="63">
+      <c r="C29" s="119"/>
+      <c r="D29" s="119"/>
+      <c r="E29" s="120"/>
+      <c r="F29" s="125">
         <v>100</v>
       </c>
-      <c r="G29" s="61"/>
-      <c r="H29" s="62"/>
+      <c r="G29" s="119"/>
+      <c r="H29" s="120"/>
       <c r="I29" s="7"/>
       <c r="J29" s="8"/>
       <c r="K29" s="8"/>
@@ -46177,17 +46186,17 @@
       <c r="A30" s="13">
         <v>5</v>
       </c>
-      <c r="B30" s="90" t="s">
+      <c r="B30" s="127" t="s">
         <v>139</v>
       </c>
-      <c r="C30" s="61"/>
-      <c r="D30" s="61"/>
-      <c r="E30" s="62"/>
-      <c r="F30" s="63">
+      <c r="C30" s="119"/>
+      <c r="D30" s="119"/>
+      <c r="E30" s="120"/>
+      <c r="F30" s="125">
         <v>80</v>
       </c>
-      <c r="G30" s="61"/>
-      <c r="H30" s="62"/>
+      <c r="G30" s="119"/>
+      <c r="H30" s="120"/>
       <c r="I30" s="7"/>
       <c r="J30" s="8"/>
       <c r="K30" s="8"/>
@@ -46211,17 +46220,17 @@
       <c r="A31" s="13">
         <v>4</v>
       </c>
-      <c r="B31" s="90" t="s">
+      <c r="B31" s="127" t="s">
         <v>50</v>
       </c>
-      <c r="C31" s="61"/>
-      <c r="D31" s="61"/>
-      <c r="E31" s="62"/>
-      <c r="F31" s="63">
+      <c r="C31" s="119"/>
+      <c r="D31" s="119"/>
+      <c r="E31" s="120"/>
+      <c r="F31" s="125">
         <v>70</v>
       </c>
-      <c r="G31" s="61"/>
-      <c r="H31" s="62"/>
+      <c r="G31" s="119"/>
+      <c r="H31" s="120"/>
       <c r="I31" s="7"/>
       <c r="J31" s="8"/>
       <c r="K31" s="8"/>
@@ -46245,17 +46254,17 @@
       <c r="A32" s="13">
         <v>3</v>
       </c>
-      <c r="B32" s="90" t="s">
+      <c r="B32" s="127" t="s">
         <v>49</v>
       </c>
-      <c r="C32" s="61"/>
-      <c r="D32" s="61"/>
-      <c r="E32" s="62"/>
-      <c r="F32" s="63">
+      <c r="C32" s="119"/>
+      <c r="D32" s="119"/>
+      <c r="E32" s="120"/>
+      <c r="F32" s="125">
         <v>65</v>
       </c>
-      <c r="G32" s="61"/>
-      <c r="H32" s="62"/>
+      <c r="G32" s="119"/>
+      <c r="H32" s="120"/>
       <c r="I32" s="7"/>
       <c r="J32" s="8"/>
       <c r="K32" s="8"/>
@@ -46279,17 +46288,17 @@
       <c r="A33" s="13">
         <v>2</v>
       </c>
-      <c r="B33" s="89" t="s">
+      <c r="B33" s="124" t="s">
         <v>19</v>
       </c>
-      <c r="C33" s="61"/>
-      <c r="D33" s="61"/>
-      <c r="E33" s="62"/>
-      <c r="F33" s="63">
+      <c r="C33" s="119"/>
+      <c r="D33" s="119"/>
+      <c r="E33" s="120"/>
+      <c r="F33" s="125">
         <v>50</v>
       </c>
-      <c r="G33" s="61"/>
-      <c r="H33" s="62"/>
+      <c r="G33" s="119"/>
+      <c r="H33" s="120"/>
       <c r="I33" s="7"/>
       <c r="J33" s="8"/>
       <c r="K33" s="8"/>
@@ -46313,17 +46322,17 @@
       <c r="A34" s="13">
         <v>1</v>
       </c>
-      <c r="B34" s="60" t="s">
+      <c r="B34" s="126" t="s">
         <v>20</v>
       </c>
-      <c r="C34" s="61"/>
-      <c r="D34" s="61"/>
-      <c r="E34" s="62"/>
-      <c r="F34" s="63">
+      <c r="C34" s="119"/>
+      <c r="D34" s="119"/>
+      <c r="E34" s="120"/>
+      <c r="F34" s="125">
         <v>30</v>
       </c>
-      <c r="G34" s="61"/>
-      <c r="H34" s="62"/>
+      <c r="G34" s="119"/>
+      <c r="H34" s="120"/>
       <c r="I34" s="7"/>
       <c r="J34" s="8"/>
       <c r="K34" s="8"/>
@@ -46412,16 +46421,16 @@
       <c r="D37" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="E37" s="163">
+      <c r="E37" s="237">
         <v>1</v>
       </c>
-      <c r="F37" s="163">
+      <c r="F37" s="237">
         <v>0</v>
       </c>
-      <c r="G37" s="164" t="s">
+      <c r="G37" s="196" t="s">
         <v>25</v>
       </c>
-      <c r="H37" s="166" t="s">
+      <c r="H37" s="198" t="s">
         <v>26</v>
       </c>
       <c r="I37" s="7"/>
@@ -46450,10 +46459,10 @@
       <c r="D38" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="E38" s="62"/>
-      <c r="F38" s="62"/>
-      <c r="G38" s="165"/>
-      <c r="H38" s="167"/>
+      <c r="E38" s="120"/>
+      <c r="F38" s="120"/>
+      <c r="G38" s="197"/>
+      <c r="H38" s="199"/>
       <c r="I38" s="7"/>
       <c r="J38" s="8"/>
       <c r="K38" s="8"/>
@@ -52303,6 +52312,47 @@
     <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="57">
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="B34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="A23:A26"/>
+    <mergeCell ref="G37:G38"/>
+    <mergeCell ref="H37:H38"/>
+    <mergeCell ref="B31:E31"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="E37:E38"/>
+    <mergeCell ref="F37:F38"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:F19"/>
     <mergeCell ref="B30:E30"/>
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="A6:H6"/>
@@ -52319,47 +52369,6 @@
     <mergeCell ref="D15:G16"/>
     <mergeCell ref="H15:J15"/>
     <mergeCell ref="A17:A22"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="E37:E38"/>
-    <mergeCell ref="F37:F38"/>
-    <mergeCell ref="G37:G38"/>
-    <mergeCell ref="H37:H38"/>
-    <mergeCell ref="B31:E31"/>
-    <mergeCell ref="F31:H31"/>
-    <mergeCell ref="B32:E32"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="B33:E33"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A10:H10"/>
-    <mergeCell ref="A11:H11"/>
-    <mergeCell ref="B34:E34"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="F28:H28"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="F29:H29"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="A23:A26"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
